--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B121" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C121" t="n" s="2">
-        <v>44561.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D121" t="n">
         <v>1.0</v>
@@ -1833,13 +1833,13 @@
         <v>5</v>
       </c>
       <c r="B122" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D122" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="123">
@@ -1850,10 +1850,10 @@
         <v>2022.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D123" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D124" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D125" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D126" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D127" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,7 +1920,7 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D128" t="n">
         <v>1.0</v>
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D129" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D130" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D131" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D132" t="n">
         <v>2.0</v>
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D133" t="n">
         <v>2.0</v>
@@ -2004,10 +2004,10 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D134" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="135">
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D135" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D136" t="n">
         <v>3.0</v>
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D137" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="138">
@@ -2060,10 +2060,10 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D138" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="139">
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D139" t="n">
         <v>3.0</v>
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D140" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D141" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D142" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,7 +2130,7 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D143" t="n">
         <v>1.0</v>
@@ -2144,7 +2144,7 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D144" t="n">
         <v>1.0</v>
@@ -2158,7 +2158,7 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D145" t="n">
         <v>1.0</v>
@@ -2172,7 +2172,7 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D146" t="n">
         <v>1.0</v>
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,10 +2312,10 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D156" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="157">
@@ -2326,10 +2326,10 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D157" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,7 +2340,7 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D158" t="n">
         <v>1.0</v>
@@ -2354,7 +2354,7 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D159" t="n">
         <v>1.0</v>
@@ -2368,10 +2368,10 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D160" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="161">
@@ -2379,13 +2379,13 @@
         <v>5</v>
       </c>
       <c r="B161" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D161" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2023.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D162" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D163" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D164" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D165" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,7 +2452,7 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D166" t="n">
         <v>4.0</v>
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D167" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D168" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D169" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D170" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D171" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D172" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D173" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D174" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D175" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D176" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D177" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D178" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D179" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D180" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D181" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D182" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D183" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D184" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D185" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D186" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D187" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D188" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D189" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D190" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D191" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,7 +2816,7 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D192" t="n">
         <v>2.0</v>
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D193" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,7 +2844,7 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D194" t="n">
         <v>5.0</v>
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D195" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D196" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D197" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,7 +2900,7 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D198" t="n">
         <v>1.0</v>
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D199" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D200" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D201" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,7 +2956,7 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D202" t="n">
         <v>8.0</v>
@@ -2970,10 +2970,10 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D203" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D204" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,7 +2998,7 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D205" t="n">
         <v>9.0</v>
@@ -3012,10 +3012,10 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D206" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D207" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D208" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D209" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D210" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D211" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D212" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="213">
@@ -3107,13 +3107,13 @@
         <v>5</v>
       </c>
       <c r="B213" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D213" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2024.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D214" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D215" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D216" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D217" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D218" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D219" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D220" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D221" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D222" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D223" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D224" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D225" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D226" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D227" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D228" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D229" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D230" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D231" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D232" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D233" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D234" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D235" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D236" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D237" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D238" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,7 +3474,7 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D239" t="n">
         <v>12.0</v>
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D240" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D241" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D242" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D243" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D244" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,7 +3558,7 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D245" t="n">
         <v>4.0</v>
@@ -3572,7 +3572,7 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D246" t="n">
         <v>4.0</v>
@@ -3586,7 +3586,7 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D247" t="n">
         <v>4.0</v>
@@ -3600,10 +3600,10 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D248" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D249" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D250" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D251" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D252" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D253" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D254" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,7 +3698,7 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D255" t="n">
         <v>3.0</v>
@@ -3712,10 +3712,10 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D256" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,7 +3726,7 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D257" t="n">
         <v>1.0</v>
@@ -3737,13 +3737,13 @@
         <v>5</v>
       </c>
       <c r="B258" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D258" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2025.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D259" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,7 +3768,7 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D260" t="n">
         <v>1.0</v>
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D261" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D262" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D263" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D264" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D265" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D266" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D267" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D268" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D269" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D270" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D271" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D272" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D273" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D274" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D275" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D276" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D277" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,7 +4020,7 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D278" t="n">
         <v>4.0</v>
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D279" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D280" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D281" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D282" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,7 +4090,7 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D283" t="n">
         <v>1.0</v>
@@ -4104,10 +4104,10 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D284" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,7 +4118,7 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D285" t="n">
         <v>3.0</v>
@@ -4132,10 +4132,10 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D286" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D287" t="n">
         <v>1.0</v>
@@ -4160,10 +4160,10 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D288" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,10 +4174,10 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D289" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,10 +4188,10 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D290" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D291" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D292" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D293" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="294">
@@ -4241,13 +4241,13 @@
         <v>5</v>
       </c>
       <c r="B294" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D294" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2026.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D295" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D296" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D297" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D298" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D299" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D300" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,7 +4342,7 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D301" t="n">
         <v>5.0</v>
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D302" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,7 +4370,7 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D303" t="n">
         <v>2.0</v>
@@ -4384,10 +4384,10 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D304" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D305" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D306" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D307" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D308" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,7 +4454,7 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D309" t="n">
         <v>4.0</v>
@@ -4468,10 +4468,10 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D310" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D311" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D312" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D313" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D314" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D315" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D316" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D317" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D318" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D319" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D320" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D321" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D322" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D323" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D324" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,24 +4678,24 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D325" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B326" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>45095.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D326" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,7 +4706,7 @@
         <v>2023.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D327" t="n">
         <v>1.0</v>
@@ -4720,7 +4720,7 @@
         <v>2023.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D328" t="n">
         <v>1.0</v>
@@ -4734,10 +4734,10 @@
         <v>2023.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D329" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,7 +4748,7 @@
         <v>2023.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D330" t="n">
         <v>3.0</v>
@@ -4762,10 +4762,10 @@
         <v>2023.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D331" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2023.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D332" t="n">
         <v>1.0</v>
@@ -4790,10 +4790,10 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D333" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D334" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D335" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D336" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D338" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4871,13 +4871,13 @@
         <v>6</v>
       </c>
       <c r="B339" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D339" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2024.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D340" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D341" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D342" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D343" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D344" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,7 +4958,7 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D345" t="n">
         <v>12.0</v>
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D346" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D347" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D348" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D349" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D350" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D351" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D352" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D353" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D354" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D355" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D356" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D357" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,7 +5140,7 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D358" t="n">
         <v>6.0</v>
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D359" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D360" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,7 +5182,7 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D361" t="n">
         <v>4.0</v>
@@ -5196,7 +5196,7 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D362" t="n">
         <v>4.0</v>
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D363" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D364" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D365" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D366" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D368" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,7 +5294,7 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D369" t="n">
         <v>1.0</v>
@@ -5308,7 +5308,7 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5322,7 +5322,7 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D372" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D373" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D374" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D375" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,7 +5392,7 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5406,7 +5406,7 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5417,13 +5417,13 @@
         <v>6</v>
       </c>
       <c r="B378" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D378" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2025.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D379" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2025.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D380" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2025.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D381" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2025.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D382" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2025.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D383" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2025.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D384" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D385" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D386" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D387" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D388" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D389" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D390" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D391" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D392" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,7 +5630,7 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D393" t="n">
         <v>4.0</v>
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D394" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,7 +5658,7 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D395" t="n">
         <v>1.0</v>
@@ -5672,7 +5672,7 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D396" t="n">
         <v>1.0</v>
@@ -5686,7 +5686,7 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D397" t="n">
         <v>1.0</v>
@@ -5700,7 +5700,7 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D398" t="n">
         <v>1.0</v>
@@ -5711,10 +5711,10 @@
         <v>6</v>
       </c>
       <c r="B399" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D399" t="n">
         <v>1.0</v>
@@ -5728,7 +5728,7 @@
         <v>2026.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D400" t="n">
         <v>1.0</v>
@@ -5736,13 +5736,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B401" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5753,10 +5753,10 @@
         <v>7</v>
       </c>
       <c r="B402" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5770,10 +5770,10 @@
         <v>2022.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D403" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D404" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D405" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D406" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,7 +5826,7 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D407" t="n">
         <v>3.0</v>
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D408" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,7 +5854,7 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D409" t="n">
         <v>5.0</v>
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D410" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D411" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D412" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D413" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D414" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D415" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D416" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D417" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D418" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D419" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D420" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D421" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D422" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D423" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D424" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,7 +6078,7 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D425" t="n">
         <v>4.0</v>
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D426" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D427" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D428" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D429" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D430" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D431" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D432" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D433" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D434" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,7 +6218,7 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D435" t="n">
         <v>2.0</v>
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D436" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D437" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D438" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D439" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="440">
@@ -6285,13 +6285,13 @@
         <v>7</v>
       </c>
       <c r="B440" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D440" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2023.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D441" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D442" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D443" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D444" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D445" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D446" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D447" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D448" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D449" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D450" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D451" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D452" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D453" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D454" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D455" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D456" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D457" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D458" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D459" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,7 +6568,7 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D460" t="n">
         <v>8.0</v>
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D461" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D462" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D463" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D464" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D465" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D466" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D467" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,7 +6680,7 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D468" t="n">
         <v>6.0</v>
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D469" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,7 +6708,7 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D470" t="n">
         <v>2.0</v>
@@ -6722,7 +6722,7 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D471" t="n">
         <v>2.0</v>
@@ -6736,7 +6736,7 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D472" t="n">
         <v>2.0</v>
@@ -6750,7 +6750,7 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D473" t="n">
         <v>2.0</v>
@@ -6764,10 +6764,10 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D474" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D475" t="n">
         <v>1.0</v>
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,10 +6848,10 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D480" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,10 +6862,10 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D481" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D482" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D483" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D484" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D485" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,7 +6932,7 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D486" t="n">
         <v>7.0</v>
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D487" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="488">
@@ -6957,13 +6957,13 @@
         <v>7</v>
       </c>
       <c r="B488" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D488" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2024.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D489" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2024.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D490" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2024.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D491" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D492" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D493" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D494" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D495" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D496" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D497" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D498" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D499" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D500" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D501" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,7 +7156,7 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D502" t="n">
         <v>1.0</v>
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D503" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D505" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,7 +7226,7 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,7 +7240,7 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,7 +7254,7 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,7 +7268,7 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,7 +7282,7 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,10 +7310,10 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D513" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D514" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D515" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D516" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="517">
@@ -7363,13 +7363,13 @@
         <v>7</v>
       </c>
       <c r="B517" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D517" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2025.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D518" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,7 +7394,7 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D519" t="n">
         <v>2.0</v>
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D520" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D521" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D522" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D523" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D524" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D525" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D526" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D527" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D528" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D529" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D530" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,7 +7562,7 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D531" t="n">
         <v>1.0</v>
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D532" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D533" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D535" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D536" t="n">
         <v>2.0</v>
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D537" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D538" t="n">
         <v>1.0</v>
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D541" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D542" t="n">
         <v>2.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D543" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7755,10 +7755,10 @@
         <v>7</v>
       </c>
       <c r="B545" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
         <v>2026.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2026.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,10 +7800,10 @@
         <v>2026.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D548" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,10 +7814,10 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D549" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D550" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D551" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D552" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D553" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,7 +7884,7 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D554" t="n">
         <v>1.0</v>
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D555" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D556" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D557" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,7 +7940,7 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D558" t="n">
         <v>1.0</v>
@@ -7954,24 +7954,24 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D559" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B560" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>45495.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D560" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2024.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D561" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="562">
@@ -7993,13 +7993,13 @@
         <v>8</v>
       </c>
       <c r="B562" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D562" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2025.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D563" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D564" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D565" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D566" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D567" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D568" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D569" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D570" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D571" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,7 +8136,7 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D572" t="n">
         <v>1.0</v>
@@ -8150,7 +8150,7 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D573" t="n">
         <v>1.0</v>
@@ -8164,7 +8164,7 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D574" t="n">
         <v>1.0</v>
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D575" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D576" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,7 +8206,7 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D577" t="n">
         <v>1.0</v>
@@ -8220,7 +8220,7 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D578" t="n">
         <v>1.0</v>
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D579" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,7 +8248,7 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D580" t="n">
         <v>2.0</v>
@@ -8262,7 +8262,7 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D581" t="n">
         <v>2.0</v>
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D582" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D583" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D584" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D585" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D586" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,7 +8346,7 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D587" t="n">
         <v>1.0</v>
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D589" t="n">
         <v>1.0</v>
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D590" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D591" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,7 +8416,7 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D592" t="n">
         <v>2.0</v>
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D593" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D594" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D595" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D596" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D597" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D598" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D599" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D600" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D601" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="602">
@@ -8553,13 +8553,13 @@
         <v>8</v>
       </c>
       <c r="B602" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D602" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2026.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D603" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2026.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D604" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2026.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D605" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2026.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D606" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2026.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D607" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2026.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D608" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2026.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D609" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2026.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D610" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2026.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D611" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D612" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D613" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D614" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D615" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D616" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D617" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D618" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D619" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D620" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D621" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D622" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D623" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D624" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D625" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D626" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D627" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D628" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D629" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D630" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D631" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D632" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D633" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D634" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D635" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,38 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
+        <v>46261.0</v>
+      </c>
+      <c r="D636" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="s">
+        <v>8</v>
+      </c>
+      <c r="B637" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C637" t="n" s="2">
         <v>46268.0</v>
       </c>
-      <c r="D636" t="n">
-        <v>1.0</v>
+      <c r="D637" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="s">
+        <v>8</v>
+      </c>
+      <c r="B638" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C638" t="n" s="2">
+        <v>46275.0</v>
+      </c>
+      <c r="D638" t="n">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -9069,7 +9097,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="4">
@@ -9077,7 +9105,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1556.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="5">
@@ -9085,7 +9113,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2262.0</v>
+        <v>2263.0</v>
       </c>
     </row>
   </sheetData>
@@ -9128,7 +9156,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
     </row>
     <row r="4">
@@ -9249,7 +9277,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>506.0</v>
+        <v>507.0</v>
       </c>
     </row>
     <row r="15">
@@ -9260,7 +9288,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>414.0</v>
+        <v>415.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B122" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C122" t="n" s="2">
-        <v>44561.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D122" t="n">
         <v>1.0</v>
@@ -1847,13 +1847,13 @@
         <v>5</v>
       </c>
       <c r="B123" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D123" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="124">
@@ -1864,10 +1864,10 @@
         <v>2022.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D124" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D125" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D126" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D127" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D128" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,7 +1934,7 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D129" t="n">
         <v>1.0</v>
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D130" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D131" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,10 +1976,10 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D132" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="133">
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D133" t="n">
         <v>2.0</v>
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D134" t="n">
         <v>2.0</v>
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D135" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,10 +2032,10 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D136" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="137">
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D137" t="n">
         <v>3.0</v>
@@ -2060,10 +2060,10 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D138" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="139">
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D139" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D140" t="n">
         <v>3.0</v>
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D141" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D142" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D143" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,7 +2144,7 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D144" t="n">
         <v>1.0</v>
@@ -2158,7 +2158,7 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D145" t="n">
         <v>1.0</v>
@@ -2172,7 +2172,7 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D146" t="n">
         <v>1.0</v>
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,7 +2312,7 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D156" t="n">
         <v>1.0</v>
@@ -2326,10 +2326,10 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D157" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="158">
@@ -2340,10 +2340,10 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D158" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,7 +2354,7 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D159" t="n">
         <v>1.0</v>
@@ -2368,7 +2368,7 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D160" t="n">
         <v>1.0</v>
@@ -2382,10 +2382,10 @@
         <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D161" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="162">
@@ -2393,13 +2393,13 @@
         <v>5</v>
       </c>
       <c r="B162" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D162" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2023.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D163" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D164" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D165" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D166" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,7 +2466,7 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D167" t="n">
         <v>4.0</v>
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D168" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D169" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D170" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D171" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D172" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D173" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D174" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D175" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D176" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D177" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D178" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D179" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D180" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D181" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D182" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D183" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D184" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D185" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D186" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D187" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D188" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D189" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D190" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D191" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D192" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,7 +2830,7 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D193" t="n">
         <v>2.0</v>
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D194" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,7 +2858,7 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D195" t="n">
         <v>5.0</v>
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D196" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D197" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D198" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,7 +2914,7 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D199" t="n">
         <v>1.0</v>
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D200" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D201" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D202" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,7 +2970,7 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D203" t="n">
         <v>8.0</v>
@@ -2984,10 +2984,10 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D204" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D205" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,7 +3012,7 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D206" t="n">
         <v>9.0</v>
@@ -3026,10 +3026,10 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D207" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D208" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D209" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D210" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D211" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D212" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D213" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="214">
@@ -3121,13 +3121,13 @@
         <v>5</v>
       </c>
       <c r="B214" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D214" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2024.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D215" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D216" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D217" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D218" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D219" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D220" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D221" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D222" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D223" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D224" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D225" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D226" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D227" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D228" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D229" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D230" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D231" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D232" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D233" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D234" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D235" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D236" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D237" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D238" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D239" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,7 +3488,7 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D240" t="n">
         <v>12.0</v>
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D241" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D242" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D243" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D244" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D245" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,7 +3572,7 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D246" t="n">
         <v>4.0</v>
@@ -3586,7 +3586,7 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D247" t="n">
         <v>4.0</v>
@@ -3600,7 +3600,7 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D248" t="n">
         <v>4.0</v>
@@ -3614,10 +3614,10 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D249" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D250" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D251" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D252" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D253" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D254" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D255" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,7 +3712,7 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D256" t="n">
         <v>3.0</v>
@@ -3726,10 +3726,10 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D257" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,7 +3740,7 @@
         <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D258" t="n">
         <v>1.0</v>
@@ -3751,13 +3751,13 @@
         <v>5</v>
       </c>
       <c r="B259" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D259" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2025.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D260" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,7 +3782,7 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D261" t="n">
         <v>1.0</v>
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D262" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D264" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D265" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D266" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D267" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D269" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D270" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D271" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D272" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D273" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D274" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D275" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D276" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D277" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D278" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,7 +4034,7 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D279" t="n">
         <v>4.0</v>
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D280" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D281" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D282" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D283" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,7 +4104,7 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D284" t="n">
         <v>1.0</v>
@@ -4118,10 +4118,10 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D285" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,7 +4132,7 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D286" t="n">
         <v>3.0</v>
@@ -4146,10 +4146,10 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D287" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D288" t="n">
         <v>1.0</v>
@@ -4174,10 +4174,10 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D289" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,10 +4188,10 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D290" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D291" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D292" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D293" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D294" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="295">
@@ -4255,13 +4255,13 @@
         <v>5</v>
       </c>
       <c r="B295" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D295" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2026.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D296" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D297" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D298" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D299" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D300" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D301" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,7 +4356,7 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D302" t="n">
         <v>5.0</v>
@@ -4370,10 +4370,10 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D303" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,7 +4384,7 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D304" t="n">
         <v>2.0</v>
@@ -4398,10 +4398,10 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D305" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D306" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D307" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D308" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D309" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,7 +4468,7 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D310" t="n">
         <v>4.0</v>
@@ -4482,10 +4482,10 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D311" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D312" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D313" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D314" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D315" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D316" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D317" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D318" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D319" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D320" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D321" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D322" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D323" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D324" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D325" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,24 +4692,24 @@
         <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D326" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B327" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>45095.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D327" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,7 +4720,7 @@
         <v>2023.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D328" t="n">
         <v>1.0</v>
@@ -4734,7 +4734,7 @@
         <v>2023.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D329" t="n">
         <v>1.0</v>
@@ -4748,10 +4748,10 @@
         <v>2023.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D330" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,7 +4762,7 @@
         <v>2023.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D331" t="n">
         <v>3.0</v>
@@ -4776,10 +4776,10 @@
         <v>2023.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D332" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,7 +4790,7 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,10 +4804,10 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D334" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,10 +4818,10 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D335" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D336" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D337" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D339" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4885,13 +4885,13 @@
         <v>6</v>
       </c>
       <c r="B340" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D340" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2024.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D341" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D342" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D343" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D344" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D345" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,7 +4972,7 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D346" t="n">
         <v>12.0</v>
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D347" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D348" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D349" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D350" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D351" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D352" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D353" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D354" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D355" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D356" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D357" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D358" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,7 +5154,7 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D359" t="n">
         <v>6.0</v>
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D360" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D361" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,7 +5196,7 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D362" t="n">
         <v>4.0</v>
@@ -5210,7 +5210,7 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D363" t="n">
         <v>4.0</v>
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D364" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D365" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D366" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D367" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D368" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D369" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,7 +5308,7 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D370" t="n">
         <v>1.0</v>
@@ -5322,7 +5322,7 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5336,7 +5336,7 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D374" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D376" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,7 +5406,7 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5420,7 +5420,7 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5431,13 +5431,13 @@
         <v>6</v>
       </c>
       <c r="B379" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D379" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2025.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D380" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2025.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D381" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2025.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D382" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2025.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D383" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2025.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D384" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D385" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D386" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D387" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D388" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D389" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D390" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D391" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D392" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D393" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,7 +5644,7 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D394" t="n">
         <v>4.0</v>
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D395" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,7 +5672,7 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D396" t="n">
         <v>1.0</v>
@@ -5686,7 +5686,7 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D397" t="n">
         <v>1.0</v>
@@ -5700,7 +5700,7 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D398" t="n">
         <v>1.0</v>
@@ -5714,7 +5714,7 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D399" t="n">
         <v>1.0</v>
@@ -5725,10 +5725,10 @@
         <v>6</v>
       </c>
       <c r="B400" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D400" t="n">
         <v>1.0</v>
@@ -5742,7 +5742,7 @@
         <v>2026.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5750,13 +5750,13 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B402" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5767,10 +5767,10 @@
         <v>7</v>
       </c>
       <c r="B403" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5784,10 +5784,10 @@
         <v>2022.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D404" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D405" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D406" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D407" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,7 +5840,7 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D408" t="n">
         <v>3.0</v>
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D409" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,7 +5868,7 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D410" t="n">
         <v>5.0</v>
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D411" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D412" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D413" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D414" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D415" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D416" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D417" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D418" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D419" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D420" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D421" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D422" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D423" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D424" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D425" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,7 +6092,7 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D426" t="n">
         <v>4.0</v>
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D427" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D428" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D429" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D430" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D431" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D432" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D433" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D434" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D435" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,7 +6232,7 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D436" t="n">
         <v>2.0</v>
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D437" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D438" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D439" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D440" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="441">
@@ -6299,13 +6299,13 @@
         <v>7</v>
       </c>
       <c r="B441" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D441" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2023.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D442" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D443" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D444" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D445" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D446" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D447" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D448" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D449" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D450" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D451" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D452" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D453" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D454" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D455" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D456" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D457" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D458" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D459" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D460" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,7 +6582,7 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D461" t="n">
         <v>8.0</v>
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D462" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D463" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D464" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D465" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D466" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D467" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D468" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,7 +6694,7 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D469" t="n">
         <v>6.0</v>
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D470" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,7 +6722,7 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D471" t="n">
         <v>2.0</v>
@@ -6736,7 +6736,7 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D472" t="n">
         <v>2.0</v>
@@ -6750,7 +6750,7 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D473" t="n">
         <v>2.0</v>
@@ -6764,7 +6764,7 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D474" t="n">
         <v>2.0</v>
@@ -6778,10 +6778,10 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D475" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D476" t="n">
         <v>1.0</v>
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,10 +6862,10 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D481" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,10 +6876,10 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D482" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D483" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D484" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D485" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D486" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,7 +6946,7 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D487" t="n">
         <v>7.0</v>
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D488" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="489">
@@ -6971,13 +6971,13 @@
         <v>7</v>
       </c>
       <c r="B489" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D489" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2024.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D490" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2024.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D491" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D492" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D493" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D494" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D495" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D496" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D497" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D498" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D499" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D500" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D501" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D502" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,7 +7170,7 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D503" t="n">
         <v>1.0</v>
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D504" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D506" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,7 +7240,7 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,7 +7254,7 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,7 +7268,7 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,7 +7282,7 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,10 +7324,10 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D514" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D515" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D516" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D517" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="518">
@@ -7377,13 +7377,13 @@
         <v>7</v>
       </c>
       <c r="B518" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D518" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2025.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D519" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,7 +7408,7 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D520" t="n">
         <v>2.0</v>
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D521" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D522" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D523" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D524" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D525" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D526" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D527" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D528" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D529" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D530" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D531" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,7 +7576,7 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D532" t="n">
         <v>1.0</v>
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D533" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D534" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D535" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D536" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D537" t="n">
         <v>2.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D538" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D542" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D543" t="n">
         <v>2.0</v>
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D544" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7769,10 +7769,10 @@
         <v>7</v>
       </c>
       <c r="B546" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2026.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2026.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,10 +7814,10 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D549" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,10 +7828,10 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D550" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D551" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D552" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D553" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D554" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,7 +7898,7 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D555" t="n">
         <v>1.0</v>
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D556" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D557" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D558" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,7 +7954,7 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D559" t="n">
         <v>1.0</v>
@@ -7968,24 +7968,24 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D560" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B561" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>45495.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D561" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2024.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D562" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="563">
@@ -8007,13 +8007,13 @@
         <v>8</v>
       </c>
       <c r="B563" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D563" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2025.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D564" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2025.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D565" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D566" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D567" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D568" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D569" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D570" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D571" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D572" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,7 +8150,7 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D573" t="n">
         <v>1.0</v>
@@ -8164,7 +8164,7 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D574" t="n">
         <v>1.0</v>
@@ -8178,7 +8178,7 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D575" t="n">
         <v>1.0</v>
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D576" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D577" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,7 +8220,7 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D578" t="n">
         <v>1.0</v>
@@ -8234,7 +8234,7 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D579" t="n">
         <v>1.0</v>
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D580" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,7 +8262,7 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D581" t="n">
         <v>2.0</v>
@@ -8276,7 +8276,7 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D582" t="n">
         <v>2.0</v>
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D583" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D584" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D585" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D586" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D587" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D589" t="n">
         <v>1.0</v>
@@ -8388,7 +8388,7 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D590" t="n">
         <v>1.0</v>
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D591" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D592" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D593" t="n">
         <v>2.0</v>
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D594" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D595" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D596" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D597" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D598" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D599" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D600" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D601" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D602" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="603">
@@ -8567,13 +8567,13 @@
         <v>8</v>
       </c>
       <c r="B603" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D603" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2026.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D604" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2026.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D605" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2026.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D606" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2026.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D607" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2026.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D608" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2026.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D609" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2026.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D610" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2026.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D611" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D612" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D613" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D614" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D615" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D616" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D617" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D618" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D619" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D620" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D621" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D622" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D623" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D624" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D625" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D626" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D627" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D628" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D629" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D630" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D631" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D632" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D633" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D634" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D635" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D636" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,7 +9046,7 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D637" t="n">
         <v>1.0</v>
@@ -9060,9 +9060,23 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="D638" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="s">
+        <v>8</v>
+      </c>
+      <c r="B639" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C639" t="n" s="2">
         <v>46275.0</v>
       </c>
-      <c r="D638" t="n">
+      <c r="D639" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -9113,7 +9127,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2263.0</v>
+        <v>2264.0</v>
       </c>
     </row>
   </sheetData>
@@ -9156,7 +9170,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
     </row>
     <row r="4">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1825,7 +1825,7 @@
         <v>46275.0</v>
       </c>
       <c r="D121" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
@@ -9127,7 +9127,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2264.0</v>
+        <v>2265.0</v>
       </c>
     </row>
   </sheetData>
@@ -9192,7 +9192,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>478.0</v>
+        <v>479.0</v>
       </c>
     </row>
     <row r="6">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -7985,18 +7985,18 @@
         <v>46268.0</v>
       </c>
       <c r="D561" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B562" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>45495.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D562" t="n">
         <v>1.0</v>
@@ -8004,16 +8004,16 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B563" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>45502.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D563" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="564">
@@ -8021,10 +8021,10 @@
         <v>8</v>
       </c>
       <c r="B564" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D564" t="n">
         <v>1.0</v>
@@ -8035,13 +8035,13 @@
         <v>8</v>
       </c>
       <c r="B565" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D565" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,7 +8052,7 @@
         <v>2025.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D566" t="n">
         <v>1.0</v>
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D567" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,7 +8080,7 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D568" t="n">
         <v>1.0</v>
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D569" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D570" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D571" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D572" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D573" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D574" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,7 +8178,7 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D575" t="n">
         <v>1.0</v>
@@ -8192,7 +8192,7 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D576" t="n">
         <v>1.0</v>
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D577" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,7 +8220,7 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D578" t="n">
         <v>1.0</v>
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D579" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,7 +8248,7 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D580" t="n">
         <v>1.0</v>
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D581" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D582" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,7 +8290,7 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D583" t="n">
         <v>2.0</v>
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D584" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D585" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D586" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D587" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D588" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D589" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,7 +8388,7 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D590" t="n">
         <v>1.0</v>
@@ -8402,7 +8402,7 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D591" t="n">
         <v>1.0</v>
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D592" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D593" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D594" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D595" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D596" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D597" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D598" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D599" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D600" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D601" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D602" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D603" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="604">
@@ -8581,13 +8581,13 @@
         <v>8</v>
       </c>
       <c r="B604" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D604" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="605">
@@ -8595,13 +8595,13 @@
         <v>8</v>
       </c>
       <c r="B605" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D605" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2026.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D606" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2026.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D607" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2026.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D608" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2026.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D609" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2026.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D610" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2026.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D611" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D612" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D613" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D614" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D615" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D616" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46121.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D617" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46128.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D618" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46135.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D619" t="n">
-        <v>35.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46142.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D620" t="n">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46149.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D621" t="n">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46156.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D622" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46163.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D623" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46170.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D624" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D625" t="n">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46184.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D626" t="n">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46191.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D627" t="n">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46198.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D628" t="n">
-        <v>9.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46205.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D629" t="n">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46212.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D630" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46219.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D631" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46226.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D632" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46233.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D633" t="n">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D634" t="n">
-        <v>25.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46247.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D635" t="n">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D636" t="n">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46261.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D637" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D638" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,9 +9074,37 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
+        <v>46261.0</v>
+      </c>
+      <c r="D639" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="s">
+        <v>8</v>
+      </c>
+      <c r="B640" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C640" t="n" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="D640" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="s">
+        <v>8</v>
+      </c>
+      <c r="B641" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C641" t="n" s="2">
         <v>46275.0</v>
       </c>
-      <c r="D639" t="n">
+      <c r="D641" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -9119,7 +9147,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1557.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="5">
@@ -9127,7 +9155,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2265.0</v>
+        <v>2267.0</v>
       </c>
     </row>
   </sheetData>
@@ -9159,7 +9187,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
     </row>
     <row r="3">
@@ -9181,7 +9209,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="5">
@@ -9291,7 +9319,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>507.0</v>
+        <v>508.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B328" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>45095.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D328" t="n">
         <v>1.0</v>
@@ -4734,7 +4734,7 @@
         <v>2023.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D329" t="n">
         <v>1.0</v>
@@ -4748,7 +4748,7 @@
         <v>2023.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D330" t="n">
         <v>1.0</v>
@@ -4762,10 +4762,10 @@
         <v>2023.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D331" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2023.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D332" t="n">
         <v>3.0</v>
@@ -4790,10 +4790,10 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D333" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,7 +4804,7 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,10 +4818,10 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D335" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,10 +4832,10 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D336" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D338" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D340" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="341">
@@ -4899,13 +4899,13 @@
         <v>6</v>
       </c>
       <c r="B341" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D341" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2024.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D342" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D343" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D344" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D345" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D346" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,7 +4986,7 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D347" t="n">
         <v>12.0</v>
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D348" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D349" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D350" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D351" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D352" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D353" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D354" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D355" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D356" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D357" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D358" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D359" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,7 +5168,7 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D360" t="n">
         <v>6.0</v>
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D361" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D362" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,7 +5210,7 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D363" t="n">
         <v>4.0</v>
@@ -5224,7 +5224,7 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D364" t="n">
         <v>4.0</v>
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D365" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D366" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D368" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D369" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D370" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,7 +5322,7 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D371" t="n">
         <v>1.0</v>
@@ -5336,7 +5336,7 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5350,7 +5350,7 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D374" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D375" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D376" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D377" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,7 +5420,7 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5434,7 +5434,7 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D379" t="n">
         <v>1.0</v>
@@ -5445,13 +5445,13 @@
         <v>6</v>
       </c>
       <c r="B380" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D380" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2025.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D381" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2025.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D382" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2025.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D383" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2025.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D384" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D385" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D386" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D387" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D388" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D389" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D390" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D391" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D392" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D393" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D394" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,7 +5658,7 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D395" t="n">
         <v>4.0</v>
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D396" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,7 +5686,7 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D397" t="n">
         <v>1.0</v>
@@ -5700,7 +5700,7 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D398" t="n">
         <v>1.0</v>
@@ -5714,7 +5714,7 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D399" t="n">
         <v>1.0</v>
@@ -5728,7 +5728,7 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D400" t="n">
         <v>1.0</v>
@@ -5739,10 +5739,10 @@
         <v>6</v>
       </c>
       <c r="B401" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5756,7 +5756,7 @@
         <v>2026.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5764,13 +5764,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B403" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5781,10 +5781,10 @@
         <v>7</v>
       </c>
       <c r="B404" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5798,10 +5798,10 @@
         <v>2022.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D405" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="406">
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D406" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D407" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D408" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,7 +5854,7 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D409" t="n">
         <v>3.0</v>
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D410" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,7 +5882,7 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D411" t="n">
         <v>5.0</v>
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D412" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D413" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D414" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D415" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D416" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D417" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D418" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D419" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D420" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D421" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D422" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D423" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D424" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D425" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D426" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,7 +6106,7 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D427" t="n">
         <v>4.0</v>
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D428" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D429" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D430" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D431" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D432" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D433" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D434" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D435" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D436" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,7 +6246,7 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D437" t="n">
         <v>2.0</v>
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D438" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D439" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D440" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D441" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="442">
@@ -6313,13 +6313,13 @@
         <v>7</v>
       </c>
       <c r="B442" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D442" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2023.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D443" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D444" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D445" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D446" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D447" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D448" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D449" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D450" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D451" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D452" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D453" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D454" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D455" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D456" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D457" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D458" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D459" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D460" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D461" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,7 +6596,7 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D462" t="n">
         <v>8.0</v>
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D463" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D464" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D465" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D466" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D467" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D468" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D469" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,7 +6708,7 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D470" t="n">
         <v>6.0</v>
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,7 +6736,7 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D472" t="n">
         <v>2.0</v>
@@ -6750,7 +6750,7 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D473" t="n">
         <v>2.0</v>
@@ -6764,7 +6764,7 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D474" t="n">
         <v>2.0</v>
@@ -6778,7 +6778,7 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D475" t="n">
         <v>2.0</v>
@@ -6792,10 +6792,10 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D476" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D477" t="n">
         <v>1.0</v>
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,10 +6876,10 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D482" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,10 +6890,10 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D483" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D484" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D485" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D486" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D487" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,7 +6960,7 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D488" t="n">
         <v>7.0</v>
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D489" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="490">
@@ -6985,13 +6985,13 @@
         <v>7</v>
       </c>
       <c r="B490" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D490" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2024.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D491" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D492" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D493" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D494" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D495" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D496" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D497" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D498" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D499" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D500" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D501" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D502" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D503" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,7 +7184,7 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D504" t="n">
         <v>1.0</v>
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D505" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D507" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,7 +7254,7 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,7 +7268,7 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,7 +7282,7 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,10 +7338,10 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D515" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D516" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D517" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D518" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="519">
@@ -7391,13 +7391,13 @@
         <v>7</v>
       </c>
       <c r="B519" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D519" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2025.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D520" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,7 +7422,7 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D521" t="n">
         <v>2.0</v>
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D522" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D523" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D524" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D525" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D526" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D527" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D528" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D529" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D530" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D531" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D532" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,7 +7590,7 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D533" t="n">
         <v>1.0</v>
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D534" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D535" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D536" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D537" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D538" t="n">
         <v>2.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D539" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D543" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D544" t="n">
         <v>2.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D545" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7783,10 +7783,10 @@
         <v>7</v>
       </c>
       <c r="B547" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2026.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,7 +7814,7 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,10 +7828,10 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D550" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D551" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D552" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D553" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D554" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D555" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,7 +7912,7 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D556" t="n">
         <v>1.0</v>
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D557" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D558" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D559" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,7 +7968,7 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D560" t="n">
         <v>1.0</v>
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D561" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D562" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,7 +8010,7 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D563" t="n">
         <v>1.0</v>
@@ -8018,13 +8018,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B564" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>45495.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D564" t="n">
         <v>1.0</v>
@@ -8038,10 +8038,10 @@
         <v>2024.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D565" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="566">
@@ -8049,13 +8049,13 @@
         <v>8</v>
       </c>
       <c r="B566" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D566" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2025.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D567" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2025.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D568" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D569" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D570" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D571" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D572" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D573" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D574" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D575" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,7 +8192,7 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D576" t="n">
         <v>1.0</v>
@@ -8206,7 +8206,7 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D577" t="n">
         <v>1.0</v>
@@ -8220,7 +8220,7 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D578" t="n">
         <v>1.0</v>
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D579" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D580" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,7 +8262,7 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D581" t="n">
         <v>1.0</v>
@@ -8276,7 +8276,7 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D582" t="n">
         <v>1.0</v>
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D583" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,7 +8304,7 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D584" t="n">
         <v>2.0</v>
@@ -8318,7 +8318,7 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D585" t="n">
         <v>2.0</v>
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D586" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D587" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D588" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D589" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D590" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,7 +8402,7 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D591" t="n">
         <v>1.0</v>
@@ -8416,7 +8416,7 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D592" t="n">
         <v>1.0</v>
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D593" t="n">
         <v>1.0</v>
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D594" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D595" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,7 +8472,7 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D596" t="n">
         <v>2.0</v>
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D597" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D598" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D599" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D600" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D601" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D602" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D603" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D604" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D605" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="606">
@@ -8609,13 +8609,13 @@
         <v>8</v>
       </c>
       <c r="B606" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D606" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2026.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D607" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2026.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D608" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2026.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D609" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2026.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D610" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2026.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D611" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D612" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D613" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D614" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D615" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D616" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D617" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D618" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D619" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D620" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D621" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D622" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D623" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D624" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D625" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D626" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D627" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D628" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D629" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D630" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D631" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D632" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D633" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D634" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D635" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D636" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D637" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D638" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D639" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,7 +9088,7 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D640" t="n">
         <v>1.0</v>
@@ -9102,9 +9102,23 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="D641" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="s">
+        <v>8</v>
+      </c>
+      <c r="B642" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C642" t="n" s="2">
         <v>46275.0</v>
       </c>
-      <c r="D641" t="n">
+      <c r="D642" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -9155,7 +9169,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2267.0</v>
+        <v>2268.0</v>
       </c>
     </row>
   </sheetData>
@@ -9220,7 +9234,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>479.0</v>
+        <v>480.0</v>
       </c>
     </row>
     <row r="6">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4728,13 +4728,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B329" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>45095.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D329" t="n">
         <v>1.0</v>
@@ -4748,7 +4748,7 @@
         <v>2023.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D330" t="n">
         <v>1.0</v>
@@ -4762,7 +4762,7 @@
         <v>2023.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D331" t="n">
         <v>1.0</v>
@@ -4776,10 +4776,10 @@
         <v>2023.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D332" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,7 +4790,7 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D333" t="n">
         <v>3.0</v>
@@ -4804,10 +4804,10 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D334" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,7 +4818,7 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4832,10 +4832,10 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D336" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D337" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D339" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D340" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D341" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4913,13 +4913,13 @@
         <v>6</v>
       </c>
       <c r="B342" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D342" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2024.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D343" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D344" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D345" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D346" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D347" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,7 +5000,7 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D348" t="n">
         <v>12.0</v>
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D349" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D350" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D351" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D352" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D353" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D354" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D355" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D356" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D357" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D358" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D359" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D360" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,7 +5182,7 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D361" t="n">
         <v>6.0</v>
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D362" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D363" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,7 +5224,7 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D364" t="n">
         <v>4.0</v>
@@ -5238,7 +5238,7 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D365" t="n">
         <v>4.0</v>
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D366" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D367" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D368" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D369" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D370" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D371" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,7 +5336,7 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D372" t="n">
         <v>1.0</v>
@@ -5350,7 +5350,7 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5364,7 +5364,7 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D376" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D377" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D378" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,7 +5434,7 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D379" t="n">
         <v>1.0</v>
@@ -5448,7 +5448,7 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D380" t="n">
         <v>1.0</v>
@@ -5459,13 +5459,13 @@
         <v>6</v>
       </c>
       <c r="B381" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D381" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2025.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D382" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2025.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D383" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2025.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D384" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D385" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D386" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D387" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D388" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D389" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D390" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D391" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D392" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D393" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D394" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D395" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,7 +5672,7 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D396" t="n">
         <v>4.0</v>
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D397" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,7 +5700,7 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D398" t="n">
         <v>1.0</v>
@@ -5714,7 +5714,7 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D399" t="n">
         <v>1.0</v>
@@ -5728,7 +5728,7 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D400" t="n">
         <v>1.0</v>
@@ -5742,7 +5742,7 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5753,10 +5753,10 @@
         <v>6</v>
       </c>
       <c r="B402" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5770,7 +5770,7 @@
         <v>2026.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5778,13 +5778,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B404" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5795,10 +5795,10 @@
         <v>7</v>
       </c>
       <c r="B405" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5812,10 +5812,10 @@
         <v>2022.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D406" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="407">
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D407" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D408" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D409" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,7 +5868,7 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D410" t="n">
         <v>3.0</v>
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D411" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,7 +5896,7 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D412" t="n">
         <v>5.0</v>
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D413" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D414" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D415" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D416" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D417" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D418" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D419" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D420" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D421" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D422" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D423" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D424" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D425" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D426" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D427" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,7 +6120,7 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D428" t="n">
         <v>4.0</v>
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D429" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D430" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D431" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D432" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D433" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D434" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D435" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D436" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D437" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,7 +6260,7 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D438" t="n">
         <v>2.0</v>
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D439" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D440" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D441" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D442" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="443">
@@ -6327,13 +6327,13 @@
         <v>7</v>
       </c>
       <c r="B443" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D443" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2023.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D444" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D445" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D446" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D447" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D448" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D449" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D450" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D451" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D452" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D453" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D454" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D455" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D456" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D457" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D458" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D459" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D460" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D461" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D462" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,7 +6610,7 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D463" t="n">
         <v>8.0</v>
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D464" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D465" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D466" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D467" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D468" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D469" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D470" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,7 +6722,7 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D471" t="n">
         <v>6.0</v>
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D472" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,7 +6750,7 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D473" t="n">
         <v>2.0</v>
@@ -6764,7 +6764,7 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D474" t="n">
         <v>2.0</v>
@@ -6778,7 +6778,7 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D475" t="n">
         <v>2.0</v>
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,10 +6806,10 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D477" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D478" t="n">
         <v>1.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,10 +6890,10 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D483" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,10 +6904,10 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D484" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D485" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D486" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D487" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D488" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,7 +6974,7 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D489" t="n">
         <v>7.0</v>
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D490" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="491">
@@ -6999,13 +6999,13 @@
         <v>7</v>
       </c>
       <c r="B491" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D491" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2024.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D492" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D493" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D494" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D495" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D496" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D497" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D498" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D499" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D500" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D501" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D502" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D503" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,7 +7198,7 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D505" t="n">
         <v>1.0</v>
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D506" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D509" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,7 +7268,7 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,7 +7282,7 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,10 +7352,10 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D516" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,10 +7366,10 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D517" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D518" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D519" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="520">
@@ -7405,13 +7405,13 @@
         <v>7</v>
       </c>
       <c r="B520" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D520" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2025.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D521" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,7 +7436,7 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D522" t="n">
         <v>2.0</v>
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D523" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D524" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D525" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D526" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D527" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D528" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D529" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D530" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D531" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D532" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D533" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,7 +7604,7 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D534" t="n">
         <v>1.0</v>
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D535" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D536" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D537" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D538" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D539" t="n">
         <v>2.0</v>
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D540" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D544" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D545" t="n">
         <v>2.0</v>
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D546" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7797,10 +7797,10 @@
         <v>7</v>
       </c>
       <c r="B548" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,7 +7814,7 @@
         <v>2026.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,7 +7828,7 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7842,10 +7842,10 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D551" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D552" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D553" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D554" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D555" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D556" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,7 +7926,7 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D557" t="n">
         <v>1.0</v>
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D558" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D559" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D560" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,7 +7982,7 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D561" t="n">
         <v>1.0</v>
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D562" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D563" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,7 +8024,7 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D564" t="n">
         <v>1.0</v>
@@ -8032,13 +8032,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B565" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>45495.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D565" t="n">
         <v>1.0</v>
@@ -8046,16 +8046,16 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B566" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>45502.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D566" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="567">
@@ -8063,10 +8063,10 @@
         <v>8</v>
       </c>
       <c r="B567" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D567" t="n">
         <v>1.0</v>
@@ -8077,13 +8077,13 @@
         <v>8</v>
       </c>
       <c r="B568" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D568" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,7 +8094,7 @@
         <v>2025.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D569" t="n">
         <v>1.0</v>
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D570" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,7 +8122,7 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D571" t="n">
         <v>1.0</v>
@@ -8136,10 +8136,10 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D572" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D573" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D574" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D575" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D576" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D577" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,7 +8220,7 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D578" t="n">
         <v>1.0</v>
@@ -8234,7 +8234,7 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D579" t="n">
         <v>1.0</v>
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D580" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,7 +8262,7 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D581" t="n">
         <v>1.0</v>
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D582" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,7 +8290,7 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D583" t="n">
         <v>1.0</v>
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D584" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D585" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,7 +8332,7 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D586" t="n">
         <v>2.0</v>
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D587" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D588" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D589" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D590" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D591" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D592" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D593" t="n">
         <v>1.0</v>
@@ -8444,7 +8444,7 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D594" t="n">
         <v>1.0</v>
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D595" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D596" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D597" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D598" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D599" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D600" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D601" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D602" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D603" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D604" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D605" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D606" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="607">
@@ -8623,13 +8623,13 @@
         <v>8</v>
       </c>
       <c r="B607" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D607" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="608">
@@ -8637,13 +8637,13 @@
         <v>8</v>
       </c>
       <c r="B608" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D608" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2026.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D609" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2026.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D610" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2026.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D611" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D612" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D613" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D614" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D615" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D616" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D617" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D618" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D619" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46121.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D620" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46128.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D621" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46135.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D622" t="n">
-        <v>35.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46142.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D623" t="n">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46149.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D624" t="n">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46156.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D625" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46163.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D626" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46170.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D627" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D628" t="n">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46184.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D629" t="n">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46191.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D630" t="n">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46198.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D631" t="n">
-        <v>9.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46205.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D632" t="n">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46212.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D633" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46219.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D634" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46226.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D635" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46233.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D636" t="n">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D637" t="n">
-        <v>25.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46247.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D638" t="n">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D639" t="n">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46261.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D640" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D641" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,9 +9116,37 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
+        <v>46261.0</v>
+      </c>
+      <c r="D642" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="s">
+        <v>8</v>
+      </c>
+      <c r="B643" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C643" t="n" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="D643" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="s">
+        <v>8</v>
+      </c>
+      <c r="B644" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C644" t="n" s="2">
         <v>46275.0</v>
       </c>
-      <c r="D642" t="n">
+      <c r="D644" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -9153,7 +9181,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
     </row>
     <row r="4">
@@ -9169,7 +9197,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2268.0</v>
+        <v>2269.0</v>
       </c>
     </row>
   </sheetData>
@@ -9267,7 +9295,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>371.0</v>
+        <v>372.0</v>
       </c>
     </row>
     <row r="9">
@@ -9344,7 +9372,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>415.0</v>
+        <v>416.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -4737,7 +4737,7 @@
         <v>46289.0</v>
       </c>
       <c r="D329" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="330">
@@ -9189,7 +9189,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1558.0</v>
+        <v>1559.0</v>
       </c>
     </row>
     <row r="5">
@@ -9229,7 +9229,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
     </row>
     <row r="3">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -9150,6 +9150,20 @@
         <v>2.0</v>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" t="s">
+        <v>8</v>
+      </c>
+      <c r="B645" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C645" t="n" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="D645" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -9173,7 +9187,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="3">
@@ -9197,7 +9211,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2269.0</v>
+        <v>2270.0</v>
       </c>
     </row>
   </sheetData>
@@ -9328,7 +9342,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="12">
@@ -9372,7 +9386,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>416.0</v>
+        <v>417.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1844,16 +1844,16 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B123" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C123" t="n" s="2">
-        <v>44561.0</v>
+        <v>46296.0</v>
       </c>
       <c r="D123" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
@@ -1861,13 +1861,13 @@
         <v>5</v>
       </c>
       <c r="B124" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D124" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
@@ -1878,10 +1878,10 @@
         <v>2022.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D125" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D126" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D127" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D128" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D129" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,7 +1948,7 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D130" t="n">
         <v>1.0</v>
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D131" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,10 +1976,10 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D132" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="133">
@@ -1990,10 +1990,10 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D133" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="134">
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D134" t="n">
         <v>2.0</v>
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D135" t="n">
         <v>2.0</v>
@@ -2032,10 +2032,10 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D136" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="137">
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D137" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="138">
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D138" t="n">
         <v>3.0</v>
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D139" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D140" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D141" t="n">
         <v>3.0</v>
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D142" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D143" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D144" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,7 +2158,7 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D145" t="n">
         <v>1.0</v>
@@ -2172,7 +2172,7 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D146" t="n">
         <v>1.0</v>
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,7 +2312,7 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D156" t="n">
         <v>1.0</v>
@@ -2326,7 +2326,7 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D157" t="n">
         <v>1.0</v>
@@ -2340,10 +2340,10 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D158" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="159">
@@ -2354,10 +2354,10 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D159" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,7 +2368,7 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D160" t="n">
         <v>1.0</v>
@@ -2382,7 +2382,7 @@
         <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D161" t="n">
         <v>1.0</v>
@@ -2396,10 +2396,10 @@
         <v>2022.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D162" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="163">
@@ -2407,13 +2407,13 @@
         <v>5</v>
       </c>
       <c r="B163" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D163" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,10 +2424,10 @@
         <v>2023.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D164" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D165" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D166" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D167" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,7 +2480,7 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D168" t="n">
         <v>4.0</v>
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D169" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D170" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D171" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D172" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D173" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D174" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D175" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D176" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D177" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D178" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D179" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D180" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D181" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D182" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D183" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D184" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D185" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D186" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D187" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D188" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D189" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D190" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D191" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D192" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D193" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,7 +2844,7 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D194" t="n">
         <v>2.0</v>
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D195" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,7 +2872,7 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D196" t="n">
         <v>5.0</v>
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D197" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D198" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D199" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,7 +2928,7 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D200" t="n">
         <v>1.0</v>
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D201" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D202" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D203" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,7 +2984,7 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D204" t="n">
         <v>8.0</v>
@@ -2998,10 +2998,10 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D205" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D206" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,7 +3026,7 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D207" t="n">
         <v>9.0</v>
@@ -3040,10 +3040,10 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D208" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D209" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D210" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D211" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D212" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D213" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2023.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D214" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="215">
@@ -3135,13 +3135,13 @@
         <v>5</v>
       </c>
       <c r="B215" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D215" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2024.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D216" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D217" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D218" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D219" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D220" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D221" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D222" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D223" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D224" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D225" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D226" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D227" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D228" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D229" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D230" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D231" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D232" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D233" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D234" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D235" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D236" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D237" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D238" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D239" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D240" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,7 +3502,7 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D241" t="n">
         <v>12.0</v>
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D242" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D243" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D244" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D245" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D246" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,7 +3586,7 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D247" t="n">
         <v>4.0</v>
@@ -3600,7 +3600,7 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D248" t="n">
         <v>4.0</v>
@@ -3614,7 +3614,7 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D249" t="n">
         <v>4.0</v>
@@ -3628,10 +3628,10 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D250" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,10 +3642,10 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D251" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D252" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D253" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D254" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D255" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D256" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,7 +3726,7 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D257" t="n">
         <v>3.0</v>
@@ -3740,10 +3740,10 @@
         <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D258" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,7 +3754,7 @@
         <v>2024.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D259" t="n">
         <v>1.0</v>
@@ -3765,13 +3765,13 @@
         <v>5</v>
       </c>
       <c r="B260" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D260" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,10 +3782,10 @@
         <v>2025.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D261" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,7 +3796,7 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D262" t="n">
         <v>1.0</v>
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D263" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D265" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D266" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D267" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D268" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D269" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D270" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D271" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D272" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D273" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D274" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D275" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D276" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D277" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D278" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D279" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,7 +4048,7 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D280" t="n">
         <v>4.0</v>
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D281" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D282" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D283" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D284" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,7 +4118,7 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D285" t="n">
         <v>1.0</v>
@@ -4132,10 +4132,10 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D286" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D287" t="n">
         <v>3.0</v>
@@ -4160,10 +4160,10 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D288" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D289" t="n">
         <v>1.0</v>
@@ -4188,10 +4188,10 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D290" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,10 +4202,10 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D291" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D292" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D293" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D294" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2025.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D295" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="296">
@@ -4269,13 +4269,13 @@
         <v>5</v>
       </c>
       <c r="B296" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D296" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2026.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D297" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D298" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D299" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D300" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D301" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D302" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,7 +4370,7 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D303" t="n">
         <v>5.0</v>
@@ -4384,10 +4384,10 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D304" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,7 +4398,7 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D305" t="n">
         <v>2.0</v>
@@ -4412,10 +4412,10 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D306" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,10 +4426,10 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D307" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D308" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D309" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D310" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,7 +4482,7 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D311" t="n">
         <v>4.0</v>
@@ -4496,10 +4496,10 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D312" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D313" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D314" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D315" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D316" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D317" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D318" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D319" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D320" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D321" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D322" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D323" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D324" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D325" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D326" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2026.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D327" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2026.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>46282.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D328" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,24 +4734,24 @@
         <v>2026.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D329" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B330" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>45095.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D330" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,7 +4762,7 @@
         <v>2023.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D331" t="n">
         <v>1.0</v>
@@ -4776,7 +4776,7 @@
         <v>2023.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D332" t="n">
         <v>1.0</v>
@@ -4790,10 +4790,10 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D333" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,7 +4804,7 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D334" t="n">
         <v>3.0</v>
@@ -4818,10 +4818,10 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D335" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,7 +4832,7 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D337" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D338" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D340" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D342" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4927,13 +4927,13 @@
         <v>6</v>
       </c>
       <c r="B343" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D343" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2024.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D344" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D345" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D346" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D347" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D348" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,7 +5014,7 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D349" t="n">
         <v>12.0</v>
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D350" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D351" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D352" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D353" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D354" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D355" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D356" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D357" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D358" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D359" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D360" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D361" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,7 +5196,7 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D362" t="n">
         <v>6.0</v>
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D363" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D364" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,7 +5238,7 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D365" t="n">
         <v>4.0</v>
@@ -5252,7 +5252,7 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D366" t="n">
         <v>4.0</v>
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D368" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D369" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D370" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D371" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D372" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,7 +5350,7 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D373" t="n">
         <v>1.0</v>
@@ -5364,7 +5364,7 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5378,7 +5378,7 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D376" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D377" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D378" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D379" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,7 +5448,7 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D380" t="n">
         <v>1.0</v>
@@ -5462,7 +5462,7 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D381" t="n">
         <v>1.0</v>
@@ -5473,13 +5473,13 @@
         <v>6</v>
       </c>
       <c r="B382" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D382" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2025.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D383" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2025.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D384" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D385" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D386" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D387" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D388" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D389" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D390" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D391" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D392" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D393" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D394" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D395" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D396" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,7 +5686,7 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D397" t="n">
         <v>4.0</v>
@@ -5700,10 +5700,10 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D398" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,7 +5714,7 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D399" t="n">
         <v>1.0</v>
@@ -5728,7 +5728,7 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D400" t="n">
         <v>1.0</v>
@@ -5742,7 +5742,7 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5756,7 +5756,7 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5767,10 +5767,10 @@
         <v>6</v>
       </c>
       <c r="B403" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5784,7 +5784,7 @@
         <v>2026.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5792,13 +5792,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B405" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5809,10 +5809,10 @@
         <v>7</v>
       </c>
       <c r="B406" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5826,10 +5826,10 @@
         <v>2022.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D407" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="408">
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D408" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D409" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D410" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,7 +5882,7 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D411" t="n">
         <v>3.0</v>
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D412" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,7 +5910,7 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D413" t="n">
         <v>5.0</v>
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D414" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D415" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D416" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D417" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D418" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D419" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D420" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D421" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D422" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D423" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D424" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D425" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D426" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D427" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D428" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,7 +6134,7 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D429" t="n">
         <v>4.0</v>
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D430" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D431" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D432" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D433" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D434" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D435" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D436" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D437" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D438" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,7 +6274,7 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D439" t="n">
         <v>2.0</v>
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D440" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D441" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D442" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D443" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="444">
@@ -6341,13 +6341,13 @@
         <v>7</v>
       </c>
       <c r="B444" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D444" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2023.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D445" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D446" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D447" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D448" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D449" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D450" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D451" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D452" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D453" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D454" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D455" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D456" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D457" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D458" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D459" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D460" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D461" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D462" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D463" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,7 +6624,7 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D464" t="n">
         <v>8.0</v>
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D465" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D466" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D467" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D468" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D469" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D470" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D471" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,7 +6736,7 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D472" t="n">
         <v>6.0</v>
@@ -6750,10 +6750,10 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D473" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,7 +6764,7 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D474" t="n">
         <v>2.0</v>
@@ -6778,7 +6778,7 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D475" t="n">
         <v>2.0</v>
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D477" t="n">
         <v>2.0</v>
@@ -6820,10 +6820,10 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D478" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D479" t="n">
         <v>1.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,10 +6904,10 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D484" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,10 +6918,10 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D485" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D486" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D487" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D488" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D489" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,7 +6988,7 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D490" t="n">
         <v>7.0</v>
@@ -7002,10 +7002,10 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D491" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="492">
@@ -7013,13 +7013,13 @@
         <v>7</v>
       </c>
       <c r="B492" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D492" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2024.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D493" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D494" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D495" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D496" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D497" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D498" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D499" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D500" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D501" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D502" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D503" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D504" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,7 +7212,7 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D506" t="n">
         <v>1.0</v>
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D507" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D509" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,7 +7282,7 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,10 +7366,10 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D517" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="518">
@@ -7380,10 +7380,10 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D518" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D519" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D520" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="521">
@@ -7419,13 +7419,13 @@
         <v>7</v>
       </c>
       <c r="B521" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D521" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2025.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D522" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,7 +7450,7 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D523" t="n">
         <v>2.0</v>
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D524" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D525" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D526" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D527" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D528" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D529" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D530" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D531" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D532" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D533" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D534" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,7 +7618,7 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D535" t="n">
         <v>1.0</v>
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D536" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D537" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D538" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D539" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D540" t="n">
         <v>2.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D541" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D542" t="n">
         <v>1.0</v>
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D545" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D546" t="n">
         <v>2.0</v>
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D547" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7811,10 +7811,10 @@
         <v>7</v>
       </c>
       <c r="B549" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,7 +7828,7 @@
         <v>2026.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7842,7 +7842,7 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D551" t="n">
         <v>1.0</v>
@@ -7856,10 +7856,10 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D552" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D553" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D554" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D555" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D556" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D557" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,7 +7940,7 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D558" t="n">
         <v>1.0</v>
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D559" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D560" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D561" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,7 +7996,7 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D562" t="n">
         <v>1.0</v>
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D563" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D564" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,7 +8038,7 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D565" t="n">
         <v>1.0</v>
@@ -8052,7 +8052,7 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D566" t="n">
         <v>1.0</v>
@@ -8060,13 +8060,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B567" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>45495.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D567" t="n">
         <v>1.0</v>
@@ -8080,10 +8080,10 @@
         <v>2024.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D568" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="569">
@@ -8091,13 +8091,13 @@
         <v>8</v>
       </c>
       <c r="B569" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D569" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2025.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D570" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,10 +8122,10 @@
         <v>2025.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D571" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,10 +8136,10 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D572" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D573" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D574" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D575" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D576" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D577" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D578" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,7 +8234,7 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D579" t="n">
         <v>1.0</v>
@@ -8248,7 +8248,7 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D580" t="n">
         <v>1.0</v>
@@ -8262,7 +8262,7 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D581" t="n">
         <v>1.0</v>
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D582" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D583" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,7 +8304,7 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D584" t="n">
         <v>1.0</v>
@@ -8318,7 +8318,7 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D585" t="n">
         <v>1.0</v>
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D586" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,7 +8346,7 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D587" t="n">
         <v>2.0</v>
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D588" t="n">
         <v>2.0</v>
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D589" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D590" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D591" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D592" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D593" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,7 +8444,7 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D594" t="n">
         <v>1.0</v>
@@ -8458,7 +8458,7 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D595" t="n">
         <v>1.0</v>
@@ -8472,7 +8472,7 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D596" t="n">
         <v>1.0</v>
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D597" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D598" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,7 +8514,7 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D599" t="n">
         <v>2.0</v>
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D600" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D601" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D602" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D603" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D604" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D605" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D606" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D607" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D608" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="609">
@@ -8651,13 +8651,13 @@
         <v>8</v>
       </c>
       <c r="B609" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D609" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2026.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D610" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2026.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D611" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D612" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D613" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D614" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D615" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D616" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D617" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D618" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D619" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D620" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D621" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D622" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D623" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D624" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D625" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D626" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D627" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D628" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D629" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D630" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D631" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D632" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D633" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D634" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D635" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D636" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D637" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D638" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D639" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D640" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D641" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D642" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,7 +9130,7 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D643" t="n">
         <v>1.0</v>
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D644" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,9 +9158,23 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
+        <v>46275.0</v>
+      </c>
+      <c r="D645" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="s">
+        <v>8</v>
+      </c>
+      <c r="B646" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C646" t="n" s="2">
         <v>46296.0</v>
       </c>
-      <c r="D645" t="n">
+      <c r="D646" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -9195,7 +9209,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>243.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="4">
@@ -9375,7 +9389,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>508.0</v>
+        <v>510.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1858,13 +1858,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B124" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C124" t="n" s="2">
-        <v>44561.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D124" t="n">
         <v>1.0</v>
@@ -1875,13 +1875,13 @@
         <v>5</v>
       </c>
       <c r="B125" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D125" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="126">
@@ -1892,10 +1892,10 @@
         <v>2022.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D126" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D127" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D128" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D129" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D130" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,7 +1962,7 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D131" t="n">
         <v>1.0</v>
@@ -1976,10 +1976,10 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D132" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="133">
@@ -1990,10 +1990,10 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D133" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="134">
@@ -2004,10 +2004,10 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D134" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="135">
@@ -2018,7 +2018,7 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D135" t="n">
         <v>2.0</v>
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D136" t="n">
         <v>2.0</v>
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D137" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="138">
@@ -2060,10 +2060,10 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D138" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="139">
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D139" t="n">
         <v>3.0</v>
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D140" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D141" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D142" t="n">
         <v>3.0</v>
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D143" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D144" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D145" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,7 +2172,7 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D146" t="n">
         <v>1.0</v>
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,7 +2312,7 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D156" t="n">
         <v>1.0</v>
@@ -2326,7 +2326,7 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D157" t="n">
         <v>1.0</v>
@@ -2340,7 +2340,7 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D158" t="n">
         <v>1.0</v>
@@ -2354,10 +2354,10 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D159" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="160">
@@ -2368,10 +2368,10 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D160" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,7 +2382,7 @@
         <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D161" t="n">
         <v>1.0</v>
@@ -2396,7 +2396,7 @@
         <v>2022.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D162" t="n">
         <v>1.0</v>
@@ -2410,10 +2410,10 @@
         <v>2022.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D163" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="164">
@@ -2421,13 +2421,13 @@
         <v>5</v>
       </c>
       <c r="B164" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D164" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="165">
@@ -2438,10 +2438,10 @@
         <v>2023.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D165" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D166" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D167" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D168" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,7 +2494,7 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D169" t="n">
         <v>4.0</v>
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D170" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D171" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D172" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D173" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D174" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D175" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D176" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D177" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D178" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D179" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D180" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D181" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D182" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D183" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D184" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D185" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D186" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D187" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D188" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D189" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D190" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D191" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D192" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D193" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D194" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,7 +2858,7 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D195" t="n">
         <v>2.0</v>
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D196" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,7 +2886,7 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D197" t="n">
         <v>5.0</v>
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D198" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D199" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D200" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,7 +2942,7 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D201" t="n">
         <v>1.0</v>
@@ -2956,10 +2956,10 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D202" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D203" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D204" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,7 +2998,7 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D205" t="n">
         <v>8.0</v>
@@ -3012,10 +3012,10 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D206" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D207" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,7 +3040,7 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D208" t="n">
         <v>9.0</v>
@@ -3054,10 +3054,10 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D209" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D210" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D211" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D212" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D213" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2023.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D214" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2023.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D215" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="216">
@@ -3149,13 +3149,13 @@
         <v>5</v>
       </c>
       <c r="B216" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D216" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2024.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D217" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D218" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D219" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D220" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D221" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D222" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D223" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D224" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D225" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D226" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D227" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D228" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D229" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D230" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D231" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D232" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D233" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D234" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D235" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D236" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D237" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D238" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D239" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D240" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D241" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,7 +3516,7 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D242" t="n">
         <v>12.0</v>
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D243" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D244" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D245" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D246" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D247" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,7 +3600,7 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D248" t="n">
         <v>4.0</v>
@@ -3614,7 +3614,7 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D249" t="n">
         <v>4.0</v>
@@ -3628,7 +3628,7 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D250" t="n">
         <v>4.0</v>
@@ -3642,10 +3642,10 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D251" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="252">
@@ -3656,10 +3656,10 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D252" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D253" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D254" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D255" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D256" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D257" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,7 +3740,7 @@
         <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D258" t="n">
         <v>3.0</v>
@@ -3754,10 +3754,10 @@
         <v>2024.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D259" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,7 +3768,7 @@
         <v>2024.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D260" t="n">
         <v>1.0</v>
@@ -3779,13 +3779,13 @@
         <v>5</v>
       </c>
       <c r="B261" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D261" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,10 +3796,10 @@
         <v>2025.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D262" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,7 +3810,7 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D263" t="n">
         <v>1.0</v>
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D264" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D265" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D266" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D267" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D268" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D269" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D270" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D271" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D272" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D273" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D274" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D275" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D276" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D277" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D278" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D279" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D280" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,7 +4062,7 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D281" t="n">
         <v>4.0</v>
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D282" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D283" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D284" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D285" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,7 +4132,7 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D286" t="n">
         <v>1.0</v>
@@ -4146,10 +4146,10 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D287" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D288" t="n">
         <v>3.0</v>
@@ -4174,10 +4174,10 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D289" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4188,7 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D290" t="n">
         <v>1.0</v>
@@ -4202,10 +4202,10 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D291" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,10 +4216,10 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D292" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D293" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D294" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2025.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D295" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2025.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D296" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="297">
@@ -4283,13 +4283,13 @@
         <v>5</v>
       </c>
       <c r="B297" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D297" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2026.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D298" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D299" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D300" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D301" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D302" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D303" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,7 +4384,7 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D304" t="n">
         <v>5.0</v>
@@ -4398,10 +4398,10 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D305" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,7 +4412,7 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D306" t="n">
         <v>2.0</v>
@@ -4426,10 +4426,10 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D307" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,10 +4440,10 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D308" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D309" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D310" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D311" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,7 +4496,7 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D312" t="n">
         <v>4.0</v>
@@ -4510,10 +4510,10 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D313" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D314" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D315" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D316" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D317" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D318" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D319" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D320" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D321" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D322" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D323" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D324" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D325" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D326" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2026.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D327" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2026.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D328" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2026.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>46282.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D329" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,24 +4748,24 @@
         <v>2026.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D330" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B331" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>45095.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D331" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,7 +4776,7 @@
         <v>2023.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D332" t="n">
         <v>1.0</v>
@@ -4790,7 +4790,7 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,10 +4804,10 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D334" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,7 +4818,7 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D335" t="n">
         <v>3.0</v>
@@ -4832,10 +4832,10 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D336" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,7 +4846,7 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D337" t="n">
         <v>1.0</v>
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D338" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D339" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D340" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D341" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D342" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D343" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4941,13 +4941,13 @@
         <v>6</v>
       </c>
       <c r="B344" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D344" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2024.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D345" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D346" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D347" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D348" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D349" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,7 +5028,7 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D350" t="n">
         <v>12.0</v>
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D351" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D352" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D353" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D354" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D355" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D356" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D357" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D358" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D359" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D360" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D361" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D362" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,7 +5210,7 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D363" t="n">
         <v>6.0</v>
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D364" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D365" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,7 +5252,7 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D366" t="n">
         <v>4.0</v>
@@ -5266,7 +5266,7 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D367" t="n">
         <v>4.0</v>
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D368" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D369" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D370" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D371" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D372" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D373" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,7 +5364,7 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D374" t="n">
         <v>1.0</v>
@@ -5378,7 +5378,7 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5392,7 +5392,7 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5406,10 +5406,10 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D377" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D378" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D379" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D380" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,7 +5462,7 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D381" t="n">
         <v>1.0</v>
@@ -5476,7 +5476,7 @@
         <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D382" t="n">
         <v>1.0</v>
@@ -5487,13 +5487,13 @@
         <v>6</v>
       </c>
       <c r="B383" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D383" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2025.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D384" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D385" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D386" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D387" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D388" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D389" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D390" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D391" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D392" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D393" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D394" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D395" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D396" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D397" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,7 +5700,7 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D398" t="n">
         <v>4.0</v>
@@ -5714,10 +5714,10 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D399" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,7 +5728,7 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D400" t="n">
         <v>1.0</v>
@@ -5742,7 +5742,7 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5756,7 +5756,7 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5770,7 +5770,7 @@
         <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5781,10 +5781,10 @@
         <v>6</v>
       </c>
       <c r="B404" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5798,7 +5798,7 @@
         <v>2026.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5806,13 +5806,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B406" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5823,10 +5823,10 @@
         <v>7</v>
       </c>
       <c r="B407" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5840,10 +5840,10 @@
         <v>2022.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D408" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="409">
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D409" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D410" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D411" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,7 +5896,7 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D412" t="n">
         <v>3.0</v>
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D413" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,7 +5924,7 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D414" t="n">
         <v>5.0</v>
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D415" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D416" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D417" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D418" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D419" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D420" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D421" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D422" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D423" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D424" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D425" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D426" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D427" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D428" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D429" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,7 +6148,7 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D430" t="n">
         <v>4.0</v>
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D431" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D432" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D433" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D434" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D435" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D436" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D437" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D438" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D439" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,7 +6288,7 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D440" t="n">
         <v>2.0</v>
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D441" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D442" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D443" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D444" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="445">
@@ -6355,13 +6355,13 @@
         <v>7</v>
       </c>
       <c r="B445" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D445" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2023.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D446" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D447" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D448" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D449" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D450" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D451" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D452" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D453" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D454" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D455" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D456" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D457" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D458" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D459" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D460" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D461" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D462" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D463" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D464" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,7 +6638,7 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D465" t="n">
         <v>8.0</v>
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D466" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D467" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D468" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D469" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D470" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D471" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D472" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,7 +6750,7 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D473" t="n">
         <v>6.0</v>
@@ -6764,10 +6764,10 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D474" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D475" t="n">
         <v>2.0</v>
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D477" t="n">
         <v>2.0</v>
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D478" t="n">
         <v>2.0</v>
@@ -6834,10 +6834,10 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D479" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D480" t="n">
         <v>1.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,10 +6918,10 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D485" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="486">
@@ -6932,10 +6932,10 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D486" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D487" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D488" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D489" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D490" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,7 +7002,7 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D491" t="n">
         <v>7.0</v>
@@ -7016,10 +7016,10 @@
         <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D492" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="493">
@@ -7027,13 +7027,13 @@
         <v>7</v>
       </c>
       <c r="B493" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D493" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2024.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D494" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D495" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D496" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D497" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D498" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D499" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D500" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D501" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D502" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D503" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D504" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D505" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D506" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,7 +7226,7 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D507" t="n">
         <v>1.0</v>
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D509" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,7 +7310,7 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,10 +7380,10 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D518" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="519">
@@ -7394,10 +7394,10 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D519" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D520" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D521" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="522">
@@ -7433,13 +7433,13 @@
         <v>7</v>
       </c>
       <c r="B522" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D522" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2025.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D523" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,7 +7464,7 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D524" t="n">
         <v>2.0</v>
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D525" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D526" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D527" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D528" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D529" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D530" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D531" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D532" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D533" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D534" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D535" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,7 +7632,7 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D536" t="n">
         <v>1.0</v>
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D537" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D538" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D539" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D540" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D541" t="n">
         <v>2.0</v>
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D542" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D543" t="n">
         <v>1.0</v>
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D546" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D547" t="n">
         <v>2.0</v>
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D548" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7825,10 +7825,10 @@
         <v>7</v>
       </c>
       <c r="B550" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7842,7 +7842,7 @@
         <v>2026.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D551" t="n">
         <v>1.0</v>
@@ -7856,7 +7856,7 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D552" t="n">
         <v>1.0</v>
@@ -7870,10 +7870,10 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D553" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D554" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D555" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D556" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D557" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D558" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,7 +7954,7 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D559" t="n">
         <v>1.0</v>
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D560" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D561" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D562" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,7 +8010,7 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D563" t="n">
         <v>1.0</v>
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D564" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D565" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,7 +8052,7 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D566" t="n">
         <v>1.0</v>
@@ -8066,7 +8066,7 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D567" t="n">
         <v>1.0</v>
@@ -8074,13 +8074,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B568" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>45495.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D568" t="n">
         <v>1.0</v>
@@ -8088,16 +8088,16 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B569" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>45502.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D569" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="570">
@@ -8105,10 +8105,10 @@
         <v>8</v>
       </c>
       <c r="B570" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45665.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D570" t="n">
         <v>1.0</v>
@@ -8119,13 +8119,13 @@
         <v>8</v>
       </c>
       <c r="B571" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45672.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D571" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="572">
@@ -8136,7 +8136,7 @@
         <v>2025.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45679.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D572" t="n">
         <v>1.0</v>
@@ -8150,10 +8150,10 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D573" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,7 +8164,7 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45693.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D574" t="n">
         <v>1.0</v>
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45700.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D575" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45707.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D576" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45714.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D577" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45721.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D578" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45728.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D579" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45742.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D580" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,7 +8262,7 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45749.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D581" t="n">
         <v>1.0</v>
@@ -8276,7 +8276,7 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45763.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D582" t="n">
         <v>1.0</v>
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45777.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D583" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,7 +8304,7 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45784.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D584" t="n">
         <v>1.0</v>
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45798.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D585" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,7 +8332,7 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45805.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D586" t="n">
         <v>1.0</v>
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45812.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D587" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45819.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D588" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45833.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D589" t="n">
         <v>2.0</v>
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45847.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D590" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45854.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D591" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45861.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D592" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45868.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D593" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45875.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D594" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45896.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D595" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,7 +8472,7 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45903.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D596" t="n">
         <v>1.0</v>
@@ -8486,7 +8486,7 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45931.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D597" t="n">
         <v>1.0</v>
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45938.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D598" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45945.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D599" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45966.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D600" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45973.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D601" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45980.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D602" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D603" t="n">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45994.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D604" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>46001.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D605" t="n">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>46008.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D606" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46015.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D607" t="n">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D608" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46029.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D609" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="610">
@@ -8665,13 +8665,13 @@
         <v>8</v>
       </c>
       <c r="B610" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D610" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="611">
@@ -8679,13 +8679,13 @@
         <v>8</v>
       </c>
       <c r="B611" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46037.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D611" t="n">
-        <v>22.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2026.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46044.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D612" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46051.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D613" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46058.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D614" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46065.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D615" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46072.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D616" t="n">
-        <v>13.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46079.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D617" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46086.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D618" t="n">
-        <v>26.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46093.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D619" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46100.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D620" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46107.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D621" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46114.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D622" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46121.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D623" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46128.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D624" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46135.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D625" t="n">
-        <v>35.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46142.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D626" t="n">
-        <v>22.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46149.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D627" t="n">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46156.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D628" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46163.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D629" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46170.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D630" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D631" t="n">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46184.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D632" t="n">
-        <v>32.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46191.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D633" t="n">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46198.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D634" t="n">
-        <v>9.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46205.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D635" t="n">
-        <v>15.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46212.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D636" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46219.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D637" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46226.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D638" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46233.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D639" t="n">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D640" t="n">
-        <v>25.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46247.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D641" t="n">
-        <v>12.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D642" t="n">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46261.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D643" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D644" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46275.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D645" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,52 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
+        <v>46268.0</v>
+      </c>
+      <c r="D646" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="s">
+        <v>8</v>
+      </c>
+      <c r="B647" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C647" t="n" s="2">
+        <v>46275.0</v>
+      </c>
+      <c r="D647" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="s">
+        <v>8</v>
+      </c>
+      <c r="B648" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C648" t="n" s="2">
         <v>46296.0</v>
       </c>
-      <c r="D646" t="n">
+      <c r="D648" t="n">
         <v>2.0</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="s">
+        <v>8</v>
+      </c>
+      <c r="B649" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C649" t="n" s="2">
+        <v>46303.0</v>
+      </c>
+      <c r="D649" t="n">
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>
@@ -9201,7 +9243,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="3">
@@ -9217,7 +9259,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1559.0</v>
+        <v>1563.0</v>
       </c>
     </row>
     <row r="5">
@@ -9225,7 +9267,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2270.0</v>
+        <v>2272.0</v>
       </c>
     </row>
   </sheetData>
@@ -9290,7 +9332,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>480.0</v>
+        <v>481.0</v>
       </c>
     </row>
     <row r="6">
@@ -9356,7 +9398,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="12">
@@ -9389,7 +9431,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>510.0</v>
+        <v>514.0</v>
       </c>
     </row>
     <row r="15">
@@ -9422,7 +9464,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -9243,7 +9243,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>59.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="3">
@@ -9267,7 +9267,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2272.0</v>
+        <v>2273.0</v>
       </c>
     </row>
   </sheetData>
@@ -9332,7 +9332,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
     </row>
     <row r="6">
@@ -9398,7 +9398,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>45.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B125" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C125" t="n" s="2">
-        <v>44561.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D125" t="n">
         <v>1.0</v>
@@ -1889,13 +1889,13 @@
         <v>5</v>
       </c>
       <c r="B126" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D126" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -1906,10 +1906,10 @@
         <v>2022.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D127" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D128" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D129" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D130" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D131" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,7 +1976,7 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D132" t="n">
         <v>1.0</v>
@@ -1990,10 +1990,10 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D133" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
@@ -2004,10 +2004,10 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D134" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="135">
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D135" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,7 +2032,7 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D136" t="n">
         <v>2.0</v>
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D137" t="n">
         <v>2.0</v>
@@ -2060,10 +2060,10 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D138" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="139">
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D139" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,7 +2088,7 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D140" t="n">
         <v>3.0</v>
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D141" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D142" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,7 +2130,7 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D143" t="n">
         <v>3.0</v>
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D144" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,10 +2158,10 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D145" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D146" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,7 +2186,7 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D147" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,7 +2312,7 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D156" t="n">
         <v>1.0</v>
@@ -2326,7 +2326,7 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D157" t="n">
         <v>1.0</v>
@@ -2340,7 +2340,7 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D158" t="n">
         <v>1.0</v>
@@ -2354,7 +2354,7 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D159" t="n">
         <v>1.0</v>
@@ -2368,10 +2368,10 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D160" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="161">
@@ -2382,10 +2382,10 @@
         <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D161" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,7 +2396,7 @@
         <v>2022.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D162" t="n">
         <v>1.0</v>
@@ -2410,7 +2410,7 @@
         <v>2022.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D163" t="n">
         <v>1.0</v>
@@ -2424,10 +2424,10 @@
         <v>2022.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D164" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="165">
@@ -2435,13 +2435,13 @@
         <v>5</v>
       </c>
       <c r="B165" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D165" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="166">
@@ -2452,10 +2452,10 @@
         <v>2023.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D166" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D167" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D168" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D169" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,7 +2508,7 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D170" t="n">
         <v>4.0</v>
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D171" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D172" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D173" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D174" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D175" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D176" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D177" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D178" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D179" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D180" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D181" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D182" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D183" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D184" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D185" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D186" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D187" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D188" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D189" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D190" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D191" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D192" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D193" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D194" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D195" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,7 +2872,7 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D196" t="n">
         <v>2.0</v>
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D197" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,7 +2900,7 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D198" t="n">
         <v>5.0</v>
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D199" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D200" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D201" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,7 +2956,7 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D202" t="n">
         <v>1.0</v>
@@ -2970,10 +2970,10 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D203" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,10 +2984,10 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D204" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D205" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,7 +3012,7 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D206" t="n">
         <v>8.0</v>
@@ -3026,10 +3026,10 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D207" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,10 +3040,10 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D208" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,7 +3054,7 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D209" t="n">
         <v>9.0</v>
@@ -3068,10 +3068,10 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D210" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,10 +3082,10 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D211" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D212" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D213" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2023.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D214" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2023.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D215" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2023.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D216" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="217">
@@ -3163,13 +3163,13 @@
         <v>5</v>
       </c>
       <c r="B217" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D217" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2024.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D218" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D219" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D220" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D221" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D222" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D223" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D224" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D225" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D226" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D227" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D228" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D229" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D230" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D231" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D232" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D233" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D234" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D235" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D236" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D237" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D238" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D239" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D240" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D241" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D242" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,7 +3530,7 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D243" t="n">
         <v>12.0</v>
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D244" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,10 +3558,10 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D245" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D246" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D247" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D248" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,7 +3614,7 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D249" t="n">
         <v>4.0</v>
@@ -3628,7 +3628,7 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D250" t="n">
         <v>4.0</v>
@@ -3642,7 +3642,7 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D251" t="n">
         <v>4.0</v>
@@ -3656,10 +3656,10 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D252" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="253">
@@ -3670,10 +3670,10 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D253" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D254" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D255" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D256" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D257" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D258" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,7 +3754,7 @@
         <v>2024.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D259" t="n">
         <v>3.0</v>
@@ -3768,10 +3768,10 @@
         <v>2024.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D260" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,7 +3782,7 @@
         <v>2024.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D261" t="n">
         <v>1.0</v>
@@ -3793,13 +3793,13 @@
         <v>5</v>
       </c>
       <c r="B262" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D262" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,10 +3810,10 @@
         <v>2025.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D263" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,7 +3824,7 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D264" t="n">
         <v>1.0</v>
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D265" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D266" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D267" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D268" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D269" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D270" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D271" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D272" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D273" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D274" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D275" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D276" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D277" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D278" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D279" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D280" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D281" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,7 +4076,7 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D282" t="n">
         <v>4.0</v>
@@ -4090,10 +4090,10 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D283" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,10 +4104,10 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D284" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D285" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D286" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,7 +4146,7 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D287" t="n">
         <v>1.0</v>
@@ -4160,10 +4160,10 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D288" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D289" t="n">
         <v>3.0</v>
@@ -4188,10 +4188,10 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D290" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,7 +4202,7 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D291" t="n">
         <v>1.0</v>
@@ -4216,10 +4216,10 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D292" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,10 +4230,10 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D293" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D294" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2025.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D295" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2025.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D296" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2025.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D297" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="298">
@@ -4297,13 +4297,13 @@
         <v>5</v>
       </c>
       <c r="B298" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D298" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2026.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D299" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D300" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D301" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D302" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D303" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D304" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,7 +4398,7 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D305" t="n">
         <v>5.0</v>
@@ -4412,10 +4412,10 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D306" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,7 +4426,7 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D307" t="n">
         <v>2.0</v>
@@ -4440,10 +4440,10 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D308" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,10 +4454,10 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D309" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D310" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D311" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D312" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,7 +4510,7 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D313" t="n">
         <v>4.0</v>
@@ -4524,10 +4524,10 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D314" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,10 +4538,10 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D315" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D316" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D317" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D318" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D319" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D320" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D321" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D322" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D323" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D324" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D325" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D326" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2026.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D327" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2026.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D328" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2026.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D329" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2026.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>46282.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D330" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,24 +4762,24 @@
         <v>2026.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D331" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B332" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>45095.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D332" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,7 +4790,7 @@
         <v>2023.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,7 +4804,7 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,10 +4818,10 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D335" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="336">
@@ -4832,7 +4832,7 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D336" t="n">
         <v>3.0</v>
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D337" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,7 +4860,7 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D339" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D340" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D342" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2023.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D344" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4955,13 +4955,13 @@
         <v>6</v>
       </c>
       <c r="B345" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D345" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2024.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D346" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D347" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D348" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D349" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D350" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,7 +5042,7 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D351" t="n">
         <v>12.0</v>
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D352" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D353" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D354" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D355" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D356" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D357" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D358" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D359" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D360" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D361" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D362" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D363" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,7 +5224,7 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D364" t="n">
         <v>6.0</v>
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D365" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D366" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,7 +5266,7 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D367" t="n">
         <v>4.0</v>
@@ -5280,7 +5280,7 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D368" t="n">
         <v>4.0</v>
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D369" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D370" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D371" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D372" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D374" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,7 +5378,7 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D375" t="n">
         <v>1.0</v>
@@ -5392,7 +5392,7 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5406,7 +5406,7 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5420,10 +5420,10 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D378" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,10 +5434,10 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D379" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D380" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D381" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,7 +5476,7 @@
         <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D382" t="n">
         <v>1.0</v>
@@ -5490,7 +5490,7 @@
         <v>2024.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D383" t="n">
         <v>1.0</v>
@@ -5501,13 +5501,13 @@
         <v>6</v>
       </c>
       <c r="B384" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D384" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2025.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D385" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D386" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D387" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D388" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D389" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D390" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D391" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D392" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D393" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D394" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D395" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D396" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D397" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D398" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,7 +5714,7 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D399" t="n">
         <v>4.0</v>
@@ -5728,10 +5728,10 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D400" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,7 +5742,7 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D401" t="n">
         <v>1.0</v>
@@ -5756,7 +5756,7 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5770,7 +5770,7 @@
         <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5784,7 +5784,7 @@
         <v>2025.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5795,10 +5795,10 @@
         <v>6</v>
       </c>
       <c r="B405" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5812,7 +5812,7 @@
         <v>2026.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5820,13 +5820,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B407" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5837,10 +5837,10 @@
         <v>7</v>
       </c>
       <c r="B408" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D408" t="n">
         <v>1.0</v>
@@ -5854,10 +5854,10 @@
         <v>2022.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D409" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="410">
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D410" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D411" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D412" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,7 +5910,7 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D413" t="n">
         <v>3.0</v>
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D414" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,7 +5938,7 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D415" t="n">
         <v>5.0</v>
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D416" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D417" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D418" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D419" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D420" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D421" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D422" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D423" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D424" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D425" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D426" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D427" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D428" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D429" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D430" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,7 +6162,7 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D431" t="n">
         <v>4.0</v>
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D432" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D433" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D434" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D435" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D436" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D437" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D438" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D439" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D440" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,7 +6302,7 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D441" t="n">
         <v>2.0</v>
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D442" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D443" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D444" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2022.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D445" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="446">
@@ -6369,13 +6369,13 @@
         <v>7</v>
       </c>
       <c r="B446" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D446" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2023.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D447" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D448" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D449" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D450" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D451" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D452" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D453" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D454" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D455" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D456" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D457" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D458" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D459" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D460" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D461" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D462" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D463" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D464" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D465" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,7 +6652,7 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D466" t="n">
         <v>8.0</v>
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D467" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D468" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D469" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D470" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D471" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D472" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D473" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,7 +6764,7 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D474" t="n">
         <v>6.0</v>
@@ -6778,10 +6778,10 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D475" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D476" t="n">
         <v>2.0</v>
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D477" t="n">
         <v>2.0</v>
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D478" t="n">
         <v>2.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D479" t="n">
         <v>2.0</v>
@@ -6848,10 +6848,10 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D480" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="481">
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D481" t="n">
         <v>1.0</v>
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,10 +6932,10 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D486" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="487">
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D487" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D488" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D489" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D490" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D491" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,7 +7016,7 @@
         <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D492" t="n">
         <v>7.0</v>
@@ -7030,10 +7030,10 @@
         <v>2023.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D493" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="494">
@@ -7041,13 +7041,13 @@
         <v>7</v>
       </c>
       <c r="B494" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D494" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2024.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D495" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D496" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D497" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D498" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D499" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D500" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D501" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D502" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D503" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D504" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D505" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D506" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D507" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,7 +7240,7 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D508" t="n">
         <v>1.0</v>
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D509" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D511" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,7 +7310,7 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D513" t="n">
         <v>1.0</v>
@@ -7324,7 +7324,7 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,10 +7394,10 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D519" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="520">
@@ -7408,10 +7408,10 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D520" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D521" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D522" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="523">
@@ -7447,13 +7447,13 @@
         <v>7</v>
       </c>
       <c r="B523" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D523" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2025.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D524" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,7 +7478,7 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D525" t="n">
         <v>2.0</v>
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D526" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D527" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D528" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D529" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D530" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D531" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D532" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D533" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D534" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D535" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D536" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,7 +7646,7 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D537" t="n">
         <v>1.0</v>
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D538" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D539" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D540" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D541" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,7 +7716,7 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D542" t="n">
         <v>2.0</v>
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D543" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D544" t="n">
         <v>1.0</v>
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D547" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D548" t="n">
         <v>2.0</v>
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D549" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7839,10 +7839,10 @@
         <v>7</v>
       </c>
       <c r="B551" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D551" t="n">
         <v>1.0</v>
@@ -7856,7 +7856,7 @@
         <v>2026.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D552" t="n">
         <v>1.0</v>
@@ -7870,7 +7870,7 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D553" t="n">
         <v>1.0</v>
@@ -7884,10 +7884,10 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D554" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="555">
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D555" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D556" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D557" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D558" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D559" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,7 +7968,7 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D560" t="n">
         <v>1.0</v>
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D561" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D562" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D563" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,7 +8024,7 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D564" t="n">
         <v>1.0</v>
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D565" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D566" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,7 +8066,7 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D567" t="n">
         <v>1.0</v>
@@ -8080,7 +8080,7 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D568" t="n">
         <v>1.0</v>
@@ -8094,7 +8094,7 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46303.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D569" t="n">
         <v>1.0</v>
@@ -8102,13 +8102,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B570" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>45495.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D570" t="n">
         <v>1.0</v>
@@ -8122,10 +8122,10 @@
         <v>2024.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D571" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="572">
@@ -8133,13 +8133,13 @@
         <v>8</v>
       </c>
       <c r="B572" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D572" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="573">
@@ -8150,10 +8150,10 @@
         <v>2025.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D573" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D574" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D575" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D576" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D577" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D578" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D579" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D580" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D581" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,7 +8276,7 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D582" t="n">
         <v>1.0</v>
@@ -8290,7 +8290,7 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D583" t="n">
         <v>1.0</v>
@@ -8304,7 +8304,7 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D584" t="n">
         <v>1.0</v>
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D585" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D586" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,7 +8346,7 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D587" t="n">
         <v>1.0</v>
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D589" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,7 +8388,7 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D590" t="n">
         <v>2.0</v>
@@ -8402,7 +8402,7 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D591" t="n">
         <v>2.0</v>
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D592" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D593" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D594" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D595" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D596" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,7 +8486,7 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D597" t="n">
         <v>1.0</v>
@@ -8500,7 +8500,7 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D598" t="n">
         <v>1.0</v>
@@ -8514,7 +8514,7 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D599" t="n">
         <v>1.0</v>
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D600" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D601" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,7 +8556,7 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D602" t="n">
         <v>2.0</v>
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D603" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D604" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D605" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D606" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D607" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D608" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D609" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D610" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D611" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="612">
@@ -8693,13 +8693,13 @@
         <v>8</v>
       </c>
       <c r="B612" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D612" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2026.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D613" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D614" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D615" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D616" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D617" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D618" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D619" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D620" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D621" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D622" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D623" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D624" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D625" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D626" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D627" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D628" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D629" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D630" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D631" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D632" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D633" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D634" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D635" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D636" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D637" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D638" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D639" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D640" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D641" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D642" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D643" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D644" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D645" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,7 +9172,7 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D646" t="n">
         <v>1.0</v>
@@ -9186,10 +9186,10 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D647" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="648">
@@ -9200,7 +9200,7 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D648" t="n">
         <v>2.0</v>
@@ -9214,9 +9214,23 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="D649" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="s">
+        <v>8</v>
+      </c>
+      <c r="B650" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C650" t="n" s="2">
         <v>46303.0</v>
       </c>
-      <c r="D649" t="n">
+      <c r="D650" t="n">
         <v>5.0</v>
       </c>
     </row>
@@ -9267,7 +9281,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2273.0</v>
+        <v>2274.0</v>
       </c>
     </row>
   </sheetData>
@@ -9442,7 +9456,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
     </row>
     <row r="16">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8116,13 +8116,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B571" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>45495.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D571" t="n">
         <v>1.0</v>
@@ -8136,10 +8136,10 @@
         <v>2024.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D572" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="573">
@@ -8147,13 +8147,13 @@
         <v>8</v>
       </c>
       <c r="B573" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D573" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="574">
@@ -8164,10 +8164,10 @@
         <v>2025.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D574" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D575" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D576" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D577" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D578" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D579" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D580" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D581" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D582" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,7 +8290,7 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D583" t="n">
         <v>1.0</v>
@@ -8304,7 +8304,7 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D584" t="n">
         <v>1.0</v>
@@ -8318,7 +8318,7 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D585" t="n">
         <v>1.0</v>
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D586" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D587" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D589" t="n">
         <v>1.0</v>
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D590" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,7 +8402,7 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D591" t="n">
         <v>2.0</v>
@@ -8416,7 +8416,7 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D592" t="n">
         <v>2.0</v>
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D593" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D594" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D595" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D596" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D597" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,7 +8500,7 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D598" t="n">
         <v>1.0</v>
@@ -8514,7 +8514,7 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D599" t="n">
         <v>1.0</v>
@@ -8528,7 +8528,7 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D600" t="n">
         <v>1.0</v>
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D601" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D602" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,7 +8570,7 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D603" t="n">
         <v>2.0</v>
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D604" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D605" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D606" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D607" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D608" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D609" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D610" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D611" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D612" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="613">
@@ -8707,13 +8707,13 @@
         <v>8</v>
       </c>
       <c r="B613" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D613" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2026.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D614" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D615" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D616" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D617" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D618" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D619" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D620" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D621" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D622" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D623" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D624" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D625" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D626" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D627" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D628" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D629" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D630" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D631" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D632" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D633" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D634" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D635" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D636" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D637" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D638" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D639" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D640" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D641" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D642" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D643" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D644" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D645" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,10 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D646" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="647">
@@ -9186,7 +9186,7 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D647" t="n">
         <v>1.0</v>
@@ -9200,10 +9200,10 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D648" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="649">
@@ -9214,7 +9214,7 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D649" t="n">
         <v>2.0</v>
@@ -9228,10 +9228,38 @@
         <v>2026.0</v>
       </c>
       <c r="C650" t="n" s="2">
+        <v>46296.0</v>
+      </c>
+      <c r="D650" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="s">
+        <v>8</v>
+      </c>
+      <c r="B651" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C651" t="n" s="2">
         <v>46303.0</v>
       </c>
-      <c r="D650" t="n">
+      <c r="D651" t="n">
         <v>5.0</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="s">
+        <v>8</v>
+      </c>
+      <c r="B652" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C652" t="n" s="2">
+        <v>46317.0</v>
+      </c>
+      <c r="D652" t="n">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -9257,7 +9285,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="3">
@@ -9281,7 +9309,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2274.0</v>
+        <v>2275.0</v>
       </c>
     </row>
   </sheetData>
@@ -9379,7 +9407,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="9">
@@ -9412,7 +9440,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -9285,7 +9285,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>59.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="3">
@@ -9301,7 +9301,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1563.0</v>
+        <v>1564.0</v>
       </c>
     </row>
     <row r="5">
@@ -9363,7 +9363,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
     </row>
     <row r="5">
@@ -9440,7 +9440,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>45.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4784,13 +4784,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B333" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>45095.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D333" t="n">
         <v>1.0</v>
@@ -4804,7 +4804,7 @@
         <v>2023.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,7 +4818,7 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4832,10 +4832,10 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D336" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="337">
@@ -4846,7 +4846,7 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D337" t="n">
         <v>3.0</v>
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D338" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,7 +4874,7 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D339" t="n">
         <v>1.0</v>
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D340" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D341" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D342" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D343" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2023.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2023.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D345" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="346">
@@ -4969,13 +4969,13 @@
         <v>6</v>
       </c>
       <c r="B346" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D346" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2024.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D347" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D348" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D349" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D350" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D351" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,7 +5056,7 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D352" t="n">
         <v>12.0</v>
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D353" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D354" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D355" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D356" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D357" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D358" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D359" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D360" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D361" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D362" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D363" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D364" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,7 +5238,7 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D365" t="n">
         <v>6.0</v>
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D366" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D367" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,7 +5280,7 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D368" t="n">
         <v>4.0</v>
@@ -5294,7 +5294,7 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D369" t="n">
         <v>4.0</v>
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D370" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,10 +5322,10 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D371" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D372" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D373" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D374" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D375" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,7 +5392,7 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D376" t="n">
         <v>1.0</v>
@@ -5406,7 +5406,7 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5420,7 +5420,7 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5434,10 +5434,10 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D379" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="380">
@@ -5448,10 +5448,10 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D380" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D381" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D382" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,7 +5490,7 @@
         <v>2024.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D383" t="n">
         <v>1.0</v>
@@ -5504,7 +5504,7 @@
         <v>2024.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D384" t="n">
         <v>1.0</v>
@@ -5515,13 +5515,13 @@
         <v>6</v>
       </c>
       <c r="B385" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D385" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,10 +5532,10 @@
         <v>2025.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D386" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D387" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D388" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D389" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D390" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D391" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D392" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D393" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D394" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D395" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D396" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D397" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D398" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D399" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,7 +5728,7 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D400" t="n">
         <v>4.0</v>
@@ -5742,10 +5742,10 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D401" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,7 +5756,7 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D402" t="n">
         <v>1.0</v>
@@ -5770,7 +5770,7 @@
         <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5784,7 +5784,7 @@
         <v>2025.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5798,7 +5798,7 @@
         <v>2025.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5809,10 +5809,10 @@
         <v>6</v>
       </c>
       <c r="B406" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5826,7 +5826,7 @@
         <v>2026.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5834,13 +5834,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B408" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D408" t="n">
         <v>1.0</v>
@@ -5851,10 +5851,10 @@
         <v>7</v>
       </c>
       <c r="B409" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D409" t="n">
         <v>1.0</v>
@@ -5868,10 +5868,10 @@
         <v>2022.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D410" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="411">
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D411" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D412" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D413" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,7 +5924,7 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D414" t="n">
         <v>3.0</v>
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D415" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,7 +5952,7 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D416" t="n">
         <v>5.0</v>
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D417" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D418" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D419" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D420" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D421" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D422" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D423" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D424" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D425" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D426" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D427" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D428" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D429" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D430" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D431" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,7 +6176,7 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D432" t="n">
         <v>4.0</v>
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D433" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D434" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D435" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D436" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D437" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D438" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D439" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D440" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D441" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,7 +6316,7 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D442" t="n">
         <v>2.0</v>
@@ -6330,10 +6330,10 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D443" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D444" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2022.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D445" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2022.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D446" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="447">
@@ -6383,13 +6383,13 @@
         <v>7</v>
       </c>
       <c r="B447" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D447" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2023.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D448" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D449" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D450" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D451" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D452" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D453" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D454" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D455" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D456" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D457" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D458" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D459" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D460" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D461" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D462" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D463" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D464" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D465" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D466" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,7 +6666,7 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D467" t="n">
         <v>8.0</v>
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D468" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D469" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D470" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D471" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D472" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D473" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D474" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,7 +6778,7 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D475" t="n">
         <v>6.0</v>
@@ -6792,10 +6792,10 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D476" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D477" t="n">
         <v>2.0</v>
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D478" t="n">
         <v>2.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D479" t="n">
         <v>2.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D480" t="n">
         <v>2.0</v>
@@ -6862,10 +6862,10 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D481" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="482">
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D482" t="n">
         <v>1.0</v>
@@ -6890,7 +6890,7 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,10 +6946,10 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D487" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="488">
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D488" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D489" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D490" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D491" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D492" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,7 +7030,7 @@
         <v>2023.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D493" t="n">
         <v>7.0</v>
@@ -7044,10 +7044,10 @@
         <v>2023.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D494" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="495">
@@ -7055,13 +7055,13 @@
         <v>7</v>
       </c>
       <c r="B495" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D495" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,10 +7072,10 @@
         <v>2024.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D496" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D497" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D498" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D499" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D500" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D501" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D502" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D503" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D504" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D505" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D506" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D507" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D508" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,7 +7254,7 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D509" t="n">
         <v>1.0</v>
@@ -7268,10 +7268,10 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D512" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D513" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,7 +7324,7 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D514" t="n">
         <v>1.0</v>
@@ -7338,7 +7338,7 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,10 +7408,10 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D520" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="521">
@@ -7422,10 +7422,10 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D521" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D522" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2024.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D523" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="524">
@@ -7461,13 +7461,13 @@
         <v>7</v>
       </c>
       <c r="B524" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D524" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2025.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D525" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,7 +7492,7 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D526" t="n">
         <v>2.0</v>
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D527" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D528" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D529" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D530" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D531" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D532" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D533" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D534" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D535" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D536" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D537" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,7 +7660,7 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D538" t="n">
         <v>1.0</v>
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D539" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D540" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D541" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D542" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,7 +7730,7 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D543" t="n">
         <v>2.0</v>
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D544" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D545" t="n">
         <v>1.0</v>
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,10 +7800,10 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D548" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="549">
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D549" t="n">
         <v>2.0</v>
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D550" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,7 +7842,7 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D551" t="n">
         <v>1.0</v>
@@ -7853,10 +7853,10 @@
         <v>7</v>
       </c>
       <c r="B552" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D552" t="n">
         <v>1.0</v>
@@ -7870,7 +7870,7 @@
         <v>2026.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D553" t="n">
         <v>1.0</v>
@@ -7884,7 +7884,7 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D554" t="n">
         <v>1.0</v>
@@ -7898,10 +7898,10 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D555" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="556">
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D556" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D557" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D558" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D559" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D560" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,7 +7982,7 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D561" t="n">
         <v>1.0</v>
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D562" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D563" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D564" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,7 +8038,7 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D565" t="n">
         <v>1.0</v>
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D566" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D567" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,7 +8080,7 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D568" t="n">
         <v>1.0</v>
@@ -8094,7 +8094,7 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D569" t="n">
         <v>1.0</v>
@@ -8108,7 +8108,7 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46303.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D570" t="n">
         <v>1.0</v>
@@ -8122,7 +8122,7 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46310.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D571" t="n">
         <v>1.0</v>
@@ -8130,13 +8130,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B572" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>45495.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D572" t="n">
         <v>1.0</v>
@@ -8150,10 +8150,10 @@
         <v>2024.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D573" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="574">
@@ -8161,13 +8161,13 @@
         <v>8</v>
       </c>
       <c r="B574" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D574" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="575">
@@ -8178,10 +8178,10 @@
         <v>2025.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D575" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D576" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D577" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D578" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D579" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D580" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D581" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D582" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D583" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,7 +8304,7 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D584" t="n">
         <v>1.0</v>
@@ -8318,7 +8318,7 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D585" t="n">
         <v>1.0</v>
@@ -8332,7 +8332,7 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D586" t="n">
         <v>1.0</v>
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D587" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,10 +8360,10 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D588" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D589" t="n">
         <v>1.0</v>
@@ -8388,7 +8388,7 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D590" t="n">
         <v>1.0</v>
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D591" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,7 +8416,7 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D592" t="n">
         <v>2.0</v>
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D593" t="n">
         <v>2.0</v>
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D594" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D595" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D596" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D597" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D598" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,7 +8514,7 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D599" t="n">
         <v>1.0</v>
@@ -8528,7 +8528,7 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D600" t="n">
         <v>1.0</v>
@@ -8542,7 +8542,7 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D601" t="n">
         <v>1.0</v>
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D602" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D603" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,7 +8584,7 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D604" t="n">
         <v>2.0</v>
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D605" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D606" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D607" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D608" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D609" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D610" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D611" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D612" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2025.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D613" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="614">
@@ -8721,13 +8721,13 @@
         <v>8</v>
       </c>
       <c r="B614" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D614" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2026.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D615" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D616" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D617" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D618" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D619" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D620" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D621" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D622" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D623" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D624" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D625" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D626" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D627" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D628" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D629" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D630" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D631" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D632" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D633" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D634" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D635" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D636" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D637" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D638" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D639" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D640" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D641" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D642" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D643" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D644" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D645" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,10 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D646" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="647">
@@ -9186,10 +9186,10 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D647" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="648">
@@ -9200,7 +9200,7 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D648" t="n">
         <v>1.0</v>
@@ -9214,10 +9214,10 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D649" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="650">
@@ -9228,7 +9228,7 @@
         <v>2026.0</v>
       </c>
       <c r="C650" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D650" t="n">
         <v>2.0</v>
@@ -9242,10 +9242,10 @@
         <v>2026.0</v>
       </c>
       <c r="C651" t="n" s="2">
-        <v>46303.0</v>
+        <v>46296.0</v>
       </c>
       <c r="D651" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="652">
@@ -9256,9 +9256,23 @@
         <v>2026.0</v>
       </c>
       <c r="C652" t="n" s="2">
+        <v>46303.0</v>
+      </c>
+      <c r="D652" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="s">
+        <v>8</v>
+      </c>
+      <c r="B653" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C653" t="n" s="2">
         <v>46317.0</v>
       </c>
-      <c r="D652" t="n">
+      <c r="D653" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -9293,7 +9307,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
     </row>
     <row r="4">
@@ -9407,7 +9421,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>373.0</v>
+        <v>374.0</v>
       </c>
     </row>
     <row r="9">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1886,13 +1886,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B126" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C126" t="n" s="2">
-        <v>44561.0</v>
+        <v>46317.0</v>
       </c>
       <c r="D126" t="n">
         <v>1.0</v>
@@ -1903,13 +1903,13 @@
         <v>5</v>
       </c>
       <c r="B127" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D127" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="128">
@@ -1920,10 +1920,10 @@
         <v>2022.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D128" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D129" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D130" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D131" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,10 +1976,10 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D132" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="133">
@@ -1990,7 +1990,7 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D133" t="n">
         <v>1.0</v>
@@ -2004,10 +2004,10 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D134" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="135">
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D135" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,10 +2032,10 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D136" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="137">
@@ -2046,7 +2046,7 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D137" t="n">
         <v>2.0</v>
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D138" t="n">
         <v>2.0</v>
@@ -2074,10 +2074,10 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D139" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="140">
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D140" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,7 +2102,7 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D141" t="n">
         <v>3.0</v>
@@ -2116,10 +2116,10 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D142" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="143">
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D143" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,7 +2144,7 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D144" t="n">
         <v>3.0</v>
@@ -2158,10 +2158,10 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D145" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="146">
@@ -2172,10 +2172,10 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D146" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D147" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,7 +2200,7 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D148" t="n">
         <v>1.0</v>
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,7 +2312,7 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D156" t="n">
         <v>1.0</v>
@@ -2326,7 +2326,7 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D157" t="n">
         <v>1.0</v>
@@ -2340,7 +2340,7 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D158" t="n">
         <v>1.0</v>
@@ -2354,7 +2354,7 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D159" t="n">
         <v>1.0</v>
@@ -2368,7 +2368,7 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D160" t="n">
         <v>1.0</v>
@@ -2382,10 +2382,10 @@
         <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D161" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="162">
@@ -2396,10 +2396,10 @@
         <v>2022.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D162" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,7 +2410,7 @@
         <v>2022.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D163" t="n">
         <v>1.0</v>
@@ -2424,7 +2424,7 @@
         <v>2022.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D164" t="n">
         <v>1.0</v>
@@ -2438,10 +2438,10 @@
         <v>2022.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D165" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="166">
@@ -2449,13 +2449,13 @@
         <v>5</v>
       </c>
       <c r="B166" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D166" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="167">
@@ -2466,10 +2466,10 @@
         <v>2023.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D168" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D169" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D170" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,7 +2522,7 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D171" t="n">
         <v>4.0</v>
@@ -2536,10 +2536,10 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D172" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="173">
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D173" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D174" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D175" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D176" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D177" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D178" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D179" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D180" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D181" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D182" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D183" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D184" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D185" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D186" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D187" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D188" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D189" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D190" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D191" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D192" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D193" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D194" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D195" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D196" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,7 +2886,7 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D197" t="n">
         <v>2.0</v>
@@ -2900,10 +2900,10 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D198" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="199">
@@ -2914,7 +2914,7 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D199" t="n">
         <v>5.0</v>
@@ -2928,10 +2928,10 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D200" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="201">
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D201" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D202" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,7 +2970,7 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D203" t="n">
         <v>1.0</v>
@@ -2984,10 +2984,10 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D204" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="205">
@@ -2998,10 +2998,10 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D205" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D206" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,7 +3026,7 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D207" t="n">
         <v>8.0</v>
@@ -3040,10 +3040,10 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D208" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="209">
@@ -3054,10 +3054,10 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D209" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,7 +3068,7 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D210" t="n">
         <v>9.0</v>
@@ -3082,10 +3082,10 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D211" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="212">
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D212" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D213" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2023.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D214" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2023.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D215" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2023.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D216" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2023.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D217" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="218">
@@ -3177,13 +3177,13 @@
         <v>5</v>
       </c>
       <c r="B218" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D218" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="219">
@@ -3194,10 +3194,10 @@
         <v>2024.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D219" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D220" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D221" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D222" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D223" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D224" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D225" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D226" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D227" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D228" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D229" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D230" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D231" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D232" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D233" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D234" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D235" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D236" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D237" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D238" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D239" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D240" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D241" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D242" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D243" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,7 +3544,7 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D244" t="n">
         <v>12.0</v>
@@ -3558,10 +3558,10 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D245" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="246">
@@ -3572,10 +3572,10 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D246" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D247" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D248" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D249" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,7 +3628,7 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D250" t="n">
         <v>4.0</v>
@@ -3642,7 +3642,7 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D251" t="n">
         <v>4.0</v>
@@ -3656,7 +3656,7 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D252" t="n">
         <v>4.0</v>
@@ -3670,10 +3670,10 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D253" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="254">
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D254" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D255" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D256" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D257" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D258" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2024.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D259" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,7 +3768,7 @@
         <v>2024.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D260" t="n">
         <v>3.0</v>
@@ -3782,10 +3782,10 @@
         <v>2024.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D261" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="262">
@@ -3796,7 +3796,7 @@
         <v>2024.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D262" t="n">
         <v>1.0</v>
@@ -3807,13 +3807,13 @@
         <v>5</v>
       </c>
       <c r="B263" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D263" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="264">
@@ -3824,10 +3824,10 @@
         <v>2025.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D264" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,7 +3838,7 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D265" t="n">
         <v>1.0</v>
@@ -3852,10 +3852,10 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D266" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="267">
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D267" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D268" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D269" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D270" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D271" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D272" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D273" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D274" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D275" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D276" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D277" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D278" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D279" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D280" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D281" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D282" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,7 +4090,7 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D283" t="n">
         <v>4.0</v>
@@ -4104,10 +4104,10 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D284" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="285">
@@ -4118,10 +4118,10 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D285" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D286" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,10 +4146,10 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D287" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4160,7 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D288" t="n">
         <v>1.0</v>
@@ -4174,10 +4174,10 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D289" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4188,7 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D290" t="n">
         <v>3.0</v>
@@ -4202,10 +4202,10 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D291" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="292">
@@ -4216,7 +4216,7 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D292" t="n">
         <v>1.0</v>
@@ -4230,10 +4230,10 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D293" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="294">
@@ -4244,10 +4244,10 @@
         <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D294" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2025.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D295" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2025.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D296" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2025.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D297" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2025.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D298" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="299">
@@ -4311,13 +4311,13 @@
         <v>5</v>
       </c>
       <c r="B299" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D299" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="300">
@@ -4328,10 +4328,10 @@
         <v>2026.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D301" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D302" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D303" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D304" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D305" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,7 +4412,7 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D306" t="n">
         <v>5.0</v>
@@ -4426,10 +4426,10 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D307" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="308">
@@ -4440,7 +4440,7 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D308" t="n">
         <v>2.0</v>
@@ -4454,10 +4454,10 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D309" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="310">
@@ -4468,10 +4468,10 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D310" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D311" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D312" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D313" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,7 +4524,7 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D314" t="n">
         <v>4.0</v>
@@ -4538,10 +4538,10 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D315" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="316">
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D316" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D317" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D318" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D319" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D320" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D321" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D322" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D323" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D324" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D325" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D326" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2026.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D327" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2026.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D328" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2026.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D329" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2026.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D330" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2026.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>46282.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D331" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2026.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D332" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,21 +4790,21 @@
         <v>2026.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>46310.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D333" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B334" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>45095.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D334" t="n">
         <v>1.0</v>
@@ -4818,7 +4818,7 @@
         <v>2023.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4832,7 +4832,7 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,10 +4846,10 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D337" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="338">
@@ -4860,7 +4860,7 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D338" t="n">
         <v>3.0</v>
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D339" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,7 +4888,7 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D340" t="n">
         <v>1.0</v>
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D341" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,10 +4916,10 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D342" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D343" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2023.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D344" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2023.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D345" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2023.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D346" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="347">
@@ -4983,13 +4983,13 @@
         <v>6</v>
       </c>
       <c r="B347" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D347" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2024.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D348" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D349" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D350" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D351" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D352" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,7 +5070,7 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D353" t="n">
         <v>12.0</v>
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D354" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D355" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D356" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D357" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D358" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D359" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D360" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D361" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D362" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D363" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D364" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D365" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,7 +5252,7 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D366" t="n">
         <v>6.0</v>
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D367" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D368" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,7 +5294,7 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D369" t="n">
         <v>4.0</v>
@@ -5308,7 +5308,7 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D370" t="n">
         <v>4.0</v>
@@ -5322,10 +5322,10 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D371" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="372">
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D372" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D374" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D376" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,7 +5406,7 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D377" t="n">
         <v>1.0</v>
@@ -5420,7 +5420,7 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5434,7 +5434,7 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D379" t="n">
         <v>1.0</v>
@@ -5448,10 +5448,10 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D380" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="381">
@@ -5462,10 +5462,10 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D381" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D382" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2024.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D383" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,7 +5504,7 @@
         <v>2024.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D384" t="n">
         <v>1.0</v>
@@ -5518,7 +5518,7 @@
         <v>2024.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D385" t="n">
         <v>1.0</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B386" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D386" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="387">
@@ -5546,10 +5546,10 @@
         <v>2025.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D387" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D388" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D389" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D390" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D391" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D392" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D393" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D394" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D395" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D396" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D397" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D398" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D399" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D400" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,7 +5742,7 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D401" t="n">
         <v>4.0</v>
@@ -5756,10 +5756,10 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D402" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,7 +5770,7 @@
         <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D403" t="n">
         <v>1.0</v>
@@ -5784,7 +5784,7 @@
         <v>2025.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5798,7 +5798,7 @@
         <v>2025.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5812,7 +5812,7 @@
         <v>2025.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5823,10 +5823,10 @@
         <v>6</v>
       </c>
       <c r="B407" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5840,7 +5840,7 @@
         <v>2026.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D408" t="n">
         <v>1.0</v>
@@ -5848,13 +5848,13 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B409" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D409" t="n">
         <v>1.0</v>
@@ -5865,10 +5865,10 @@
         <v>7</v>
       </c>
       <c r="B410" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D410" t="n">
         <v>1.0</v>
@@ -5882,10 +5882,10 @@
         <v>2022.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D411" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="412">
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D412" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D413" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D414" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,7 +5938,7 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D415" t="n">
         <v>3.0</v>
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D416" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,7 +5966,7 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D417" t="n">
         <v>5.0</v>
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D418" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D419" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D420" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D421" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D422" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D423" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D424" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D425" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D426" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D427" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D428" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D429" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D430" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D431" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D432" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,7 +6190,7 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D433" t="n">
         <v>4.0</v>
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D434" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D435" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D436" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D437" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D438" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D439" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D440" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D441" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D442" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,7 +6330,7 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D443" t="n">
         <v>2.0</v>
@@ -6344,10 +6344,10 @@
         <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D444" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,10 +6358,10 @@
         <v>2022.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D445" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2022.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D446" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2022.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D447" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="448">
@@ -6397,13 +6397,13 @@
         <v>7</v>
       </c>
       <c r="B448" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D448" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2023.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D449" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D450" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D451" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D452" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D453" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D454" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D455" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D456" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D457" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D458" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D459" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D460" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D461" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D462" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D463" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D464" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D465" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D466" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D467" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,7 +6680,7 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D468" t="n">
         <v>8.0</v>
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D469" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D470" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D471" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D472" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D473" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D474" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D475" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,7 +6792,7 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D476" t="n">
         <v>6.0</v>
@@ -6806,10 +6806,10 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D477" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D478" t="n">
         <v>2.0</v>
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D479" t="n">
         <v>2.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D480" t="n">
         <v>2.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D481" t="n">
         <v>2.0</v>
@@ -6876,10 +6876,10 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D482" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="483">
@@ -6890,7 +6890,7 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D483" t="n">
         <v>1.0</v>
@@ -6904,7 +6904,7 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,7 +6946,7 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D487" t="n">
         <v>1.0</v>
@@ -6960,10 +6960,10 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D488" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="489">
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D489" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D490" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D491" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D492" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2023.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D493" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,7 +7044,7 @@
         <v>2023.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D494" t="n">
         <v>7.0</v>
@@ -7058,10 +7058,10 @@
         <v>2023.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D495" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="496">
@@ -7069,13 +7069,13 @@
         <v>7</v>
       </c>
       <c r="B496" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D496" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="497">
@@ -7086,10 +7086,10 @@
         <v>2024.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D497" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D498" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D499" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D500" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D501" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D502" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D503" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D504" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D505" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D506" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D507" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D508" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D509" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,7 +7268,7 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D510" t="n">
         <v>1.0</v>
@@ -7282,10 +7282,10 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D511" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,10 +7296,10 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D512" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D513" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,7 +7338,7 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D515" t="n">
         <v>1.0</v>
@@ -7352,7 +7352,7 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,7 +7408,7 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,10 +7422,10 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D521" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="522">
@@ -7436,10 +7436,10 @@
         <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D522" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2024.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D523" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2024.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D524" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="525">
@@ -7475,13 +7475,13 @@
         <v>7</v>
       </c>
       <c r="B525" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D525" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2025.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D526" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,7 +7506,7 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D527" t="n">
         <v>2.0</v>
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D528" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D529" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D530" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D531" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D532" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D533" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D534" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D535" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D536" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D537" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D538" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,7 +7674,7 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D539" t="n">
         <v>1.0</v>
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D540" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D541" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D542" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D543" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,7 +7744,7 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D544" t="n">
         <v>2.0</v>
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D545" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D546" t="n">
         <v>1.0</v>
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,10 +7814,10 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D549" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="550">
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D550" t="n">
         <v>2.0</v>
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D551" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,7 +7856,7 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D552" t="n">
         <v>1.0</v>
@@ -7867,10 +7867,10 @@
         <v>7</v>
       </c>
       <c r="B553" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D553" t="n">
         <v>1.0</v>
@@ -7884,7 +7884,7 @@
         <v>2026.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D554" t="n">
         <v>1.0</v>
@@ -7898,7 +7898,7 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D555" t="n">
         <v>1.0</v>
@@ -7912,10 +7912,10 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D556" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="557">
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D557" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D558" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D559" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D560" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D561" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,7 +7996,7 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D562" t="n">
         <v>1.0</v>
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D563" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D564" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D565" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,7 +8052,7 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D566" t="n">
         <v>1.0</v>
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D567" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D568" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,7 +8094,7 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D569" t="n">
         <v>1.0</v>
@@ -8108,7 +8108,7 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D570" t="n">
         <v>1.0</v>
@@ -8122,7 +8122,7 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46303.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D571" t="n">
         <v>1.0</v>
@@ -8136,7 +8136,7 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46310.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D572" t="n">
         <v>1.0</v>
@@ -8144,13 +8144,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B573" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>45495.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D573" t="n">
         <v>1.0</v>
@@ -8164,10 +8164,10 @@
         <v>2024.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D574" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="575">
@@ -8175,13 +8175,13 @@
         <v>8</v>
       </c>
       <c r="B575" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D575" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="576">
@@ -8192,10 +8192,10 @@
         <v>2025.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D576" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D577" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D578" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D579" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D580" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D581" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D582" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D583" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D584" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,7 +8318,7 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D585" t="n">
         <v>1.0</v>
@@ -8332,7 +8332,7 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D586" t="n">
         <v>1.0</v>
@@ -8346,7 +8346,7 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D587" t="n">
         <v>1.0</v>
@@ -8360,10 +8360,10 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D588" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="589">
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D589" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,7 +8388,7 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D590" t="n">
         <v>1.0</v>
@@ -8402,7 +8402,7 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D591" t="n">
         <v>1.0</v>
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D592" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D593" t="n">
         <v>2.0</v>
@@ -8444,7 +8444,7 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D594" t="n">
         <v>2.0</v>
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D595" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D596" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D597" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D598" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D599" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,7 +8528,7 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D600" t="n">
         <v>1.0</v>
@@ -8542,7 +8542,7 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D601" t="n">
         <v>1.0</v>
@@ -8556,7 +8556,7 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D602" t="n">
         <v>1.0</v>
@@ -8570,10 +8570,10 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D603" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="604">
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D604" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,7 +8598,7 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D605" t="n">
         <v>2.0</v>
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D606" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D607" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D608" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D609" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D610" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D611" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D612" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2025.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D613" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2025.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D614" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="615">
@@ -8735,13 +8735,13 @@
         <v>8</v>
       </c>
       <c r="B615" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D615" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2026.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D616" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D617" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D618" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D619" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D620" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D621" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D622" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D623" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D624" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D625" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D626" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D627" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D628" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D629" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D630" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D631" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D632" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D633" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D634" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D635" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D636" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D637" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D638" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D639" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D640" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D641" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D642" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D643" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D644" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D645" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,10 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D646" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="647">
@@ -9186,10 +9186,10 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D647" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="648">
@@ -9200,10 +9200,10 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D648" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="649">
@@ -9214,7 +9214,7 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D649" t="n">
         <v>1.0</v>
@@ -9228,10 +9228,10 @@
         <v>2026.0</v>
       </c>
       <c r="C650" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D650" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="651">
@@ -9242,7 +9242,7 @@
         <v>2026.0</v>
       </c>
       <c r="C651" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D651" t="n">
         <v>2.0</v>
@@ -9256,10 +9256,10 @@
         <v>2026.0</v>
       </c>
       <c r="C652" t="n" s="2">
-        <v>46303.0</v>
+        <v>46296.0</v>
       </c>
       <c r="D652" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="653">
@@ -9270,10 +9270,24 @@
         <v>2026.0</v>
       </c>
       <c r="C653" t="n" s="2">
+        <v>46303.0</v>
+      </c>
+      <c r="D653" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="s">
+        <v>8</v>
+      </c>
+      <c r="B654" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C654" t="n" s="2">
         <v>46317.0</v>
       </c>
-      <c r="D653" t="n">
-        <v>1.0</v>
+      <c r="D654" t="n">
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -9299,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="3">
@@ -9315,7 +9329,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1564.0</v>
+        <v>1565.0</v>
       </c>
     </row>
     <row r="5">
@@ -9454,7 +9468,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="12">
@@ -9487,7 +9501,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>514.0</v>
+        <v>515.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -4812,13 +4812,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B335" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>45095.0</v>
+        <v>46317.0</v>
       </c>
       <c r="D335" t="n">
         <v>1.0</v>
@@ -4832,7 +4832,7 @@
         <v>2023.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,7 +4846,7 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D337" t="n">
         <v>1.0</v>
@@ -4860,10 +4860,10 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D338" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="339">
@@ -4874,7 +4874,7 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D339" t="n">
         <v>3.0</v>
@@ -4888,10 +4888,10 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D340" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="341">
@@ -4902,7 +4902,7 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D341" t="n">
         <v>1.0</v>
@@ -4916,10 +4916,10 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D342" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="343">
@@ -4930,10 +4930,10 @@
         <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D343" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2023.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D344" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2023.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D345" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2023.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D346" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2023.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D347" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="348">
@@ -4997,13 +4997,13 @@
         <v>6</v>
       </c>
       <c r="B348" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D348" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="349">
@@ -5014,10 +5014,10 @@
         <v>2024.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D349" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D350" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D351" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D352" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D353" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,7 +5084,7 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D354" t="n">
         <v>12.0</v>
@@ -5098,10 +5098,10 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D355" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="356">
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D356" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D357" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D358" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D359" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D360" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D361" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D362" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D363" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D364" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D365" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D366" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,7 +5266,7 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D367" t="n">
         <v>6.0</v>
@@ -5280,10 +5280,10 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D368" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="369">
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D369" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,7 +5308,7 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D370" t="n">
         <v>4.0</v>
@@ -5322,7 +5322,7 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D371" t="n">
         <v>4.0</v>
@@ -5336,10 +5336,10 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D372" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="373">
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D373" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D374" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D375" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D376" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D377" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,7 +5420,7 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D378" t="n">
         <v>1.0</v>
@@ -5434,7 +5434,7 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D379" t="n">
         <v>1.0</v>
@@ -5448,7 +5448,7 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D380" t="n">
         <v>1.0</v>
@@ -5462,10 +5462,10 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D381" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="382">
@@ -5476,10 +5476,10 @@
         <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D382" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2024.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D383" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2024.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D384" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,7 +5518,7 @@
         <v>2024.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D385" t="n">
         <v>1.0</v>
@@ -5532,7 +5532,7 @@
         <v>2024.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D386" t="n">
         <v>1.0</v>
@@ -5543,13 +5543,13 @@
         <v>6</v>
       </c>
       <c r="B387" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D387" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="388">
@@ -5560,10 +5560,10 @@
         <v>2025.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D388" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D389" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D390" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D391" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D392" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D393" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D394" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D395" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D396" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D397" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D398" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D399" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D400" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D401" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,7 +5756,7 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D402" t="n">
         <v>4.0</v>
@@ -5770,10 +5770,10 @@
         <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D403" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="404">
@@ -5784,7 +5784,7 @@
         <v>2025.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D404" t="n">
         <v>1.0</v>
@@ -5798,7 +5798,7 @@
         <v>2025.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5812,7 +5812,7 @@
         <v>2025.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5826,7 +5826,7 @@
         <v>2025.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5837,10 +5837,10 @@
         <v>6</v>
       </c>
       <c r="B408" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D408" t="n">
         <v>1.0</v>
@@ -5854,7 +5854,7 @@
         <v>2026.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D409" t="n">
         <v>1.0</v>
@@ -5862,13 +5862,13 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B410" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D410" t="n">
         <v>1.0</v>
@@ -5879,10 +5879,10 @@
         <v>7</v>
       </c>
       <c r="B411" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D411" t="n">
         <v>1.0</v>
@@ -5896,10 +5896,10 @@
         <v>2022.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D412" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="413">
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D413" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D414" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D415" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,7 +5952,7 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D416" t="n">
         <v>3.0</v>
@@ -5966,10 +5966,10 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D417" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="418">
@@ -5980,7 +5980,7 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D418" t="n">
         <v>5.0</v>
@@ -5994,10 +5994,10 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D419" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="420">
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D420" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D421" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D422" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D423" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D424" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D425" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D426" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D427" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D428" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D429" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D430" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D431" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D432" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D433" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,7 +6204,7 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D434" t="n">
         <v>4.0</v>
@@ -6218,10 +6218,10 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D435" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="436">
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D436" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D437" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D438" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D439" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D440" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D441" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D442" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D443" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,7 +6344,7 @@
         <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D444" t="n">
         <v>2.0</v>
@@ -6358,10 +6358,10 @@
         <v>2022.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D445" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="446">
@@ -6372,10 +6372,10 @@
         <v>2022.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D446" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2022.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D447" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2022.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D448" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="449">
@@ -6411,13 +6411,13 @@
         <v>7</v>
       </c>
       <c r="B449" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D449" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="450">
@@ -6428,10 +6428,10 @@
         <v>2023.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D450" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D451" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D452" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D453" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D454" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D455" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D456" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D457" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D458" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D459" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D460" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D461" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D462" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D463" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D464" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D465" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D466" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D467" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D468" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,7 +6694,7 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D469" t="n">
         <v>8.0</v>
@@ -6708,10 +6708,10 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D470" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="471">
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D471" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D472" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D473" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D474" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D475" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D476" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,7 +6806,7 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D477" t="n">
         <v>6.0</v>
@@ -6820,10 +6820,10 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D478" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="479">
@@ -6834,7 +6834,7 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D479" t="n">
         <v>2.0</v>
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D480" t="n">
         <v>2.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D481" t="n">
         <v>2.0</v>
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D482" t="n">
         <v>2.0</v>
@@ -6890,10 +6890,10 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D483" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="484">
@@ -6904,7 +6904,7 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D484" t="n">
         <v>1.0</v>
@@ -6918,7 +6918,7 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,7 +6946,7 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D487" t="n">
         <v>1.0</v>
@@ -6960,7 +6960,7 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D488" t="n">
         <v>1.0</v>
@@ -6974,10 +6974,10 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D489" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="490">
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D490" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D491" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D492" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2023.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D493" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2023.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D494" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,7 +7058,7 @@
         <v>2023.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D495" t="n">
         <v>7.0</v>
@@ -7072,10 +7072,10 @@
         <v>2023.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D496" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="497">
@@ -7083,13 +7083,13 @@
         <v>7</v>
       </c>
       <c r="B497" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D497" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="498">
@@ -7100,10 +7100,10 @@
         <v>2024.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D498" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D499" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D500" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D501" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D502" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D503" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D504" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D505" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D506" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D507" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D508" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D509" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D510" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,7 +7282,7 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D511" t="n">
         <v>1.0</v>
@@ -7296,10 +7296,10 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D512" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="513">
@@ -7310,10 +7310,10 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D513" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D514" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D515" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,7 +7352,7 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D516" t="n">
         <v>1.0</v>
@@ -7366,7 +7366,7 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,7 +7408,7 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,7 +7422,7 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D521" t="n">
         <v>1.0</v>
@@ -7436,10 +7436,10 @@
         <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D522" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="523">
@@ -7450,10 +7450,10 @@
         <v>2024.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D523" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2024.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D524" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2024.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D525" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="526">
@@ -7489,13 +7489,13 @@
         <v>7</v>
       </c>
       <c r="B526" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D526" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="527">
@@ -7506,10 +7506,10 @@
         <v>2025.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D527" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,7 +7520,7 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D528" t="n">
         <v>2.0</v>
@@ -7534,10 +7534,10 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D529" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="530">
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D530" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D531" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D532" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D533" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D534" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D535" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D536" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D537" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D538" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D539" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,7 +7688,7 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D540" t="n">
         <v>1.0</v>
@@ -7702,10 +7702,10 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D541" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="542">
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D542" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D543" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D544" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,7 +7758,7 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D545" t="n">
         <v>2.0</v>
@@ -7772,10 +7772,10 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D546" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="547">
@@ -7786,7 +7786,7 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D547" t="n">
         <v>1.0</v>
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,10 +7828,10 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D550" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="551">
@@ -7842,7 +7842,7 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D551" t="n">
         <v>2.0</v>
@@ -7856,10 +7856,10 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D552" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="553">
@@ -7870,7 +7870,7 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D553" t="n">
         <v>1.0</v>
@@ -7881,10 +7881,10 @@
         <v>7</v>
       </c>
       <c r="B554" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D554" t="n">
         <v>1.0</v>
@@ -7898,7 +7898,7 @@
         <v>2026.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D555" t="n">
         <v>1.0</v>
@@ -7912,7 +7912,7 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D556" t="n">
         <v>1.0</v>
@@ -7926,10 +7926,10 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D557" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="558">
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D558" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D559" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D560" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D561" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D562" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,7 +8010,7 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D563" t="n">
         <v>1.0</v>
@@ -8024,10 +8024,10 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D564" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="565">
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D565" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D566" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,7 +8066,7 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D567" t="n">
         <v>1.0</v>
@@ -8080,10 +8080,10 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D568" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="569">
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D569" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,7 +8108,7 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D570" t="n">
         <v>1.0</v>
@@ -8122,7 +8122,7 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D571" t="n">
         <v>1.0</v>
@@ -8136,7 +8136,7 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46303.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D572" t="n">
         <v>1.0</v>
@@ -8150,7 +8150,7 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46310.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D573" t="n">
         <v>1.0</v>
@@ -8158,13 +8158,13 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B574" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>45495.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D574" t="n">
         <v>1.0</v>
@@ -8178,10 +8178,10 @@
         <v>2024.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D575" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="576">
@@ -8189,13 +8189,13 @@
         <v>8</v>
       </c>
       <c r="B576" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D576" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2025.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D577" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D578" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D579" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D580" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D581" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D582" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D583" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D584" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D585" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,7 +8332,7 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D586" t="n">
         <v>1.0</v>
@@ -8346,7 +8346,7 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D587" t="n">
         <v>1.0</v>
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,10 +8374,10 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D589" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="590">
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D590" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,7 +8402,7 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D591" t="n">
         <v>1.0</v>
@@ -8416,7 +8416,7 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D592" t="n">
         <v>1.0</v>
@@ -8430,10 +8430,10 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D593" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="594">
@@ -8444,7 +8444,7 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D594" t="n">
         <v>2.0</v>
@@ -8458,7 +8458,7 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D595" t="n">
         <v>2.0</v>
@@ -8472,10 +8472,10 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D596" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="597">
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D597" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D598" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D599" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D600" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,7 +8542,7 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D601" t="n">
         <v>1.0</v>
@@ -8556,7 +8556,7 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D602" t="n">
         <v>1.0</v>
@@ -8570,7 +8570,7 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D603" t="n">
         <v>1.0</v>
@@ -8584,10 +8584,10 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D604" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="605">
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D605" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,7 +8612,7 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D606" t="n">
         <v>2.0</v>
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D607" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D608" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D609" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D610" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D611" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D612" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2025.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D613" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2025.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D614" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2025.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D615" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="616">
@@ -8749,13 +8749,13 @@
         <v>8</v>
       </c>
       <c r="B616" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D616" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2026.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D617" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D618" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D619" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D620" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D621" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D622" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D623" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D624" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D625" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D626" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D627" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D628" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D629" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D630" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D631" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D632" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D633" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D634" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D635" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D636" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D637" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D638" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D639" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D640" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D641" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D642" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D643" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D644" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D645" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,10 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D646" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="647">
@@ -9186,10 +9186,10 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D647" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="648">
@@ -9200,10 +9200,10 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D648" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="649">
@@ -9214,10 +9214,10 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D649" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="650">
@@ -9228,7 +9228,7 @@
         <v>2026.0</v>
       </c>
       <c r="C650" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D650" t="n">
         <v>1.0</v>
@@ -9242,10 +9242,10 @@
         <v>2026.0</v>
       </c>
       <c r="C651" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D651" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="652">
@@ -9256,7 +9256,7 @@
         <v>2026.0</v>
       </c>
       <c r="C652" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D652" t="n">
         <v>2.0</v>
@@ -9270,10 +9270,10 @@
         <v>2026.0</v>
       </c>
       <c r="C653" t="n" s="2">
-        <v>46303.0</v>
+        <v>46296.0</v>
       </c>
       <c r="D653" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="654">
@@ -9284,9 +9284,23 @@
         <v>2026.0</v>
       </c>
       <c r="C654" t="n" s="2">
+        <v>46303.0</v>
+      </c>
+      <c r="D654" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="s">
+        <v>8</v>
+      </c>
+      <c r="B655" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C655" t="n" s="2">
         <v>46317.0</v>
       </c>
-      <c r="D654" t="n">
+      <c r="D655" t="n">
         <v>3.0</v>
       </c>
     </row>
@@ -9313,7 +9327,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>60.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="3">
@@ -9329,7 +9343,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1565.0</v>
+        <v>1567.0</v>
       </c>
     </row>
     <row r="5">
@@ -9337,7 +9351,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2275.0</v>
+        <v>2276.0</v>
       </c>
     </row>
   </sheetData>
@@ -9380,7 +9394,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="4">
@@ -9435,7 +9449,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>374.0</v>
+        <v>375.0</v>
       </c>
     </row>
     <row r="9">
@@ -9468,7 +9482,7 @@
         <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>46.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="12">
@@ -9490,7 +9504,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="14">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1895,7 +1895,7 @@
         <v>46317.0</v>
       </c>
       <c r="D126" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="127">
@@ -9343,7 +9343,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1567.0</v>
+        <v>1568.0</v>
       </c>
     </row>
     <row r="5">
@@ -9515,7 +9515,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>515.0</v>
+        <v>516.0</v>
       </c>
     </row>
     <row r="15">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -1900,13 +1900,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B127" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C127" t="n" s="2">
-        <v>44561.0</v>
+        <v>46324.0</v>
       </c>
       <c r="D127" t="n">
         <v>1.0</v>
@@ -1917,13 +1917,13 @@
         <v>5</v>
       </c>
       <c r="B128" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C128" t="n" s="2">
-        <v>44576.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D128" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="129">
@@ -1934,10 +1934,10 @@
         <v>2022.0</v>
       </c>
       <c r="C129" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D129" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="130">
@@ -1948,10 +1948,10 @@
         <v>2022.0</v>
       </c>
       <c r="C130" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D130" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="131">
@@ -1962,10 +1962,10 @@
         <v>2022.0</v>
       </c>
       <c r="C131" t="n" s="2">
-        <v>44597.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D131" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="132">
@@ -1976,10 +1976,10 @@
         <v>2022.0</v>
       </c>
       <c r="C132" t="n" s="2">
-        <v>44604.0</v>
+        <v>44597.0</v>
       </c>
       <c r="D132" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="133">
@@ -1990,10 +1990,10 @@
         <v>2022.0</v>
       </c>
       <c r="C133" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D133" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="134">
@@ -2004,7 +2004,7 @@
         <v>2022.0</v>
       </c>
       <c r="C134" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D134" t="n">
         <v>1.0</v>
@@ -2018,10 +2018,10 @@
         <v>2022.0</v>
       </c>
       <c r="C135" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D135" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="136">
@@ -2032,10 +2032,10 @@
         <v>2022.0</v>
       </c>
       <c r="C136" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D136" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="137">
@@ -2046,10 +2046,10 @@
         <v>2022.0</v>
       </c>
       <c r="C137" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D137" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="138">
@@ -2060,7 +2060,7 @@
         <v>2022.0</v>
       </c>
       <c r="C138" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D138" t="n">
         <v>2.0</v>
@@ -2074,7 +2074,7 @@
         <v>2022.0</v>
       </c>
       <c r="C139" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D139" t="n">
         <v>2.0</v>
@@ -2088,10 +2088,10 @@
         <v>2022.0</v>
       </c>
       <c r="C140" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D140" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="141">
@@ -2102,10 +2102,10 @@
         <v>2022.0</v>
       </c>
       <c r="C141" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D141" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="142">
@@ -2116,7 +2116,7 @@
         <v>2022.0</v>
       </c>
       <c r="C142" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D142" t="n">
         <v>3.0</v>
@@ -2130,10 +2130,10 @@
         <v>2022.0</v>
       </c>
       <c r="C143" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D143" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="144">
@@ -2144,10 +2144,10 @@
         <v>2022.0</v>
       </c>
       <c r="C144" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D144" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="145">
@@ -2158,7 +2158,7 @@
         <v>2022.0</v>
       </c>
       <c r="C145" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D145" t="n">
         <v>3.0</v>
@@ -2172,10 +2172,10 @@
         <v>2022.0</v>
       </c>
       <c r="C146" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D146" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="147">
@@ -2186,10 +2186,10 @@
         <v>2022.0</v>
       </c>
       <c r="C147" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D147" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="148">
@@ -2200,10 +2200,10 @@
         <v>2022.0</v>
       </c>
       <c r="C148" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D148" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="149">
@@ -2214,7 +2214,7 @@
         <v>2022.0</v>
       </c>
       <c r="C149" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D149" t="n">
         <v>1.0</v>
@@ -2228,7 +2228,7 @@
         <v>2022.0</v>
       </c>
       <c r="C150" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D150" t="n">
         <v>1.0</v>
@@ -2242,7 +2242,7 @@
         <v>2022.0</v>
       </c>
       <c r="C151" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D151" t="n">
         <v>1.0</v>
@@ -2256,7 +2256,7 @@
         <v>2022.0</v>
       </c>
       <c r="C152" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D152" t="n">
         <v>1.0</v>
@@ -2270,7 +2270,7 @@
         <v>2022.0</v>
       </c>
       <c r="C153" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D153" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>2022.0</v>
       </c>
       <c r="C154" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D154" t="n">
         <v>1.0</v>
@@ -2298,7 +2298,7 @@
         <v>2022.0</v>
       </c>
       <c r="C155" t="n" s="2">
-        <v>44772.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D155" t="n">
         <v>1.0</v>
@@ -2312,7 +2312,7 @@
         <v>2022.0</v>
       </c>
       <c r="C156" t="n" s="2">
-        <v>44793.0</v>
+        <v>44772.0</v>
       </c>
       <c r="D156" t="n">
         <v>1.0</v>
@@ -2326,7 +2326,7 @@
         <v>2022.0</v>
       </c>
       <c r="C157" t="n" s="2">
-        <v>44800.0</v>
+        <v>44793.0</v>
       </c>
       <c r="D157" t="n">
         <v>1.0</v>
@@ -2340,7 +2340,7 @@
         <v>2022.0</v>
       </c>
       <c r="C158" t="n" s="2">
-        <v>44828.0</v>
+        <v>44800.0</v>
       </c>
       <c r="D158" t="n">
         <v>1.0</v>
@@ -2354,7 +2354,7 @@
         <v>2022.0</v>
       </c>
       <c r="C159" t="n" s="2">
-        <v>44849.0</v>
+        <v>44828.0</v>
       </c>
       <c r="D159" t="n">
         <v>1.0</v>
@@ -2368,7 +2368,7 @@
         <v>2022.0</v>
       </c>
       <c r="C160" t="n" s="2">
-        <v>44856.0</v>
+        <v>44849.0</v>
       </c>
       <c r="D160" t="n">
         <v>1.0</v>
@@ -2382,7 +2382,7 @@
         <v>2022.0</v>
       </c>
       <c r="C161" t="n" s="2">
-        <v>44863.0</v>
+        <v>44856.0</v>
       </c>
       <c r="D161" t="n">
         <v>1.0</v>
@@ -2396,10 +2396,10 @@
         <v>2022.0</v>
       </c>
       <c r="C162" t="n" s="2">
-        <v>44884.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D162" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="163">
@@ -2410,10 +2410,10 @@
         <v>2022.0</v>
       </c>
       <c r="C163" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D163" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="164">
@@ -2424,7 +2424,7 @@
         <v>2022.0</v>
       </c>
       <c r="C164" t="n" s="2">
-        <v>44905.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D164" t="n">
         <v>1.0</v>
@@ -2438,7 +2438,7 @@
         <v>2022.0</v>
       </c>
       <c r="C165" t="n" s="2">
-        <v>44912.0</v>
+        <v>44905.0</v>
       </c>
       <c r="D165" t="n">
         <v>1.0</v>
@@ -2452,10 +2452,10 @@
         <v>2022.0</v>
       </c>
       <c r="C166" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D166" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="167">
@@ -2463,13 +2463,13 @@
         <v>5</v>
       </c>
       <c r="B167" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C167" t="n" s="2">
-        <v>44934.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D167" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="168">
@@ -2480,10 +2480,10 @@
         <v>2023.0</v>
       </c>
       <c r="C168" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="169">
@@ -2494,10 +2494,10 @@
         <v>2023.0</v>
       </c>
       <c r="C169" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D169" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="170">
@@ -2508,10 +2508,10 @@
         <v>2023.0</v>
       </c>
       <c r="C170" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D170" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="171">
@@ -2522,10 +2522,10 @@
         <v>2023.0</v>
       </c>
       <c r="C171" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D171" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="172">
@@ -2536,7 +2536,7 @@
         <v>2023.0</v>
       </c>
       <c r="C172" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D172" t="n">
         <v>4.0</v>
@@ -2550,10 +2550,10 @@
         <v>2023.0</v>
       </c>
       <c r="C173" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D173" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="174">
@@ -2564,10 +2564,10 @@
         <v>2023.0</v>
       </c>
       <c r="C174" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D174" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="175">
@@ -2578,10 +2578,10 @@
         <v>2023.0</v>
       </c>
       <c r="C175" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D175" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="176">
@@ -2592,10 +2592,10 @@
         <v>2023.0</v>
       </c>
       <c r="C176" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D176" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="177">
@@ -2606,10 +2606,10 @@
         <v>2023.0</v>
       </c>
       <c r="C177" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D177" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="178">
@@ -2620,10 +2620,10 @@
         <v>2023.0</v>
       </c>
       <c r="C178" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D178" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="179">
@@ -2634,10 +2634,10 @@
         <v>2023.0</v>
       </c>
       <c r="C179" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D179" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="180">
@@ -2648,10 +2648,10 @@
         <v>2023.0</v>
       </c>
       <c r="C180" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D180" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="181">
@@ -2662,10 +2662,10 @@
         <v>2023.0</v>
       </c>
       <c r="C181" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D181" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="182">
@@ -2676,10 +2676,10 @@
         <v>2023.0</v>
       </c>
       <c r="C182" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D182" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="183">
@@ -2690,10 +2690,10 @@
         <v>2023.0</v>
       </c>
       <c r="C183" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D183" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="184">
@@ -2704,10 +2704,10 @@
         <v>2023.0</v>
       </c>
       <c r="C184" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D184" t="n">
-        <v>16.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="185">
@@ -2718,10 +2718,10 @@
         <v>2023.0</v>
       </c>
       <c r="C185" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D185" t="n">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="186">
@@ -2732,10 +2732,10 @@
         <v>2023.0</v>
       </c>
       <c r="C186" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D186" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="187">
@@ -2746,10 +2746,10 @@
         <v>2023.0</v>
       </c>
       <c r="C187" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D187" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="188">
@@ -2760,10 +2760,10 @@
         <v>2023.0</v>
       </c>
       <c r="C188" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D188" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="189">
@@ -2774,10 +2774,10 @@
         <v>2023.0</v>
       </c>
       <c r="C189" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D189" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="190">
@@ -2788,10 +2788,10 @@
         <v>2023.0</v>
       </c>
       <c r="C190" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D190" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="191">
@@ -2802,10 +2802,10 @@
         <v>2023.0</v>
       </c>
       <c r="C191" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D191" t="n">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="192">
@@ -2816,10 +2816,10 @@
         <v>2023.0</v>
       </c>
       <c r="C192" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D192" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="193">
@@ -2830,10 +2830,10 @@
         <v>2023.0</v>
       </c>
       <c r="C193" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D193" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="194">
@@ -2844,10 +2844,10 @@
         <v>2023.0</v>
       </c>
       <c r="C194" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D194" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="195">
@@ -2858,10 +2858,10 @@
         <v>2023.0</v>
       </c>
       <c r="C195" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D195" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="196">
@@ -2872,10 +2872,10 @@
         <v>2023.0</v>
       </c>
       <c r="C196" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D196" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="197">
@@ -2886,10 +2886,10 @@
         <v>2023.0</v>
       </c>
       <c r="C197" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D197" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="198">
@@ -2900,7 +2900,7 @@
         <v>2023.0</v>
       </c>
       <c r="C198" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D198" t="n">
         <v>2.0</v>
@@ -2914,10 +2914,10 @@
         <v>2023.0</v>
       </c>
       <c r="C199" t="n" s="2">
-        <v>45158.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D199" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="200">
@@ -2928,7 +2928,7 @@
         <v>2023.0</v>
       </c>
       <c r="C200" t="n" s="2">
-        <v>45165.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D200" t="n">
         <v>5.0</v>
@@ -2942,10 +2942,10 @@
         <v>2023.0</v>
       </c>
       <c r="C201" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D201" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="202">
@@ -2956,10 +2956,10 @@
         <v>2023.0</v>
       </c>
       <c r="C202" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D202" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="203">
@@ -2970,10 +2970,10 @@
         <v>2023.0</v>
       </c>
       <c r="C203" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D203" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="204">
@@ -2984,7 +2984,7 @@
         <v>2023.0</v>
       </c>
       <c r="C204" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D204" t="n">
         <v>1.0</v>
@@ -2998,10 +2998,10 @@
         <v>2023.0</v>
       </c>
       <c r="C205" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D205" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="206">
@@ -3012,10 +3012,10 @@
         <v>2023.0</v>
       </c>
       <c r="C206" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D206" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="207">
@@ -3026,10 +3026,10 @@
         <v>2023.0</v>
       </c>
       <c r="C207" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D207" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="208">
@@ -3040,7 +3040,7 @@
         <v>2023.0</v>
       </c>
       <c r="C208" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D208" t="n">
         <v>8.0</v>
@@ -3054,10 +3054,10 @@
         <v>2023.0</v>
       </c>
       <c r="C209" t="n" s="2">
-        <v>45228.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D209" t="n">
-        <v>17.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="210">
@@ -3068,10 +3068,10 @@
         <v>2023.0</v>
       </c>
       <c r="C210" t="n" s="2">
-        <v>45235.0</v>
+        <v>45228.0</v>
       </c>
       <c r="D210" t="n">
-        <v>9.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="211">
@@ -3082,7 +3082,7 @@
         <v>2023.0</v>
       </c>
       <c r="C211" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D211" t="n">
         <v>9.0</v>
@@ -3096,10 +3096,10 @@
         <v>2023.0</v>
       </c>
       <c r="C212" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D212" t="n">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="213">
@@ -3110,10 +3110,10 @@
         <v>2023.0</v>
       </c>
       <c r="C213" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D213" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="214">
@@ -3124,10 +3124,10 @@
         <v>2023.0</v>
       </c>
       <c r="C214" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D214" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="215">
@@ -3138,10 +3138,10 @@
         <v>2023.0</v>
       </c>
       <c r="C215" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D215" t="n">
-        <v>26.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="216">
@@ -3152,10 +3152,10 @@
         <v>2023.0</v>
       </c>
       <c r="C216" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D216" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="217">
@@ -3166,10 +3166,10 @@
         <v>2023.0</v>
       </c>
       <c r="C217" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D217" t="n">
-        <v>21.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="218">
@@ -3180,10 +3180,10 @@
         <v>2023.0</v>
       </c>
       <c r="C218" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D218" t="n">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="219">
@@ -3191,13 +3191,13 @@
         <v>5</v>
       </c>
       <c r="B219" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C219" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D219" t="n">
-        <v>26.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="220">
@@ -3208,10 +3208,10 @@
         <v>2024.0</v>
       </c>
       <c r="C220" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D220" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="221">
@@ -3222,10 +3222,10 @@
         <v>2024.0</v>
       </c>
       <c r="C221" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D221" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="222">
@@ -3236,10 +3236,10 @@
         <v>2024.0</v>
       </c>
       <c r="C222" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D222" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="223">
@@ -3250,10 +3250,10 @@
         <v>2024.0</v>
       </c>
       <c r="C223" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D223" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="224">
@@ -3264,10 +3264,10 @@
         <v>2024.0</v>
       </c>
       <c r="C224" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D224" t="n">
-        <v>13.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="225">
@@ -3278,10 +3278,10 @@
         <v>2024.0</v>
       </c>
       <c r="C225" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D225" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="226">
@@ -3292,10 +3292,10 @@
         <v>2024.0</v>
       </c>
       <c r="C226" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D226" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="227">
@@ -3306,10 +3306,10 @@
         <v>2024.0</v>
       </c>
       <c r="C227" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D227" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="228">
@@ -3320,10 +3320,10 @@
         <v>2024.0</v>
       </c>
       <c r="C228" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D228" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="229">
@@ -3334,10 +3334,10 @@
         <v>2024.0</v>
       </c>
       <c r="C229" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D229" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="230">
@@ -3348,10 +3348,10 @@
         <v>2024.0</v>
       </c>
       <c r="C230" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D230" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="231">
@@ -3362,10 +3362,10 @@
         <v>2024.0</v>
       </c>
       <c r="C231" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D231" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="232">
@@ -3376,10 +3376,10 @@
         <v>2024.0</v>
       </c>
       <c r="C232" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D232" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="233">
@@ -3390,10 +3390,10 @@
         <v>2024.0</v>
       </c>
       <c r="C233" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D233" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="234">
@@ -3404,10 +3404,10 @@
         <v>2024.0</v>
       </c>
       <c r="C234" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D234" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="235">
@@ -3418,10 +3418,10 @@
         <v>2024.0</v>
       </c>
       <c r="C235" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D235" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="236">
@@ -3432,10 +3432,10 @@
         <v>2024.0</v>
       </c>
       <c r="C236" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D236" t="n">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="237">
@@ -3446,10 +3446,10 @@
         <v>2024.0</v>
       </c>
       <c r="C237" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D237" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="238">
@@ -3460,10 +3460,10 @@
         <v>2024.0</v>
       </c>
       <c r="C238" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D238" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="239">
@@ -3474,10 +3474,10 @@
         <v>2024.0</v>
       </c>
       <c r="C239" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D239" t="n">
-        <v>30.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="240">
@@ -3488,10 +3488,10 @@
         <v>2024.0</v>
       </c>
       <c r="C240" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D240" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="241">
@@ -3502,10 +3502,10 @@
         <v>2024.0</v>
       </c>
       <c r="C241" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D241" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="242">
@@ -3516,10 +3516,10 @@
         <v>2024.0</v>
       </c>
       <c r="C242" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D242" t="n">
-        <v>26.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="243">
@@ -3530,10 +3530,10 @@
         <v>2024.0</v>
       </c>
       <c r="C243" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D243" t="n">
-        <v>8.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="244">
@@ -3544,10 +3544,10 @@
         <v>2024.0</v>
       </c>
       <c r="C244" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D244" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="245">
@@ -3558,7 +3558,7 @@
         <v>2024.0</v>
       </c>
       <c r="C245" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D245" t="n">
         <v>12.0</v>
@@ -3572,10 +3572,10 @@
         <v>2024.0</v>
       </c>
       <c r="C246" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D246" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="247">
@@ -3586,10 +3586,10 @@
         <v>2024.0</v>
       </c>
       <c r="C247" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D247" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="248">
@@ -3600,10 +3600,10 @@
         <v>2024.0</v>
       </c>
       <c r="C248" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D248" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="249">
@@ -3614,10 +3614,10 @@
         <v>2024.0</v>
       </c>
       <c r="C249" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D249" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="250">
@@ -3628,10 +3628,10 @@
         <v>2024.0</v>
       </c>
       <c r="C250" t="n" s="2">
-        <v>45516.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D250" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="251">
@@ -3642,7 +3642,7 @@
         <v>2024.0</v>
       </c>
       <c r="C251" t="n" s="2">
-        <v>45523.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D251" t="n">
         <v>4.0</v>
@@ -3656,7 +3656,7 @@
         <v>2024.0</v>
       </c>
       <c r="C252" t="n" s="2">
-        <v>45530.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D252" t="n">
         <v>4.0</v>
@@ -3670,7 +3670,7 @@
         <v>2024.0</v>
       </c>
       <c r="C253" t="n" s="2">
-        <v>45537.0</v>
+        <v>45530.0</v>
       </c>
       <c r="D253" t="n">
         <v>4.0</v>
@@ -3684,10 +3684,10 @@
         <v>2024.0</v>
       </c>
       <c r="C254" t="n" s="2">
-        <v>45544.0</v>
+        <v>45537.0</v>
       </c>
       <c r="D254" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="255">
@@ -3698,10 +3698,10 @@
         <v>2024.0</v>
       </c>
       <c r="C255" t="n" s="2">
-        <v>45551.0</v>
+        <v>45544.0</v>
       </c>
       <c r="D255" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="256">
@@ -3712,10 +3712,10 @@
         <v>2024.0</v>
       </c>
       <c r="C256" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D256" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="257">
@@ -3726,10 +3726,10 @@
         <v>2024.0</v>
       </c>
       <c r="C257" t="n" s="2">
-        <v>45600.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D257" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="258">
@@ -3740,10 +3740,10 @@
         <v>2024.0</v>
       </c>
       <c r="C258" t="n" s="2">
-        <v>45607.0</v>
+        <v>45600.0</v>
       </c>
       <c r="D258" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="259">
@@ -3754,10 +3754,10 @@
         <v>2024.0</v>
       </c>
       <c r="C259" t="n" s="2">
-        <v>45628.0</v>
+        <v>45607.0</v>
       </c>
       <c r="D259" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="260">
@@ -3768,10 +3768,10 @@
         <v>2024.0</v>
       </c>
       <c r="C260" t="n" s="2">
-        <v>45635.0</v>
+        <v>45628.0</v>
       </c>
       <c r="D260" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="261">
@@ -3782,7 +3782,7 @@
         <v>2024.0</v>
       </c>
       <c r="C261" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D261" t="n">
         <v>3.0</v>
@@ -3796,10 +3796,10 @@
         <v>2024.0</v>
       </c>
       <c r="C262" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D262" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="263">
@@ -3810,7 +3810,7 @@
         <v>2024.0</v>
       </c>
       <c r="C263" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D263" t="n">
         <v>1.0</v>
@@ -3821,13 +3821,13 @@
         <v>5</v>
       </c>
       <c r="B264" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C264" t="n" s="2">
-        <v>45672.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D264" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="265">
@@ -3838,10 +3838,10 @@
         <v>2025.0</v>
       </c>
       <c r="C265" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D265" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="266">
@@ -3852,7 +3852,7 @@
         <v>2025.0</v>
       </c>
       <c r="C266" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D266" t="n">
         <v>1.0</v>
@@ -3866,10 +3866,10 @@
         <v>2025.0</v>
       </c>
       <c r="C267" t="n" s="2">
-        <v>45721.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D267" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="268">
@@ -3880,10 +3880,10 @@
         <v>2025.0</v>
       </c>
       <c r="C268" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D268" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="269">
@@ -3894,10 +3894,10 @@
         <v>2025.0</v>
       </c>
       <c r="C269" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D269" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="270">
@@ -3908,10 +3908,10 @@
         <v>2025.0</v>
       </c>
       <c r="C270" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D270" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="271">
@@ -3922,10 +3922,10 @@
         <v>2025.0</v>
       </c>
       <c r="C271" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D271" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="272">
@@ -3936,10 +3936,10 @@
         <v>2025.0</v>
       </c>
       <c r="C272" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D272" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="273">
@@ -3950,10 +3950,10 @@
         <v>2025.0</v>
       </c>
       <c r="C273" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D273" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="274">
@@ -3964,10 +3964,10 @@
         <v>2025.0</v>
       </c>
       <c r="C274" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D274" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="275">
@@ -3978,10 +3978,10 @@
         <v>2025.0</v>
       </c>
       <c r="C275" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D275" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="276">
@@ -3992,10 +3992,10 @@
         <v>2025.0</v>
       </c>
       <c r="C276" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D276" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="277">
@@ -4006,10 +4006,10 @@
         <v>2025.0</v>
       </c>
       <c r="C277" t="n" s="2">
-        <v>45798.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D277" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="278">
@@ -4020,10 +4020,10 @@
         <v>2025.0</v>
       </c>
       <c r="C278" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D278" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="279">
@@ -4034,10 +4034,10 @@
         <v>2025.0</v>
       </c>
       <c r="C279" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D279" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="280">
@@ -4048,10 +4048,10 @@
         <v>2025.0</v>
       </c>
       <c r="C280" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D280" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="281">
@@ -4062,10 +4062,10 @@
         <v>2025.0</v>
       </c>
       <c r="C281" t="n" s="2">
-        <v>45826.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D281" t="n">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="282">
@@ -4076,10 +4076,10 @@
         <v>2025.0</v>
       </c>
       <c r="C282" t="n" s="2">
-        <v>45833.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D282" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="283">
@@ -4090,10 +4090,10 @@
         <v>2025.0</v>
       </c>
       <c r="C283" t="n" s="2">
-        <v>45840.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D283" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="284">
@@ -4104,7 +4104,7 @@
         <v>2025.0</v>
       </c>
       <c r="C284" t="n" s="2">
-        <v>45847.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D284" t="n">
         <v>4.0</v>
@@ -4118,10 +4118,10 @@
         <v>2025.0</v>
       </c>
       <c r="C285" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D285" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="286">
@@ -4132,10 +4132,10 @@
         <v>2025.0</v>
       </c>
       <c r="C286" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D286" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="287">
@@ -4146,10 +4146,10 @@
         <v>2025.0</v>
       </c>
       <c r="C287" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D287" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="288">
@@ -4160,10 +4160,10 @@
         <v>2025.0</v>
       </c>
       <c r="C288" t="n" s="2">
-        <v>45882.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D288" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="289">
@@ -4174,7 +4174,7 @@
         <v>2025.0</v>
       </c>
       <c r="C289" t="n" s="2">
-        <v>45889.0</v>
+        <v>45882.0</v>
       </c>
       <c r="D289" t="n">
         <v>1.0</v>
@@ -4188,10 +4188,10 @@
         <v>2025.0</v>
       </c>
       <c r="C290" t="n" s="2">
-        <v>45896.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D290" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="291">
@@ -4202,7 +4202,7 @@
         <v>2025.0</v>
       </c>
       <c r="C291" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D291" t="n">
         <v>3.0</v>
@@ -4216,10 +4216,10 @@
         <v>2025.0</v>
       </c>
       <c r="C292" t="n" s="2">
-        <v>45910.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D292" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="293">
@@ -4230,7 +4230,7 @@
         <v>2025.0</v>
       </c>
       <c r="C293" t="n" s="2">
-        <v>45973.0</v>
+        <v>45910.0</v>
       </c>
       <c r="D293" t="n">
         <v>1.0</v>
@@ -4244,10 +4244,10 @@
         <v>2025.0</v>
       </c>
       <c r="C294" t="n" s="2">
-        <v>45987.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D294" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="295">
@@ -4258,10 +4258,10 @@
         <v>2025.0</v>
       </c>
       <c r="C295" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D295" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="296">
@@ -4272,10 +4272,10 @@
         <v>2025.0</v>
       </c>
       <c r="C296" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D296" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="297">
@@ -4286,10 +4286,10 @@
         <v>2025.0</v>
       </c>
       <c r="C297" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D297" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="298">
@@ -4300,10 +4300,10 @@
         <v>2025.0</v>
       </c>
       <c r="C298" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D298" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="299">
@@ -4314,10 +4314,10 @@
         <v>2025.0</v>
       </c>
       <c r="C299" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D299" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="300">
@@ -4325,13 +4325,13 @@
         <v>5</v>
       </c>
       <c r="B300" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C300" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D300" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="301">
@@ -4342,10 +4342,10 @@
         <v>2026.0</v>
       </c>
       <c r="C301" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D301" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="302">
@@ -4356,10 +4356,10 @@
         <v>2026.0</v>
       </c>
       <c r="C302" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D302" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="303">
@@ -4370,10 +4370,10 @@
         <v>2026.0</v>
       </c>
       <c r="C303" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D303" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="304">
@@ -4384,10 +4384,10 @@
         <v>2026.0</v>
       </c>
       <c r="C304" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D304" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="305">
@@ -4398,10 +4398,10 @@
         <v>2026.0</v>
       </c>
       <c r="C305" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D305" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="306">
@@ -4412,10 +4412,10 @@
         <v>2026.0</v>
       </c>
       <c r="C306" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D306" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="307">
@@ -4426,7 +4426,7 @@
         <v>2026.0</v>
       </c>
       <c r="C307" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D307" t="n">
         <v>5.0</v>
@@ -4440,10 +4440,10 @@
         <v>2026.0</v>
       </c>
       <c r="C308" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D308" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="309">
@@ -4454,7 +4454,7 @@
         <v>2026.0</v>
       </c>
       <c r="C309" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D309" t="n">
         <v>2.0</v>
@@ -4468,10 +4468,10 @@
         <v>2026.0</v>
       </c>
       <c r="C310" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D310" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="311">
@@ -4482,10 +4482,10 @@
         <v>2026.0</v>
       </c>
       <c r="C311" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D311" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="312">
@@ -4496,10 +4496,10 @@
         <v>2026.0</v>
       </c>
       <c r="C312" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D312" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="313">
@@ -4510,10 +4510,10 @@
         <v>2026.0</v>
       </c>
       <c r="C313" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D313" t="n">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="314">
@@ -4524,10 +4524,10 @@
         <v>2026.0</v>
       </c>
       <c r="C314" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D314" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="315">
@@ -4538,7 +4538,7 @@
         <v>2026.0</v>
       </c>
       <c r="C315" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D315" t="n">
         <v>4.0</v>
@@ -4552,10 +4552,10 @@
         <v>2026.0</v>
       </c>
       <c r="C316" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D316" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="317">
@@ -4566,10 +4566,10 @@
         <v>2026.0</v>
       </c>
       <c r="C317" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D317" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="318">
@@ -4580,10 +4580,10 @@
         <v>2026.0</v>
       </c>
       <c r="C318" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D318" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="319">
@@ -4594,10 +4594,10 @@
         <v>2026.0</v>
       </c>
       <c r="C319" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D319" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="320">
@@ -4608,10 +4608,10 @@
         <v>2026.0</v>
       </c>
       <c r="C320" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D320" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="321">
@@ -4622,10 +4622,10 @@
         <v>2026.0</v>
       </c>
       <c r="C321" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D321" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="322">
@@ -4636,10 +4636,10 @@
         <v>2026.0</v>
       </c>
       <c r="C322" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D322" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="323">
@@ -4650,10 +4650,10 @@
         <v>2026.0</v>
       </c>
       <c r="C323" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D323" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="324">
@@ -4664,10 +4664,10 @@
         <v>2026.0</v>
       </c>
       <c r="C324" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D324" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="325">
@@ -4678,10 +4678,10 @@
         <v>2026.0</v>
       </c>
       <c r="C325" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D325" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="326">
@@ -4692,10 +4692,10 @@
         <v>2026.0</v>
       </c>
       <c r="C326" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D326" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="327">
@@ -4706,10 +4706,10 @@
         <v>2026.0</v>
       </c>
       <c r="C327" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D327" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="328">
@@ -4720,10 +4720,10 @@
         <v>2026.0</v>
       </c>
       <c r="C328" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D328" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="329">
@@ -4734,10 +4734,10 @@
         <v>2026.0</v>
       </c>
       <c r="C329" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D329" t="n">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="330">
@@ -4748,10 +4748,10 @@
         <v>2026.0</v>
       </c>
       <c r="C330" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D330" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="331">
@@ -4762,10 +4762,10 @@
         <v>2026.0</v>
       </c>
       <c r="C331" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D331" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         <v>2026.0</v>
       </c>
       <c r="C332" t="n" s="2">
-        <v>46282.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D332" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="333">
@@ -4790,10 +4790,10 @@
         <v>2026.0</v>
       </c>
       <c r="C333" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D333" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="334">
@@ -4804,10 +4804,10 @@
         <v>2026.0</v>
       </c>
       <c r="C334" t="n" s="2">
-        <v>46310.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D334" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="335">
@@ -4818,21 +4818,21 @@
         <v>2026.0</v>
       </c>
       <c r="C335" t="n" s="2">
-        <v>46317.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D335" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B336" t="n">
-        <v>2023.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C336" t="n" s="2">
-        <v>45095.0</v>
+        <v>46317.0</v>
       </c>
       <c r="D336" t="n">
         <v>1.0</v>
@@ -4846,7 +4846,7 @@
         <v>2023.0</v>
       </c>
       <c r="C337" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D337" t="n">
         <v>1.0</v>
@@ -4860,7 +4860,7 @@
         <v>2023.0</v>
       </c>
       <c r="C338" t="n" s="2">
-        <v>45158.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D338" t="n">
         <v>1.0</v>
@@ -4874,10 +4874,10 @@
         <v>2023.0</v>
       </c>
       <c r="C339" t="n" s="2">
-        <v>45207.0</v>
+        <v>45158.0</v>
       </c>
       <c r="D339" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="340">
@@ -4888,7 +4888,7 @@
         <v>2023.0</v>
       </c>
       <c r="C340" t="n" s="2">
-        <v>45214.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D340" t="n">
         <v>3.0</v>
@@ -4902,10 +4902,10 @@
         <v>2023.0</v>
       </c>
       <c r="C341" t="n" s="2">
-        <v>45221.0</v>
+        <v>45214.0</v>
       </c>
       <c r="D341" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="342">
@@ -4916,7 +4916,7 @@
         <v>2023.0</v>
       </c>
       <c r="C342" t="n" s="2">
-        <v>45249.0</v>
+        <v>45221.0</v>
       </c>
       <c r="D342" t="n">
         <v>1.0</v>
@@ -4930,10 +4930,10 @@
         <v>2023.0</v>
       </c>
       <c r="C343" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D343" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="344">
@@ -4944,10 +4944,10 @@
         <v>2023.0</v>
       </c>
       <c r="C344" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D344" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="345">
@@ -4958,10 +4958,10 @@
         <v>2023.0</v>
       </c>
       <c r="C345" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D345" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="346">
@@ -4972,10 +4972,10 @@
         <v>2023.0</v>
       </c>
       <c r="C346" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D346" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="347">
@@ -4986,10 +4986,10 @@
         <v>2023.0</v>
       </c>
       <c r="C347" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D347" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="348">
@@ -5000,10 +5000,10 @@
         <v>2023.0</v>
       </c>
       <c r="C348" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D348" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="349">
@@ -5011,13 +5011,13 @@
         <v>6</v>
       </c>
       <c r="B349" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C349" t="n" s="2">
-        <v>45306.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D349" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="350">
@@ -5028,10 +5028,10 @@
         <v>2024.0</v>
       </c>
       <c r="C350" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D350" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="351">
@@ -5042,10 +5042,10 @@
         <v>2024.0</v>
       </c>
       <c r="C351" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D351" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="352">
@@ -5056,10 +5056,10 @@
         <v>2024.0</v>
       </c>
       <c r="C352" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D352" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="353">
@@ -5070,10 +5070,10 @@
         <v>2024.0</v>
       </c>
       <c r="C353" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D353" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="354">
@@ -5084,10 +5084,10 @@
         <v>2024.0</v>
       </c>
       <c r="C354" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D354" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="355">
@@ -5098,7 +5098,7 @@
         <v>2024.0</v>
       </c>
       <c r="C355" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D355" t="n">
         <v>12.0</v>
@@ -5112,10 +5112,10 @@
         <v>2024.0</v>
       </c>
       <c r="C356" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D356" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="357">
@@ -5126,10 +5126,10 @@
         <v>2024.0</v>
       </c>
       <c r="C357" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D357" t="n">
-        <v>12.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="358">
@@ -5140,10 +5140,10 @@
         <v>2024.0</v>
       </c>
       <c r="C358" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D358" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="359">
@@ -5154,10 +5154,10 @@
         <v>2024.0</v>
       </c>
       <c r="C359" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D359" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="360">
@@ -5168,10 +5168,10 @@
         <v>2024.0</v>
       </c>
       <c r="C360" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D360" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="361">
@@ -5182,10 +5182,10 @@
         <v>2024.0</v>
       </c>
       <c r="C361" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D361" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="362">
@@ -5196,10 +5196,10 @@
         <v>2024.0</v>
       </c>
       <c r="C362" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D362" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="363">
@@ -5210,10 +5210,10 @@
         <v>2024.0</v>
       </c>
       <c r="C363" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D363" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="364">
@@ -5224,10 +5224,10 @@
         <v>2024.0</v>
       </c>
       <c r="C364" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D364" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="365">
@@ -5238,10 +5238,10 @@
         <v>2024.0</v>
       </c>
       <c r="C365" t="n" s="2">
-        <v>45418.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D365" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="366">
@@ -5252,10 +5252,10 @@
         <v>2024.0</v>
       </c>
       <c r="C366" t="n" s="2">
-        <v>45425.0</v>
+        <v>45418.0</v>
       </c>
       <c r="D366" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="367">
@@ -5266,10 +5266,10 @@
         <v>2024.0</v>
       </c>
       <c r="C367" t="n" s="2">
-        <v>45432.0</v>
+        <v>45425.0</v>
       </c>
       <c r="D367" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="368">
@@ -5280,7 +5280,7 @@
         <v>2024.0</v>
       </c>
       <c r="C368" t="n" s="2">
-        <v>45439.0</v>
+        <v>45432.0</v>
       </c>
       <c r="D368" t="n">
         <v>6.0</v>
@@ -5294,10 +5294,10 @@
         <v>2024.0</v>
       </c>
       <c r="C369" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D369" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="370">
@@ -5308,10 +5308,10 @@
         <v>2024.0</v>
       </c>
       <c r="C370" t="n" s="2">
-        <v>45453.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D370" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="371">
@@ -5322,7 +5322,7 @@
         <v>2024.0</v>
       </c>
       <c r="C371" t="n" s="2">
-        <v>45460.0</v>
+        <v>45453.0</v>
       </c>
       <c r="D371" t="n">
         <v>4.0</v>
@@ -5336,7 +5336,7 @@
         <v>2024.0</v>
       </c>
       <c r="C372" t="n" s="2">
-        <v>45467.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D372" t="n">
         <v>4.0</v>
@@ -5350,10 +5350,10 @@
         <v>2024.0</v>
       </c>
       <c r="C373" t="n" s="2">
-        <v>45474.0</v>
+        <v>45467.0</v>
       </c>
       <c r="D373" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="374">
@@ -5364,10 +5364,10 @@
         <v>2024.0</v>
       </c>
       <c r="C374" t="n" s="2">
-        <v>45481.0</v>
+        <v>45474.0</v>
       </c>
       <c r="D374" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="375">
@@ -5378,10 +5378,10 @@
         <v>2024.0</v>
       </c>
       <c r="C375" t="n" s="2">
-        <v>45488.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D375" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="376">
@@ -5392,10 +5392,10 @@
         <v>2024.0</v>
       </c>
       <c r="C376" t="n" s="2">
-        <v>45495.0</v>
+        <v>45488.0</v>
       </c>
       <c r="D376" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="377">
@@ -5406,10 +5406,10 @@
         <v>2024.0</v>
       </c>
       <c r="C377" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D377" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="378">
@@ -5420,10 +5420,10 @@
         <v>2024.0</v>
       </c>
       <c r="C378" t="n" s="2">
-        <v>45509.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D378" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="379">
@@ -5434,7 +5434,7 @@
         <v>2024.0</v>
       </c>
       <c r="C379" t="n" s="2">
-        <v>45523.0</v>
+        <v>45509.0</v>
       </c>
       <c r="D379" t="n">
         <v>1.0</v>
@@ -5448,7 +5448,7 @@
         <v>2024.0</v>
       </c>
       <c r="C380" t="n" s="2">
-        <v>45551.0</v>
+        <v>45523.0</v>
       </c>
       <c r="D380" t="n">
         <v>1.0</v>
@@ -5462,7 +5462,7 @@
         <v>2024.0</v>
       </c>
       <c r="C381" t="n" s="2">
-        <v>45558.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D381" t="n">
         <v>1.0</v>
@@ -5476,10 +5476,10 @@
         <v>2024.0</v>
       </c>
       <c r="C382" t="n" s="2">
-        <v>45572.0</v>
+        <v>45558.0</v>
       </c>
       <c r="D382" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="383">
@@ -5490,10 +5490,10 @@
         <v>2024.0</v>
       </c>
       <c r="C383" t="n" s="2">
-        <v>45593.0</v>
+        <v>45572.0</v>
       </c>
       <c r="D383" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="384">
@@ -5504,10 +5504,10 @@
         <v>2024.0</v>
       </c>
       <c r="C384" t="n" s="2">
-        <v>45614.0</v>
+        <v>45593.0</v>
       </c>
       <c r="D384" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="385">
@@ -5518,10 +5518,10 @@
         <v>2024.0</v>
       </c>
       <c r="C385" t="n" s="2">
-        <v>45621.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D385" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="386">
@@ -5532,7 +5532,7 @@
         <v>2024.0</v>
       </c>
       <c r="C386" t="n" s="2">
-        <v>45635.0</v>
+        <v>45621.0</v>
       </c>
       <c r="D386" t="n">
         <v>1.0</v>
@@ -5546,7 +5546,7 @@
         <v>2024.0</v>
       </c>
       <c r="C387" t="n" s="2">
-        <v>45649.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D387" t="n">
         <v>1.0</v>
@@ -5557,13 +5557,13 @@
         <v>6</v>
       </c>
       <c r="B388" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C388" t="n" s="2">
-        <v>45665.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D388" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="389">
@@ -5574,10 +5574,10 @@
         <v>2025.0</v>
       </c>
       <c r="C389" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D389" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="390">
@@ -5588,10 +5588,10 @@
         <v>2025.0</v>
       </c>
       <c r="C390" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D390" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="391">
@@ -5602,10 +5602,10 @@
         <v>2025.0</v>
       </c>
       <c r="C391" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D391" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="392">
@@ -5616,10 +5616,10 @@
         <v>2025.0</v>
       </c>
       <c r="C392" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D392" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="393">
@@ -5630,10 +5630,10 @@
         <v>2025.0</v>
       </c>
       <c r="C393" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D393" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="394">
@@ -5644,10 +5644,10 @@
         <v>2025.0</v>
       </c>
       <c r="C394" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D394" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="395">
@@ -5658,10 +5658,10 @@
         <v>2025.0</v>
       </c>
       <c r="C395" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D395" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="396">
@@ -5672,10 +5672,10 @@
         <v>2025.0</v>
       </c>
       <c r="C396" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D396" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="397">
@@ -5686,10 +5686,10 @@
         <v>2025.0</v>
       </c>
       <c r="C397" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D397" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="398">
@@ -5700,10 +5700,10 @@
         <v>2025.0</v>
       </c>
       <c r="C398" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D398" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="399">
@@ -5714,10 +5714,10 @@
         <v>2025.0</v>
       </c>
       <c r="C399" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D399" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="400">
@@ -5728,10 +5728,10 @@
         <v>2025.0</v>
       </c>
       <c r="C400" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D400" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="401">
@@ -5742,10 +5742,10 @@
         <v>2025.0</v>
       </c>
       <c r="C401" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D401" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="402">
@@ -5756,10 +5756,10 @@
         <v>2025.0</v>
       </c>
       <c r="C402" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D402" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="403">
@@ -5770,7 +5770,7 @@
         <v>2025.0</v>
       </c>
       <c r="C403" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D403" t="n">
         <v>4.0</v>
@@ -5784,10 +5784,10 @@
         <v>2025.0</v>
       </c>
       <c r="C404" t="n" s="2">
-        <v>45777.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D404" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="405">
@@ -5798,7 +5798,7 @@
         <v>2025.0</v>
       </c>
       <c r="C405" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D405" t="n">
         <v>1.0</v>
@@ -5812,7 +5812,7 @@
         <v>2025.0</v>
       </c>
       <c r="C406" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D406" t="n">
         <v>1.0</v>
@@ -5826,7 +5826,7 @@
         <v>2025.0</v>
       </c>
       <c r="C407" t="n" s="2">
-        <v>45840.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D407" t="n">
         <v>1.0</v>
@@ -5840,7 +5840,7 @@
         <v>2025.0</v>
       </c>
       <c r="C408" t="n" s="2">
-        <v>46001.0</v>
+        <v>45840.0</v>
       </c>
       <c r="D408" t="n">
         <v>1.0</v>
@@ -5851,10 +5851,10 @@
         <v>6</v>
       </c>
       <c r="B409" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C409" t="n" s="2">
-        <v>46037.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D409" t="n">
         <v>1.0</v>
@@ -5868,7 +5868,7 @@
         <v>2026.0</v>
       </c>
       <c r="C410" t="n" s="2">
-        <v>46212.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D410" t="n">
         <v>1.0</v>
@@ -5876,13 +5876,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B411" t="n">
-        <v>2021.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C411" t="n" s="2">
-        <v>44561.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D411" t="n">
         <v>1.0</v>
@@ -5893,10 +5893,10 @@
         <v>7</v>
       </c>
       <c r="B412" t="n">
-        <v>2022.0</v>
+        <v>2021.0</v>
       </c>
       <c r="C412" t="n" s="2">
-        <v>44569.0</v>
+        <v>44561.0</v>
       </c>
       <c r="D412" t="n">
         <v>1.0</v>
@@ -5910,10 +5910,10 @@
         <v>2022.0</v>
       </c>
       <c r="C413" t="n" s="2">
-        <v>44576.0</v>
+        <v>44569.0</v>
       </c>
       <c r="D413" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="414">
@@ -5924,10 +5924,10 @@
         <v>2022.0</v>
       </c>
       <c r="C414" t="n" s="2">
-        <v>44583.0</v>
+        <v>44576.0</v>
       </c>
       <c r="D414" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="415">
@@ -5938,10 +5938,10 @@
         <v>2022.0</v>
       </c>
       <c r="C415" t="n" s="2">
-        <v>44590.0</v>
+        <v>44583.0</v>
       </c>
       <c r="D415" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="416">
@@ -5952,10 +5952,10 @@
         <v>2022.0</v>
       </c>
       <c r="C416" t="n" s="2">
-        <v>44604.0</v>
+        <v>44590.0</v>
       </c>
       <c r="D416" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="417">
@@ -5966,7 +5966,7 @@
         <v>2022.0</v>
       </c>
       <c r="C417" t="n" s="2">
-        <v>44611.0</v>
+        <v>44604.0</v>
       </c>
       <c r="D417" t="n">
         <v>3.0</v>
@@ -5980,10 +5980,10 @@
         <v>2022.0</v>
       </c>
       <c r="C418" t="n" s="2">
-        <v>44618.0</v>
+        <v>44611.0</v>
       </c>
       <c r="D418" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="419">
@@ -5994,7 +5994,7 @@
         <v>2022.0</v>
       </c>
       <c r="C419" t="n" s="2">
-        <v>44625.0</v>
+        <v>44618.0</v>
       </c>
       <c r="D419" t="n">
         <v>5.0</v>
@@ -6008,10 +6008,10 @@
         <v>2022.0</v>
       </c>
       <c r="C420" t="n" s="2">
-        <v>44632.0</v>
+        <v>44625.0</v>
       </c>
       <c r="D420" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="421">
@@ -6022,10 +6022,10 @@
         <v>2022.0</v>
       </c>
       <c r="C421" t="n" s="2">
-        <v>44639.0</v>
+        <v>44632.0</v>
       </c>
       <c r="D421" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="422">
@@ -6036,10 +6036,10 @@
         <v>2022.0</v>
       </c>
       <c r="C422" t="n" s="2">
-        <v>44646.0</v>
+        <v>44639.0</v>
       </c>
       <c r="D422" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="423">
@@ -6050,10 +6050,10 @@
         <v>2022.0</v>
       </c>
       <c r="C423" t="n" s="2">
-        <v>44653.0</v>
+        <v>44646.0</v>
       </c>
       <c r="D423" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="424">
@@ -6064,10 +6064,10 @@
         <v>2022.0</v>
       </c>
       <c r="C424" t="n" s="2">
-        <v>44660.0</v>
+        <v>44653.0</v>
       </c>
       <c r="D424" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="425">
@@ -6078,10 +6078,10 @@
         <v>2022.0</v>
       </c>
       <c r="C425" t="n" s="2">
-        <v>44667.0</v>
+        <v>44660.0</v>
       </c>
       <c r="D425" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="426">
@@ -6092,10 +6092,10 @@
         <v>2022.0</v>
       </c>
       <c r="C426" t="n" s="2">
-        <v>44674.0</v>
+        <v>44667.0</v>
       </c>
       <c r="D426" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="427">
@@ -6106,10 +6106,10 @@
         <v>2022.0</v>
       </c>
       <c r="C427" t="n" s="2">
-        <v>44681.0</v>
+        <v>44674.0</v>
       </c>
       <c r="D427" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="428">
@@ -6120,10 +6120,10 @@
         <v>2022.0</v>
       </c>
       <c r="C428" t="n" s="2">
-        <v>44688.0</v>
+        <v>44681.0</v>
       </c>
       <c r="D428" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="429">
@@ -6134,10 +6134,10 @@
         <v>2022.0</v>
       </c>
       <c r="C429" t="n" s="2">
-        <v>44695.0</v>
+        <v>44688.0</v>
       </c>
       <c r="D429" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="430">
@@ -6148,10 +6148,10 @@
         <v>2022.0</v>
       </c>
       <c r="C430" t="n" s="2">
-        <v>44702.0</v>
+        <v>44695.0</v>
       </c>
       <c r="D430" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="431">
@@ -6162,10 +6162,10 @@
         <v>2022.0</v>
       </c>
       <c r="C431" t="n" s="2">
-        <v>44709.0</v>
+        <v>44702.0</v>
       </c>
       <c r="D431" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="432">
@@ -6176,10 +6176,10 @@
         <v>2022.0</v>
       </c>
       <c r="C432" t="n" s="2">
-        <v>44716.0</v>
+        <v>44709.0</v>
       </c>
       <c r="D432" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="433">
@@ -6190,10 +6190,10 @@
         <v>2022.0</v>
       </c>
       <c r="C433" t="n" s="2">
-        <v>44723.0</v>
+        <v>44716.0</v>
       </c>
       <c r="D433" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="434">
@@ -6204,10 +6204,10 @@
         <v>2022.0</v>
       </c>
       <c r="C434" t="n" s="2">
-        <v>44730.0</v>
+        <v>44723.0</v>
       </c>
       <c r="D434" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="435">
@@ -6218,7 +6218,7 @@
         <v>2022.0</v>
       </c>
       <c r="C435" t="n" s="2">
-        <v>44737.0</v>
+        <v>44730.0</v>
       </c>
       <c r="D435" t="n">
         <v>4.0</v>
@@ -6232,10 +6232,10 @@
         <v>2022.0</v>
       </c>
       <c r="C436" t="n" s="2">
-        <v>44744.0</v>
+        <v>44737.0</v>
       </c>
       <c r="D436" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="437">
@@ -6246,10 +6246,10 @@
         <v>2022.0</v>
       </c>
       <c r="C437" t="n" s="2">
-        <v>44751.0</v>
+        <v>44744.0</v>
       </c>
       <c r="D437" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="438">
@@ -6260,10 +6260,10 @@
         <v>2022.0</v>
       </c>
       <c r="C438" t="n" s="2">
-        <v>44758.0</v>
+        <v>44751.0</v>
       </c>
       <c r="D438" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="439">
@@ -6274,10 +6274,10 @@
         <v>2022.0</v>
       </c>
       <c r="C439" t="n" s="2">
-        <v>44765.0</v>
+        <v>44758.0</v>
       </c>
       <c r="D439" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="440">
@@ -6288,10 +6288,10 @@
         <v>2022.0</v>
       </c>
       <c r="C440" t="n" s="2">
-        <v>44779.0</v>
+        <v>44765.0</v>
       </c>
       <c r="D440" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="441">
@@ -6302,10 +6302,10 @@
         <v>2022.0</v>
       </c>
       <c r="C441" t="n" s="2">
-        <v>44786.0</v>
+        <v>44779.0</v>
       </c>
       <c r="D441" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="442">
@@ -6316,10 +6316,10 @@
         <v>2022.0</v>
       </c>
       <c r="C442" t="n" s="2">
-        <v>44863.0</v>
+        <v>44786.0</v>
       </c>
       <c r="D442" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="443">
@@ -6330,10 +6330,10 @@
         <v>2022.0</v>
       </c>
       <c r="C443" t="n" s="2">
-        <v>44870.0</v>
+        <v>44863.0</v>
       </c>
       <c r="D443" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="444">
@@ -6344,10 +6344,10 @@
         <v>2022.0</v>
       </c>
       <c r="C444" t="n" s="2">
-        <v>44884.0</v>
+        <v>44870.0</v>
       </c>
       <c r="D444" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="445">
@@ -6358,7 +6358,7 @@
         <v>2022.0</v>
       </c>
       <c r="C445" t="n" s="2">
-        <v>44891.0</v>
+        <v>44884.0</v>
       </c>
       <c r="D445" t="n">
         <v>2.0</v>
@@ -6372,10 +6372,10 @@
         <v>2022.0</v>
       </c>
       <c r="C446" t="n" s="2">
-        <v>44898.0</v>
+        <v>44891.0</v>
       </c>
       <c r="D446" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="447">
@@ -6386,10 +6386,10 @@
         <v>2022.0</v>
       </c>
       <c r="C447" t="n" s="2">
-        <v>44912.0</v>
+        <v>44898.0</v>
       </c>
       <c r="D447" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="448">
@@ -6400,10 +6400,10 @@
         <v>2022.0</v>
       </c>
       <c r="C448" t="n" s="2">
-        <v>44919.0</v>
+        <v>44912.0</v>
       </c>
       <c r="D448" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="449">
@@ -6414,10 +6414,10 @@
         <v>2022.0</v>
       </c>
       <c r="C449" t="n" s="2">
-        <v>44926.0</v>
+        <v>44919.0</v>
       </c>
       <c r="D449" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="450">
@@ -6425,13 +6425,13 @@
         <v>7</v>
       </c>
       <c r="B450" t="n">
-        <v>2023.0</v>
+        <v>2022.0</v>
       </c>
       <c r="C450" t="n" s="2">
-        <v>44934.0</v>
+        <v>44926.0</v>
       </c>
       <c r="D450" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="451">
@@ -6442,10 +6442,10 @@
         <v>2023.0</v>
       </c>
       <c r="C451" t="n" s="2">
-        <v>44941.0</v>
+        <v>44934.0</v>
       </c>
       <c r="D451" t="n">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="452">
@@ -6456,10 +6456,10 @@
         <v>2023.0</v>
       </c>
       <c r="C452" t="n" s="2">
-        <v>44948.0</v>
+        <v>44941.0</v>
       </c>
       <c r="D452" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="453">
@@ -6470,10 +6470,10 @@
         <v>2023.0</v>
       </c>
       <c r="C453" t="n" s="2">
-        <v>44955.0</v>
+        <v>44948.0</v>
       </c>
       <c r="D453" t="n">
-        <v>19.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="454">
@@ -6484,10 +6484,10 @@
         <v>2023.0</v>
       </c>
       <c r="C454" t="n" s="2">
-        <v>44962.0</v>
+        <v>44955.0</v>
       </c>
       <c r="D454" t="n">
-        <v>22.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="455">
@@ -6498,10 +6498,10 @@
         <v>2023.0</v>
       </c>
       <c r="C455" t="n" s="2">
-        <v>44969.0</v>
+        <v>44962.0</v>
       </c>
       <c r="D455" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="456">
@@ -6512,10 +6512,10 @@
         <v>2023.0</v>
       </c>
       <c r="C456" t="n" s="2">
-        <v>44976.0</v>
+        <v>44969.0</v>
       </c>
       <c r="D456" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="457">
@@ -6526,10 +6526,10 @@
         <v>2023.0</v>
       </c>
       <c r="C457" t="n" s="2">
-        <v>44983.0</v>
+        <v>44976.0</v>
       </c>
       <c r="D457" t="n">
-        <v>29.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="458">
@@ -6540,10 +6540,10 @@
         <v>2023.0</v>
       </c>
       <c r="C458" t="n" s="2">
-        <v>44990.0</v>
+        <v>44983.0</v>
       </c>
       <c r="D458" t="n">
-        <v>5.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="459">
@@ -6554,10 +6554,10 @@
         <v>2023.0</v>
       </c>
       <c r="C459" t="n" s="2">
-        <v>44997.0</v>
+        <v>44990.0</v>
       </c>
       <c r="D459" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="460">
@@ -6568,10 +6568,10 @@
         <v>2023.0</v>
       </c>
       <c r="C460" t="n" s="2">
-        <v>45004.0</v>
+        <v>44997.0</v>
       </c>
       <c r="D460" t="n">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="461">
@@ -6582,10 +6582,10 @@
         <v>2023.0</v>
       </c>
       <c r="C461" t="n" s="2">
-        <v>45011.0</v>
+        <v>45004.0</v>
       </c>
       <c r="D461" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="462">
@@ -6596,10 +6596,10 @@
         <v>2023.0</v>
       </c>
       <c r="C462" t="n" s="2">
-        <v>45018.0</v>
+        <v>45011.0</v>
       </c>
       <c r="D462" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="463">
@@ -6610,10 +6610,10 @@
         <v>2023.0</v>
       </c>
       <c r="C463" t="n" s="2">
-        <v>45025.0</v>
+        <v>45018.0</v>
       </c>
       <c r="D463" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="464">
@@ -6624,10 +6624,10 @@
         <v>2023.0</v>
       </c>
       <c r="C464" t="n" s="2">
-        <v>45032.0</v>
+        <v>45025.0</v>
       </c>
       <c r="D464" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="465">
@@ -6638,10 +6638,10 @@
         <v>2023.0</v>
       </c>
       <c r="C465" t="n" s="2">
-        <v>45039.0</v>
+        <v>45032.0</v>
       </c>
       <c r="D465" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="466">
@@ -6652,10 +6652,10 @@
         <v>2023.0</v>
       </c>
       <c r="C466" t="n" s="2">
-        <v>45046.0</v>
+        <v>45039.0</v>
       </c>
       <c r="D466" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="467">
@@ -6666,10 +6666,10 @@
         <v>2023.0</v>
       </c>
       <c r="C467" t="n" s="2">
-        <v>45053.0</v>
+        <v>45046.0</v>
       </c>
       <c r="D467" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="468">
@@ -6680,10 +6680,10 @@
         <v>2023.0</v>
       </c>
       <c r="C468" t="n" s="2">
-        <v>45060.0</v>
+        <v>45053.0</v>
       </c>
       <c r="D468" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="469">
@@ -6694,10 +6694,10 @@
         <v>2023.0</v>
       </c>
       <c r="C469" t="n" s="2">
-        <v>45067.0</v>
+        <v>45060.0</v>
       </c>
       <c r="D469" t="n">
-        <v>8.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="470">
@@ -6708,7 +6708,7 @@
         <v>2023.0</v>
       </c>
       <c r="C470" t="n" s="2">
-        <v>45074.0</v>
+        <v>45067.0</v>
       </c>
       <c r="D470" t="n">
         <v>8.0</v>
@@ -6722,10 +6722,10 @@
         <v>2023.0</v>
       </c>
       <c r="C471" t="n" s="2">
-        <v>45081.0</v>
+        <v>45074.0</v>
       </c>
       <c r="D471" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="472">
@@ -6736,10 +6736,10 @@
         <v>2023.0</v>
       </c>
       <c r="C472" t="n" s="2">
-        <v>45088.0</v>
+        <v>45081.0</v>
       </c>
       <c r="D472" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="473">
@@ -6750,10 +6750,10 @@
         <v>2023.0</v>
       </c>
       <c r="C473" t="n" s="2">
-        <v>45095.0</v>
+        <v>45088.0</v>
       </c>
       <c r="D473" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="474">
@@ -6764,10 +6764,10 @@
         <v>2023.0</v>
       </c>
       <c r="C474" t="n" s="2">
-        <v>45102.0</v>
+        <v>45095.0</v>
       </c>
       <c r="D474" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="475">
@@ -6778,10 +6778,10 @@
         <v>2023.0</v>
       </c>
       <c r="C475" t="n" s="2">
-        <v>45109.0</v>
+        <v>45102.0</v>
       </c>
       <c r="D475" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="476">
@@ -6792,10 +6792,10 @@
         <v>2023.0</v>
       </c>
       <c r="C476" t="n" s="2">
-        <v>45116.0</v>
+        <v>45109.0</v>
       </c>
       <c r="D476" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="477">
@@ -6806,10 +6806,10 @@
         <v>2023.0</v>
       </c>
       <c r="C477" t="n" s="2">
-        <v>45123.0</v>
+        <v>45116.0</v>
       </c>
       <c r="D477" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="478">
@@ -6820,7 +6820,7 @@
         <v>2023.0</v>
       </c>
       <c r="C478" t="n" s="2">
-        <v>45130.0</v>
+        <v>45123.0</v>
       </c>
       <c r="D478" t="n">
         <v>6.0</v>
@@ -6834,10 +6834,10 @@
         <v>2023.0</v>
       </c>
       <c r="C479" t="n" s="2">
-        <v>45137.0</v>
+        <v>45130.0</v>
       </c>
       <c r="D479" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="480">
@@ -6848,7 +6848,7 @@
         <v>2023.0</v>
       </c>
       <c r="C480" t="n" s="2">
-        <v>45144.0</v>
+        <v>45137.0</v>
       </c>
       <c r="D480" t="n">
         <v>2.0</v>
@@ -6862,7 +6862,7 @@
         <v>2023.0</v>
       </c>
       <c r="C481" t="n" s="2">
-        <v>45151.0</v>
+        <v>45144.0</v>
       </c>
       <c r="D481" t="n">
         <v>2.0</v>
@@ -6876,7 +6876,7 @@
         <v>2023.0</v>
       </c>
       <c r="C482" t="n" s="2">
-        <v>45165.0</v>
+        <v>45151.0</v>
       </c>
       <c r="D482" t="n">
         <v>2.0</v>
@@ -6890,7 +6890,7 @@
         <v>2023.0</v>
       </c>
       <c r="C483" t="n" s="2">
-        <v>45172.0</v>
+        <v>45165.0</v>
       </c>
       <c r="D483" t="n">
         <v>2.0</v>
@@ -6904,10 +6904,10 @@
         <v>2023.0</v>
       </c>
       <c r="C484" t="n" s="2">
-        <v>45179.0</v>
+        <v>45172.0</v>
       </c>
       <c r="D484" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="485">
@@ -6918,7 +6918,7 @@
         <v>2023.0</v>
       </c>
       <c r="C485" t="n" s="2">
-        <v>45186.0</v>
+        <v>45179.0</v>
       </c>
       <c r="D485" t="n">
         <v>1.0</v>
@@ -6932,7 +6932,7 @@
         <v>2023.0</v>
       </c>
       <c r="C486" t="n" s="2">
-        <v>45193.0</v>
+        <v>45186.0</v>
       </c>
       <c r="D486" t="n">
         <v>1.0</v>
@@ -6946,7 +6946,7 @@
         <v>2023.0</v>
       </c>
       <c r="C487" t="n" s="2">
-        <v>45200.0</v>
+        <v>45193.0</v>
       </c>
       <c r="D487" t="n">
         <v>1.0</v>
@@ -6960,7 +6960,7 @@
         <v>2023.0</v>
       </c>
       <c r="C488" t="n" s="2">
-        <v>45207.0</v>
+        <v>45200.0</v>
       </c>
       <c r="D488" t="n">
         <v>1.0</v>
@@ -6974,7 +6974,7 @@
         <v>2023.0</v>
       </c>
       <c r="C489" t="n" s="2">
-        <v>45235.0</v>
+        <v>45207.0</v>
       </c>
       <c r="D489" t="n">
         <v>1.0</v>
@@ -6988,10 +6988,10 @@
         <v>2023.0</v>
       </c>
       <c r="C490" t="n" s="2">
-        <v>45242.0</v>
+        <v>45235.0</v>
       </c>
       <c r="D490" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="491">
@@ -7002,10 +7002,10 @@
         <v>2023.0</v>
       </c>
       <c r="C491" t="n" s="2">
-        <v>45249.0</v>
+        <v>45242.0</v>
       </c>
       <c r="D491" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="492">
@@ -7016,10 +7016,10 @@
         <v>2023.0</v>
       </c>
       <c r="C492" t="n" s="2">
-        <v>45256.0</v>
+        <v>45249.0</v>
       </c>
       <c r="D492" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="493">
@@ -7030,10 +7030,10 @@
         <v>2023.0</v>
       </c>
       <c r="C493" t="n" s="2">
-        <v>45263.0</v>
+        <v>45256.0</v>
       </c>
       <c r="D493" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="494">
@@ -7044,10 +7044,10 @@
         <v>2023.0</v>
       </c>
       <c r="C494" t="n" s="2">
-        <v>45270.0</v>
+        <v>45263.0</v>
       </c>
       <c r="D494" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="495">
@@ -7058,10 +7058,10 @@
         <v>2023.0</v>
       </c>
       <c r="C495" t="n" s="2">
-        <v>45277.0</v>
+        <v>45270.0</v>
       </c>
       <c r="D495" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="496">
@@ -7072,7 +7072,7 @@
         <v>2023.0</v>
       </c>
       <c r="C496" t="n" s="2">
-        <v>45284.0</v>
+        <v>45277.0</v>
       </c>
       <c r="D496" t="n">
         <v>7.0</v>
@@ -7086,10 +7086,10 @@
         <v>2023.0</v>
       </c>
       <c r="C497" t="n" s="2">
-        <v>45291.0</v>
+        <v>45284.0</v>
       </c>
       <c r="D497" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="498">
@@ -7097,13 +7097,13 @@
         <v>7</v>
       </c>
       <c r="B498" t="n">
-        <v>2024.0</v>
+        <v>2023.0</v>
       </c>
       <c r="C498" t="n" s="2">
-        <v>45299.0</v>
+        <v>45291.0</v>
       </c>
       <c r="D498" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="499">
@@ -7114,10 +7114,10 @@
         <v>2024.0</v>
       </c>
       <c r="C499" t="n" s="2">
-        <v>45306.0</v>
+        <v>45299.0</v>
       </c>
       <c r="D499" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="500">
@@ -7128,10 +7128,10 @@
         <v>2024.0</v>
       </c>
       <c r="C500" t="n" s="2">
-        <v>45313.0</v>
+        <v>45306.0</v>
       </c>
       <c r="D500" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="501">
@@ -7142,10 +7142,10 @@
         <v>2024.0</v>
       </c>
       <c r="C501" t="n" s="2">
-        <v>45320.0</v>
+        <v>45313.0</v>
       </c>
       <c r="D501" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="502">
@@ -7156,10 +7156,10 @@
         <v>2024.0</v>
       </c>
       <c r="C502" t="n" s="2">
-        <v>45327.0</v>
+        <v>45320.0</v>
       </c>
       <c r="D502" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="503">
@@ -7170,10 +7170,10 @@
         <v>2024.0</v>
       </c>
       <c r="C503" t="n" s="2">
-        <v>45334.0</v>
+        <v>45327.0</v>
       </c>
       <c r="D503" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="504">
@@ -7184,10 +7184,10 @@
         <v>2024.0</v>
       </c>
       <c r="C504" t="n" s="2">
-        <v>45341.0</v>
+        <v>45334.0</v>
       </c>
       <c r="D504" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="505">
@@ -7198,10 +7198,10 @@
         <v>2024.0</v>
       </c>
       <c r="C505" t="n" s="2">
-        <v>45348.0</v>
+        <v>45341.0</v>
       </c>
       <c r="D505" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="506">
@@ -7212,10 +7212,10 @@
         <v>2024.0</v>
       </c>
       <c r="C506" t="n" s="2">
-        <v>45355.0</v>
+        <v>45348.0</v>
       </c>
       <c r="D506" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="507">
@@ -7226,10 +7226,10 @@
         <v>2024.0</v>
       </c>
       <c r="C507" t="n" s="2">
-        <v>45362.0</v>
+        <v>45355.0</v>
       </c>
       <c r="D507" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="508">
@@ -7240,10 +7240,10 @@
         <v>2024.0</v>
       </c>
       <c r="C508" t="n" s="2">
-        <v>45369.0</v>
+        <v>45362.0</v>
       </c>
       <c r="D508" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="509">
@@ -7254,10 +7254,10 @@
         <v>2024.0</v>
       </c>
       <c r="C509" t="n" s="2">
-        <v>45376.0</v>
+        <v>45369.0</v>
       </c>
       <c r="D509" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="510">
@@ -7268,10 +7268,10 @@
         <v>2024.0</v>
       </c>
       <c r="C510" t="n" s="2">
-        <v>45383.0</v>
+        <v>45376.0</v>
       </c>
       <c r="D510" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="511">
@@ -7282,10 +7282,10 @@
         <v>2024.0</v>
       </c>
       <c r="C511" t="n" s="2">
-        <v>45390.0</v>
+        <v>45383.0</v>
       </c>
       <c r="D511" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512">
@@ -7296,7 +7296,7 @@
         <v>2024.0</v>
       </c>
       <c r="C512" t="n" s="2">
-        <v>45397.0</v>
+        <v>45390.0</v>
       </c>
       <c r="D512" t="n">
         <v>1.0</v>
@@ -7310,10 +7310,10 @@
         <v>2024.0</v>
       </c>
       <c r="C513" t="n" s="2">
-        <v>45404.0</v>
+        <v>45397.0</v>
       </c>
       <c r="D513" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="514">
@@ -7324,10 +7324,10 @@
         <v>2024.0</v>
       </c>
       <c r="C514" t="n" s="2">
-        <v>45411.0</v>
+        <v>45404.0</v>
       </c>
       <c r="D514" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="515">
@@ -7338,10 +7338,10 @@
         <v>2024.0</v>
       </c>
       <c r="C515" t="n" s="2">
-        <v>45439.0</v>
+        <v>45411.0</v>
       </c>
       <c r="D515" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="516">
@@ -7352,10 +7352,10 @@
         <v>2024.0</v>
       </c>
       <c r="C516" t="n" s="2">
-        <v>45446.0</v>
+        <v>45439.0</v>
       </c>
       <c r="D516" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="517">
@@ -7366,7 +7366,7 @@
         <v>2024.0</v>
       </c>
       <c r="C517" t="n" s="2">
-        <v>45460.0</v>
+        <v>45446.0</v>
       </c>
       <c r="D517" t="n">
         <v>1.0</v>
@@ -7380,7 +7380,7 @@
         <v>2024.0</v>
       </c>
       <c r="C518" t="n" s="2">
-        <v>45481.0</v>
+        <v>45460.0</v>
       </c>
       <c r="D518" t="n">
         <v>1.0</v>
@@ -7394,7 +7394,7 @@
         <v>2024.0</v>
       </c>
       <c r="C519" t="n" s="2">
-        <v>45516.0</v>
+        <v>45481.0</v>
       </c>
       <c r="D519" t="n">
         <v>1.0</v>
@@ -7408,7 +7408,7 @@
         <v>2024.0</v>
       </c>
       <c r="C520" t="n" s="2">
-        <v>45551.0</v>
+        <v>45516.0</v>
       </c>
       <c r="D520" t="n">
         <v>1.0</v>
@@ -7422,7 +7422,7 @@
         <v>2024.0</v>
       </c>
       <c r="C521" t="n" s="2">
-        <v>45579.0</v>
+        <v>45551.0</v>
       </c>
       <c r="D521" t="n">
         <v>1.0</v>
@@ -7436,7 +7436,7 @@
         <v>2024.0</v>
       </c>
       <c r="C522" t="n" s="2">
-        <v>45614.0</v>
+        <v>45579.0</v>
       </c>
       <c r="D522" t="n">
         <v>1.0</v>
@@ -7450,10 +7450,10 @@
         <v>2024.0</v>
       </c>
       <c r="C523" t="n" s="2">
-        <v>45635.0</v>
+        <v>45614.0</v>
       </c>
       <c r="D523" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="524">
@@ -7464,10 +7464,10 @@
         <v>2024.0</v>
       </c>
       <c r="C524" t="n" s="2">
-        <v>45642.0</v>
+        <v>45635.0</v>
       </c>
       <c r="D524" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="525">
@@ -7478,10 +7478,10 @@
         <v>2024.0</v>
       </c>
       <c r="C525" t="n" s="2">
-        <v>45649.0</v>
+        <v>45642.0</v>
       </c>
       <c r="D525" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="526">
@@ -7492,10 +7492,10 @@
         <v>2024.0</v>
       </c>
       <c r="C526" t="n" s="2">
-        <v>45656.0</v>
+        <v>45649.0</v>
       </c>
       <c r="D526" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="527">
@@ -7503,13 +7503,13 @@
         <v>7</v>
       </c>
       <c r="B527" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C527" t="n" s="2">
-        <v>45665.0</v>
+        <v>45656.0</v>
       </c>
       <c r="D527" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="528">
@@ -7520,10 +7520,10 @@
         <v>2025.0</v>
       </c>
       <c r="C528" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D528" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="529">
@@ -7534,7 +7534,7 @@
         <v>2025.0</v>
       </c>
       <c r="C529" t="n" s="2">
-        <v>45686.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D529" t="n">
         <v>2.0</v>
@@ -7548,10 +7548,10 @@
         <v>2025.0</v>
       </c>
       <c r="C530" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D530" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="531">
@@ -7562,10 +7562,10 @@
         <v>2025.0</v>
       </c>
       <c r="C531" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D531" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="532">
@@ -7576,10 +7576,10 @@
         <v>2025.0</v>
       </c>
       <c r="C532" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D532" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="533">
@@ -7590,10 +7590,10 @@
         <v>2025.0</v>
       </c>
       <c r="C533" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D533" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="534">
@@ -7604,10 +7604,10 @@
         <v>2025.0</v>
       </c>
       <c r="C534" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D534" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="535">
@@ -7618,10 +7618,10 @@
         <v>2025.0</v>
       </c>
       <c r="C535" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D535" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="536">
@@ -7632,10 +7632,10 @@
         <v>2025.0</v>
       </c>
       <c r="C536" t="n" s="2">
-        <v>45735.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D536" t="n">
-        <v>19.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="537">
@@ -7646,10 +7646,10 @@
         <v>2025.0</v>
       </c>
       <c r="C537" t="n" s="2">
-        <v>45742.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D537" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="538">
@@ -7660,10 +7660,10 @@
         <v>2025.0</v>
       </c>
       <c r="C538" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D538" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="539">
@@ -7674,10 +7674,10 @@
         <v>2025.0</v>
       </c>
       <c r="C539" t="n" s="2">
-        <v>45756.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D539" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="540">
@@ -7688,10 +7688,10 @@
         <v>2025.0</v>
       </c>
       <c r="C540" t="n" s="2">
-        <v>45763.0</v>
+        <v>45756.0</v>
       </c>
       <c r="D540" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="541">
@@ -7702,7 +7702,7 @@
         <v>2025.0</v>
       </c>
       <c r="C541" t="n" s="2">
-        <v>45770.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D541" t="n">
         <v>1.0</v>
@@ -7716,10 +7716,10 @@
         <v>2025.0</v>
       </c>
       <c r="C542" t="n" s="2">
-        <v>45784.0</v>
+        <v>45770.0</v>
       </c>
       <c r="D542" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="543">
@@ -7730,10 +7730,10 @@
         <v>2025.0</v>
       </c>
       <c r="C543" t="n" s="2">
-        <v>45791.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D543" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="544">
@@ -7744,10 +7744,10 @@
         <v>2025.0</v>
       </c>
       <c r="C544" t="n" s="2">
-        <v>45805.0</v>
+        <v>45791.0</v>
       </c>
       <c r="D544" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="545">
@@ -7758,10 +7758,10 @@
         <v>2025.0</v>
       </c>
       <c r="C545" t="n" s="2">
-        <v>45826.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D545" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="546">
@@ -7772,7 +7772,7 @@
         <v>2025.0</v>
       </c>
       <c r="C546" t="n" s="2">
-        <v>45861.0</v>
+        <v>45826.0</v>
       </c>
       <c r="D546" t="n">
         <v>2.0</v>
@@ -7786,10 +7786,10 @@
         <v>2025.0</v>
       </c>
       <c r="C547" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D547" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="548">
@@ -7800,7 +7800,7 @@
         <v>2025.0</v>
       </c>
       <c r="C548" t="n" s="2">
-        <v>45889.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D548" t="n">
         <v>1.0</v>
@@ -7814,7 +7814,7 @@
         <v>2025.0</v>
       </c>
       <c r="C549" t="n" s="2">
-        <v>45924.0</v>
+        <v>45889.0</v>
       </c>
       <c r="D549" t="n">
         <v>1.0</v>
@@ -7828,7 +7828,7 @@
         <v>2025.0</v>
       </c>
       <c r="C550" t="n" s="2">
-        <v>45945.0</v>
+        <v>45924.0</v>
       </c>
       <c r="D550" t="n">
         <v>1.0</v>
@@ -7842,10 +7842,10 @@
         <v>2025.0</v>
       </c>
       <c r="C551" t="n" s="2">
-        <v>45959.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D551" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="552">
@@ -7856,7 +7856,7 @@
         <v>2025.0</v>
       </c>
       <c r="C552" t="n" s="2">
-        <v>46001.0</v>
+        <v>45959.0</v>
       </c>
       <c r="D552" t="n">
         <v>2.0</v>
@@ -7870,10 +7870,10 @@
         <v>2025.0</v>
       </c>
       <c r="C553" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D553" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="554">
@@ -7884,7 +7884,7 @@
         <v>2025.0</v>
       </c>
       <c r="C554" t="n" s="2">
-        <v>46022.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D554" t="n">
         <v>1.0</v>
@@ -7895,10 +7895,10 @@
         <v>7</v>
       </c>
       <c r="B555" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C555" t="n" s="2">
-        <v>46030.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D555" t="n">
         <v>1.0</v>
@@ -7912,7 +7912,7 @@
         <v>2026.0</v>
       </c>
       <c r="C556" t="n" s="2">
-        <v>46051.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D556" t="n">
         <v>1.0</v>
@@ -7926,7 +7926,7 @@
         <v>2026.0</v>
       </c>
       <c r="C557" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D557" t="n">
         <v>1.0</v>
@@ -7940,10 +7940,10 @@
         <v>2026.0</v>
       </c>
       <c r="C558" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D558" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="559">
@@ -7954,10 +7954,10 @@
         <v>2026.0</v>
       </c>
       <c r="C559" t="n" s="2">
-        <v>46135.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D559" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="560">
@@ -7968,10 +7968,10 @@
         <v>2026.0</v>
       </c>
       <c r="C560" t="n" s="2">
-        <v>46156.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D560" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="561">
@@ -7982,10 +7982,10 @@
         <v>2026.0</v>
       </c>
       <c r="C561" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D561" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="562">
@@ -7996,10 +7996,10 @@
         <v>2026.0</v>
       </c>
       <c r="C562" t="n" s="2">
-        <v>46177.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D562" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="563">
@@ -8010,10 +8010,10 @@
         <v>2026.0</v>
       </c>
       <c r="C563" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D563" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="564">
@@ -8024,7 +8024,7 @@
         <v>2026.0</v>
       </c>
       <c r="C564" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D564" t="n">
         <v>1.0</v>
@@ -8038,10 +8038,10 @@
         <v>2026.0</v>
       </c>
       <c r="C565" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D565" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="566">
@@ -8052,10 +8052,10 @@
         <v>2026.0</v>
       </c>
       <c r="C566" t="n" s="2">
-        <v>46226.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D566" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="567">
@@ -8066,10 +8066,10 @@
         <v>2026.0</v>
       </c>
       <c r="C567" t="n" s="2">
-        <v>46240.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D567" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="568">
@@ -8080,7 +8080,7 @@
         <v>2026.0</v>
       </c>
       <c r="C568" t="n" s="2">
-        <v>46254.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D568" t="n">
         <v>1.0</v>
@@ -8094,10 +8094,10 @@
         <v>2026.0</v>
       </c>
       <c r="C569" t="n" s="2">
-        <v>46268.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D569" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="570">
@@ -8108,10 +8108,10 @@
         <v>2026.0</v>
       </c>
       <c r="C570" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D570" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="571">
@@ -8122,7 +8122,7 @@
         <v>2026.0</v>
       </c>
       <c r="C571" t="n" s="2">
-        <v>46282.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D571" t="n">
         <v>1.0</v>
@@ -8136,7 +8136,7 @@
         <v>2026.0</v>
       </c>
       <c r="C572" t="n" s="2">
-        <v>46289.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D572" t="n">
         <v>1.0</v>
@@ -8150,7 +8150,7 @@
         <v>2026.0</v>
       </c>
       <c r="C573" t="n" s="2">
-        <v>46303.0</v>
+        <v>46289.0</v>
       </c>
       <c r="D573" t="n">
         <v>1.0</v>
@@ -8164,7 +8164,7 @@
         <v>2026.0</v>
       </c>
       <c r="C574" t="n" s="2">
-        <v>46310.0</v>
+        <v>46303.0</v>
       </c>
       <c r="D574" t="n">
         <v>1.0</v>
@@ -8172,13 +8172,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B575" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C575" t="n" s="2">
-        <v>45495.0</v>
+        <v>46310.0</v>
       </c>
       <c r="D575" t="n">
         <v>1.0</v>
@@ -8192,10 +8192,10 @@
         <v>2024.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D576" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="577">
@@ -8203,13 +8203,13 @@
         <v>8</v>
       </c>
       <c r="B577" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D577" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="578">
@@ -8220,10 +8220,10 @@
         <v>2025.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D578" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D579" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D580" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D581" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D582" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D583" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D584" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D585" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D586" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,7 +8346,7 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D587" t="n">
         <v>1.0</v>
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D589" t="n">
         <v>1.0</v>
@@ -8388,10 +8388,10 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D590" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="591">
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D591" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,7 +8416,7 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D592" t="n">
         <v>1.0</v>
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D593" t="n">
         <v>1.0</v>
@@ -8444,10 +8444,10 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D594" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="595">
@@ -8458,7 +8458,7 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D595" t="n">
         <v>2.0</v>
@@ -8472,7 +8472,7 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D596" t="n">
         <v>2.0</v>
@@ -8486,10 +8486,10 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D597" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="598">
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D598" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D599" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D600" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D601" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,7 +8556,7 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D602" t="n">
         <v>1.0</v>
@@ -8570,7 +8570,7 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D603" t="n">
         <v>1.0</v>
@@ -8584,7 +8584,7 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D604" t="n">
         <v>1.0</v>
@@ -8598,10 +8598,10 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D605" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="606">
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D606" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,7 +8626,7 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D607" t="n">
         <v>2.0</v>
@@ -8640,10 +8640,10 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D608" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="609">
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D609" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D610" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D611" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D612" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2025.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D613" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2025.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D614" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2025.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D615" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2025.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D616" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="617">
@@ -8763,13 +8763,13 @@
         <v>8</v>
       </c>
       <c r="B617" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D617" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="618">
@@ -8780,10 +8780,10 @@
         <v>2026.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D618" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D619" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D620" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D621" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D622" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D623" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D624" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D625" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D626" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D627" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D628" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D629" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D630" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D631" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D632" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D633" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D634" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D635" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D636" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D637" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D638" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D639" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D640" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D641" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D642" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D643" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D644" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D645" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,10 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D646" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="647">
@@ -9186,10 +9186,10 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D647" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="648">
@@ -9200,10 +9200,10 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D648" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="649">
@@ -9214,10 +9214,10 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D649" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="650">
@@ -9228,10 +9228,10 @@
         <v>2026.0</v>
       </c>
       <c r="C650" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D650" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="651">
@@ -9242,7 +9242,7 @@
         <v>2026.0</v>
       </c>
       <c r="C651" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D651" t="n">
         <v>1.0</v>
@@ -9256,10 +9256,10 @@
         <v>2026.0</v>
       </c>
       <c r="C652" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D652" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="653">
@@ -9270,7 +9270,7 @@
         <v>2026.0</v>
       </c>
       <c r="C653" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D653" t="n">
         <v>2.0</v>
@@ -9284,10 +9284,10 @@
         <v>2026.0</v>
       </c>
       <c r="C654" t="n" s="2">
-        <v>46303.0</v>
+        <v>46296.0</v>
       </c>
       <c r="D654" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="655">
@@ -9298,9 +9298,23 @@
         <v>2026.0</v>
       </c>
       <c r="C655" t="n" s="2">
+        <v>46303.0</v>
+      </c>
+      <c r="D655" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="s">
+        <v>8</v>
+      </c>
+      <c r="B656" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C656" t="n" s="2">
         <v>46317.0</v>
       </c>
-      <c r="D655" t="n">
+      <c r="D656" t="n">
         <v>3.0</v>
       </c>
     </row>
@@ -9335,7 +9349,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
     </row>
     <row r="4">
@@ -9351,7 +9365,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2276.0</v>
+        <v>2277.0</v>
       </c>
     </row>
   </sheetData>
@@ -9449,7 +9463,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>375.0</v>
+        <v>376.0</v>
       </c>
     </row>
     <row r="9">
@@ -9471,7 +9485,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="11">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="23">
   <si>
     <t>NOME_REGIONE</t>
   </si>
@@ -8186,16 +8186,16 @@
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B576" t="n">
-        <v>2024.0</v>
+        <v>2026.0</v>
       </c>
       <c r="C576" t="n" s="2">
-        <v>45495.0</v>
+        <v>46324.0</v>
       </c>
       <c r="D576" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="577">
@@ -8206,10 +8206,10 @@
         <v>2024.0</v>
       </c>
       <c r="C577" t="n" s="2">
-        <v>45502.0</v>
+        <v>45495.0</v>
       </c>
       <c r="D577" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="578">
@@ -8217,13 +8217,13 @@
         <v>8</v>
       </c>
       <c r="B578" t="n">
-        <v>2025.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C578" t="n" s="2">
-        <v>45665.0</v>
+        <v>45502.0</v>
       </c>
       <c r="D578" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="579">
@@ -8234,10 +8234,10 @@
         <v>2025.0</v>
       </c>
       <c r="C579" t="n" s="2">
-        <v>45672.0</v>
+        <v>45665.0</v>
       </c>
       <c r="D579" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="580">
@@ -8248,10 +8248,10 @@
         <v>2025.0</v>
       </c>
       <c r="C580" t="n" s="2">
-        <v>45679.0</v>
+        <v>45672.0</v>
       </c>
       <c r="D580" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="581">
@@ -8262,10 +8262,10 @@
         <v>2025.0</v>
       </c>
       <c r="C581" t="n" s="2">
-        <v>45686.0</v>
+        <v>45679.0</v>
       </c>
       <c r="D581" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="582">
@@ -8276,10 +8276,10 @@
         <v>2025.0</v>
       </c>
       <c r="C582" t="n" s="2">
-        <v>45693.0</v>
+        <v>45686.0</v>
       </c>
       <c r="D582" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="583">
@@ -8290,10 +8290,10 @@
         <v>2025.0</v>
       </c>
       <c r="C583" t="n" s="2">
-        <v>45700.0</v>
+        <v>45693.0</v>
       </c>
       <c r="D583" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="584">
@@ -8304,10 +8304,10 @@
         <v>2025.0</v>
       </c>
       <c r="C584" t="n" s="2">
-        <v>45707.0</v>
+        <v>45700.0</v>
       </c>
       <c r="D584" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="585">
@@ -8318,10 +8318,10 @@
         <v>2025.0</v>
       </c>
       <c r="C585" t="n" s="2">
-        <v>45714.0</v>
+        <v>45707.0</v>
       </c>
       <c r="D585" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="586">
@@ -8332,10 +8332,10 @@
         <v>2025.0</v>
       </c>
       <c r="C586" t="n" s="2">
-        <v>45721.0</v>
+        <v>45714.0</v>
       </c>
       <c r="D586" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="587">
@@ -8346,10 +8346,10 @@
         <v>2025.0</v>
       </c>
       <c r="C587" t="n" s="2">
-        <v>45728.0</v>
+        <v>45721.0</v>
       </c>
       <c r="D587" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="588">
@@ -8360,7 +8360,7 @@
         <v>2025.0</v>
       </c>
       <c r="C588" t="n" s="2">
-        <v>45742.0</v>
+        <v>45728.0</v>
       </c>
       <c r="D588" t="n">
         <v>1.0</v>
@@ -8374,7 +8374,7 @@
         <v>2025.0</v>
       </c>
       <c r="C589" t="n" s="2">
-        <v>45749.0</v>
+        <v>45742.0</v>
       </c>
       <c r="D589" t="n">
         <v>1.0</v>
@@ -8388,7 +8388,7 @@
         <v>2025.0</v>
       </c>
       <c r="C590" t="n" s="2">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D590" t="n">
         <v>1.0</v>
@@ -8402,10 +8402,10 @@
         <v>2025.0</v>
       </c>
       <c r="C591" t="n" s="2">
-        <v>45777.0</v>
+        <v>45763.0</v>
       </c>
       <c r="D591" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="592">
@@ -8416,10 +8416,10 @@
         <v>2025.0</v>
       </c>
       <c r="C592" t="n" s="2">
-        <v>45784.0</v>
+        <v>45777.0</v>
       </c>
       <c r="D592" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="593">
@@ -8430,7 +8430,7 @@
         <v>2025.0</v>
       </c>
       <c r="C593" t="n" s="2">
-        <v>45798.0</v>
+        <v>45784.0</v>
       </c>
       <c r="D593" t="n">
         <v>1.0</v>
@@ -8444,7 +8444,7 @@
         <v>2025.0</v>
       </c>
       <c r="C594" t="n" s="2">
-        <v>45805.0</v>
+        <v>45798.0</v>
       </c>
       <c r="D594" t="n">
         <v>1.0</v>
@@ -8458,10 +8458,10 @@
         <v>2025.0</v>
       </c>
       <c r="C595" t="n" s="2">
-        <v>45812.0</v>
+        <v>45805.0</v>
       </c>
       <c r="D595" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="596">
@@ -8472,7 +8472,7 @@
         <v>2025.0</v>
       </c>
       <c r="C596" t="n" s="2">
-        <v>45819.0</v>
+        <v>45812.0</v>
       </c>
       <c r="D596" t="n">
         <v>2.0</v>
@@ -8486,7 +8486,7 @@
         <v>2025.0</v>
       </c>
       <c r="C597" t="n" s="2">
-        <v>45833.0</v>
+        <v>45819.0</v>
       </c>
       <c r="D597" t="n">
         <v>2.0</v>
@@ -8500,10 +8500,10 @@
         <v>2025.0</v>
       </c>
       <c r="C598" t="n" s="2">
-        <v>45847.0</v>
+        <v>45833.0</v>
       </c>
       <c r="D598" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="599">
@@ -8514,10 +8514,10 @@
         <v>2025.0</v>
       </c>
       <c r="C599" t="n" s="2">
-        <v>45854.0</v>
+        <v>45847.0</v>
       </c>
       <c r="D599" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="600">
@@ -8528,10 +8528,10 @@
         <v>2025.0</v>
       </c>
       <c r="C600" t="n" s="2">
-        <v>45861.0</v>
+        <v>45854.0</v>
       </c>
       <c r="D600" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="601">
@@ -8542,10 +8542,10 @@
         <v>2025.0</v>
       </c>
       <c r="C601" t="n" s="2">
-        <v>45868.0</v>
+        <v>45861.0</v>
       </c>
       <c r="D601" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="602">
@@ -8556,10 +8556,10 @@
         <v>2025.0</v>
       </c>
       <c r="C602" t="n" s="2">
-        <v>45875.0</v>
+        <v>45868.0</v>
       </c>
       <c r="D602" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="603">
@@ -8570,7 +8570,7 @@
         <v>2025.0</v>
       </c>
       <c r="C603" t="n" s="2">
-        <v>45896.0</v>
+        <v>45875.0</v>
       </c>
       <c r="D603" t="n">
         <v>1.0</v>
@@ -8584,7 +8584,7 @@
         <v>2025.0</v>
       </c>
       <c r="C604" t="n" s="2">
-        <v>45903.0</v>
+        <v>45896.0</v>
       </c>
       <c r="D604" t="n">
         <v>1.0</v>
@@ -8598,7 +8598,7 @@
         <v>2025.0</v>
       </c>
       <c r="C605" t="n" s="2">
-        <v>45931.0</v>
+        <v>45903.0</v>
       </c>
       <c r="D605" t="n">
         <v>1.0</v>
@@ -8612,10 +8612,10 @@
         <v>2025.0</v>
       </c>
       <c r="C606" t="n" s="2">
-        <v>45938.0</v>
+        <v>45931.0</v>
       </c>
       <c r="D606" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="607">
@@ -8626,10 +8626,10 @@
         <v>2025.0</v>
       </c>
       <c r="C607" t="n" s="2">
-        <v>45945.0</v>
+        <v>45938.0</v>
       </c>
       <c r="D607" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="608">
@@ -8640,7 +8640,7 @@
         <v>2025.0</v>
       </c>
       <c r="C608" t="n" s="2">
-        <v>45966.0</v>
+        <v>45945.0</v>
       </c>
       <c r="D608" t="n">
         <v>2.0</v>
@@ -8654,10 +8654,10 @@
         <v>2025.0</v>
       </c>
       <c r="C609" t="n" s="2">
-        <v>45973.0</v>
+        <v>45966.0</v>
       </c>
       <c r="D609" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="610">
@@ -8668,10 +8668,10 @@
         <v>2025.0</v>
       </c>
       <c r="C610" t="n" s="2">
-        <v>45980.0</v>
+        <v>45973.0</v>
       </c>
       <c r="D610" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="611">
@@ -8682,10 +8682,10 @@
         <v>2025.0</v>
       </c>
       <c r="C611" t="n" s="2">
-        <v>45987.0</v>
+        <v>45980.0</v>
       </c>
       <c r="D611" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="612">
@@ -8696,10 +8696,10 @@
         <v>2025.0</v>
       </c>
       <c r="C612" t="n" s="2">
-        <v>45994.0</v>
+        <v>45987.0</v>
       </c>
       <c r="D612" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="613">
@@ -8710,10 +8710,10 @@
         <v>2025.0</v>
       </c>
       <c r="C613" t="n" s="2">
-        <v>46001.0</v>
+        <v>45994.0</v>
       </c>
       <c r="D613" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="614">
@@ -8724,10 +8724,10 @@
         <v>2025.0</v>
       </c>
       <c r="C614" t="n" s="2">
-        <v>46008.0</v>
+        <v>46001.0</v>
       </c>
       <c r="D614" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="615">
@@ -8738,10 +8738,10 @@
         <v>2025.0</v>
       </c>
       <c r="C615" t="n" s="2">
-        <v>46015.0</v>
+        <v>46008.0</v>
       </c>
       <c r="D615" t="n">
-        <v>13.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="616">
@@ -8752,10 +8752,10 @@
         <v>2025.0</v>
       </c>
       <c r="C616" t="n" s="2">
-        <v>46022.0</v>
+        <v>46015.0</v>
       </c>
       <c r="D616" t="n">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="617">
@@ -8766,10 +8766,10 @@
         <v>2025.0</v>
       </c>
       <c r="C617" t="n" s="2">
-        <v>46029.0</v>
+        <v>46022.0</v>
       </c>
       <c r="D617" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="618">
@@ -8777,13 +8777,13 @@
         <v>8</v>
       </c>
       <c r="B618" t="n">
-        <v>2026.0</v>
+        <v>2025.0</v>
       </c>
       <c r="C618" t="n" s="2">
-        <v>46030.0</v>
+        <v>46029.0</v>
       </c>
       <c r="D618" t="n">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="619">
@@ -8794,10 +8794,10 @@
         <v>2026.0</v>
       </c>
       <c r="C619" t="n" s="2">
-        <v>46037.0</v>
+        <v>46030.0</v>
       </c>
       <c r="D619" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="620">
@@ -8808,10 +8808,10 @@
         <v>2026.0</v>
       </c>
       <c r="C620" t="n" s="2">
-        <v>46044.0</v>
+        <v>46037.0</v>
       </c>
       <c r="D620" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="621">
@@ -8822,10 +8822,10 @@
         <v>2026.0</v>
       </c>
       <c r="C621" t="n" s="2">
-        <v>46051.0</v>
+        <v>46044.0</v>
       </c>
       <c r="D621" t="n">
-        <v>18.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="622">
@@ -8836,10 +8836,10 @@
         <v>2026.0</v>
       </c>
       <c r="C622" t="n" s="2">
-        <v>46058.0</v>
+        <v>46051.0</v>
       </c>
       <c r="D622" t="n">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="623">
@@ -8850,10 +8850,10 @@
         <v>2026.0</v>
       </c>
       <c r="C623" t="n" s="2">
-        <v>46065.0</v>
+        <v>46058.0</v>
       </c>
       <c r="D623" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="624">
@@ -8864,10 +8864,10 @@
         <v>2026.0</v>
       </c>
       <c r="C624" t="n" s="2">
-        <v>46072.0</v>
+        <v>46065.0</v>
       </c>
       <c r="D624" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="625">
@@ -8878,10 +8878,10 @@
         <v>2026.0</v>
       </c>
       <c r="C625" t="n" s="2">
-        <v>46079.0</v>
+        <v>46072.0</v>
       </c>
       <c r="D625" t="n">
-        <v>24.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="626">
@@ -8892,10 +8892,10 @@
         <v>2026.0</v>
       </c>
       <c r="C626" t="n" s="2">
-        <v>46086.0</v>
+        <v>46079.0</v>
       </c>
       <c r="D626" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="627">
@@ -8906,10 +8906,10 @@
         <v>2026.0</v>
       </c>
       <c r="C627" t="n" s="2">
-        <v>46093.0</v>
+        <v>46086.0</v>
       </c>
       <c r="D627" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="628">
@@ -8920,10 +8920,10 @@
         <v>2026.0</v>
       </c>
       <c r="C628" t="n" s="2">
-        <v>46100.0</v>
+        <v>46093.0</v>
       </c>
       <c r="D628" t="n">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="629">
@@ -8934,10 +8934,10 @@
         <v>2026.0</v>
       </c>
       <c r="C629" t="n" s="2">
-        <v>46107.0</v>
+        <v>46100.0</v>
       </c>
       <c r="D629" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="630">
@@ -8948,10 +8948,10 @@
         <v>2026.0</v>
       </c>
       <c r="C630" t="n" s="2">
-        <v>46114.0</v>
+        <v>46107.0</v>
       </c>
       <c r="D630" t="n">
-        <v>10.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="631">
@@ -8962,10 +8962,10 @@
         <v>2026.0</v>
       </c>
       <c r="C631" t="n" s="2">
-        <v>46121.0</v>
+        <v>46114.0</v>
       </c>
       <c r="D631" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="632">
@@ -8976,10 +8976,10 @@
         <v>2026.0</v>
       </c>
       <c r="C632" t="n" s="2">
-        <v>46128.0</v>
+        <v>46121.0</v>
       </c>
       <c r="D632" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="633">
@@ -8990,10 +8990,10 @@
         <v>2026.0</v>
       </c>
       <c r="C633" t="n" s="2">
-        <v>46135.0</v>
+        <v>46128.0</v>
       </c>
       <c r="D633" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="634">
@@ -9004,10 +9004,10 @@
         <v>2026.0</v>
       </c>
       <c r="C634" t="n" s="2">
-        <v>46142.0</v>
+        <v>46135.0</v>
       </c>
       <c r="D634" t="n">
-        <v>22.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="635">
@@ -9018,10 +9018,10 @@
         <v>2026.0</v>
       </c>
       <c r="C635" t="n" s="2">
-        <v>46149.0</v>
+        <v>46142.0</v>
       </c>
       <c r="D635" t="n">
-        <v>6.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="636">
@@ -9032,10 +9032,10 @@
         <v>2026.0</v>
       </c>
       <c r="C636" t="n" s="2">
-        <v>46156.0</v>
+        <v>46149.0</v>
       </c>
       <c r="D636" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="637">
@@ -9046,10 +9046,10 @@
         <v>2026.0</v>
       </c>
       <c r="C637" t="n" s="2">
-        <v>46163.0</v>
+        <v>46156.0</v>
       </c>
       <c r="D637" t="n">
-        <v>13.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="638">
@@ -9060,10 +9060,10 @@
         <v>2026.0</v>
       </c>
       <c r="C638" t="n" s="2">
-        <v>46170.0</v>
+        <v>46163.0</v>
       </c>
       <c r="D638" t="n">
-        <v>28.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="639">
@@ -9074,10 +9074,10 @@
         <v>2026.0</v>
       </c>
       <c r="C639" t="n" s="2">
-        <v>46177.0</v>
+        <v>46170.0</v>
       </c>
       <c r="D639" t="n">
-        <v>16.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="640">
@@ -9088,10 +9088,10 @@
         <v>2026.0</v>
       </c>
       <c r="C640" t="n" s="2">
-        <v>46184.0</v>
+        <v>46177.0</v>
       </c>
       <c r="D640" t="n">
-        <v>32.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="641">
@@ -9102,10 +9102,10 @@
         <v>2026.0</v>
       </c>
       <c r="C641" t="n" s="2">
-        <v>46191.0</v>
+        <v>46184.0</v>
       </c>
       <c r="D641" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="642">
@@ -9116,10 +9116,10 @@
         <v>2026.0</v>
       </c>
       <c r="C642" t="n" s="2">
-        <v>46198.0</v>
+        <v>46191.0</v>
       </c>
       <c r="D642" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="643">
@@ -9130,10 +9130,10 @@
         <v>2026.0</v>
       </c>
       <c r="C643" t="n" s="2">
-        <v>46205.0</v>
+        <v>46198.0</v>
       </c>
       <c r="D643" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="644">
@@ -9144,10 +9144,10 @@
         <v>2026.0</v>
       </c>
       <c r="C644" t="n" s="2">
-        <v>46212.0</v>
+        <v>46205.0</v>
       </c>
       <c r="D644" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="645">
@@ -9158,10 +9158,10 @@
         <v>2026.0</v>
       </c>
       <c r="C645" t="n" s="2">
-        <v>46219.0</v>
+        <v>46212.0</v>
       </c>
       <c r="D645" t="n">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="646">
@@ -9172,10 +9172,10 @@
         <v>2026.0</v>
       </c>
       <c r="C646" t="n" s="2">
-        <v>46226.0</v>
+        <v>46219.0</v>
       </c>
       <c r="D646" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="647">
@@ -9186,10 +9186,10 @@
         <v>2026.0</v>
       </c>
       <c r="C647" t="n" s="2">
-        <v>46233.0</v>
+        <v>46226.0</v>
       </c>
       <c r="D647" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="648">
@@ -9200,10 +9200,10 @@
         <v>2026.0</v>
       </c>
       <c r="C648" t="n" s="2">
-        <v>46240.0</v>
+        <v>46233.0</v>
       </c>
       <c r="D648" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="649">
@@ -9214,10 +9214,10 @@
         <v>2026.0</v>
       </c>
       <c r="C649" t="n" s="2">
-        <v>46247.0</v>
+        <v>46240.0</v>
       </c>
       <c r="D649" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="650">
@@ -9228,10 +9228,10 @@
         <v>2026.0</v>
       </c>
       <c r="C650" t="n" s="2">
-        <v>46254.0</v>
+        <v>46247.0</v>
       </c>
       <c r="D650" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="651">
@@ -9242,10 +9242,10 @@
         <v>2026.0</v>
       </c>
       <c r="C651" t="n" s="2">
-        <v>46261.0</v>
+        <v>46254.0</v>
       </c>
       <c r="D651" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="652">
@@ -9256,7 +9256,7 @@
         <v>2026.0</v>
       </c>
       <c r="C652" t="n" s="2">
-        <v>46268.0</v>
+        <v>46261.0</v>
       </c>
       <c r="D652" t="n">
         <v>1.0</v>
@@ -9270,10 +9270,10 @@
         <v>2026.0</v>
       </c>
       <c r="C653" t="n" s="2">
-        <v>46275.0</v>
+        <v>46268.0</v>
       </c>
       <c r="D653" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="654">
@@ -9284,7 +9284,7 @@
         <v>2026.0</v>
       </c>
       <c r="C654" t="n" s="2">
-        <v>46296.0</v>
+        <v>46275.0</v>
       </c>
       <c r="D654" t="n">
         <v>2.0</v>
@@ -9298,10 +9298,10 @@
         <v>2026.0</v>
       </c>
       <c r="C655" t="n" s="2">
-        <v>46303.0</v>
+        <v>46296.0</v>
       </c>
       <c r="D655" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="656">
@@ -9312,9 +9312,23 @@
         <v>2026.0</v>
       </c>
       <c r="C656" t="n" s="2">
+        <v>46303.0</v>
+      </c>
+      <c r="D656" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="s">
+        <v>8</v>
+      </c>
+      <c r="B657" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C657" t="n" s="2">
         <v>46317.0</v>
       </c>
-      <c r="D656" t="n">
+      <c r="D657" t="n">
         <v>3.0</v>
       </c>
     </row>
@@ -9365,7 +9379,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>2277.0</v>
+        <v>2279.0</v>
       </c>
     </row>
   </sheetData>
@@ -9430,7 +9444,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>482.0</v>
+        <v>483.0</v>
       </c>
     </row>
     <row r="6">
@@ -9463,7 +9477,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
     </row>
     <row r="9">

--- a/Download/Focus_Positivi_ZR.xlsx
+++ b/Download/Focus_Positivi_ZR.xlsx
@@ -1909,7 +1909,7 @@
         <v>46324.0</v>
       </c>
       <c r="D127" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="128">
@@ -9371,7 +9371,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1568.0</v>
+        <v>1569.0</v>
       </c>
     </row>
     <row r="5">
@@ -9543,7 +9543,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>516.0</v>
+        <v>517.0</v>
       </c>
     </row>
     <row r="15">
